--- a/artfynd/A 23758-2025 artfynd.xlsx
+++ b/artfynd/A 23758-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126091099</v>
+        <v>126091089</v>
       </c>
       <c r="B2" t="n">
-        <v>98243</v>
+        <v>80076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220093</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>557073</v>
+        <v>557054</v>
       </c>
       <c r="R2" t="n">
-        <v>7227326</v>
+        <v>7227146</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -754,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126091092</v>
+        <v>126091099</v>
       </c>
       <c r="B3" t="n">
-        <v>79979</v>
+        <v>98243</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>220093</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556906</v>
+        <v>557073</v>
       </c>
       <c r="R3" t="n">
-        <v>7227086</v>
+        <v>7227326</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -842,12 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -856,6 +855,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -878,32 +878,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126091089</v>
+        <v>126091092</v>
       </c>
       <c r="B4" t="n">
-        <v>80076</v>
+        <v>79979</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>557054</v>
+        <v>556906</v>
       </c>
       <c r="R4" t="n">
-        <v>7227146</v>
+        <v>7227086</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126091117</v>
+        <v>126091087</v>
       </c>
       <c r="B7" t="n">
-        <v>57807</v>
+        <v>80076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103022</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556827</v>
+        <v>556869</v>
       </c>
       <c r="R7" t="n">
-        <v>7227124</v>
+        <v>7227096</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1392,10 +1392,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126091087</v>
+        <v>126091117</v>
       </c>
       <c r="B9" t="n">
-        <v>80076</v>
+        <v>57807</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1403,21 +1403,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>103022</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556869</v>
+        <v>556827</v>
       </c>
       <c r="R9" t="n">
-        <v>7227096</v>
+        <v>7227124</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1897,32 +1897,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126091112</v>
+        <v>126091118</v>
       </c>
       <c r="B14" t="n">
-        <v>57755</v>
+        <v>57807</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103031</v>
+        <v>103022</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>556726</v>
+        <v>556859</v>
       </c>
       <c r="R14" t="n">
-        <v>7227088</v>
+        <v>7227119</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1998,32 +1998,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126091118</v>
+        <v>126091112</v>
       </c>
       <c r="B15" t="n">
-        <v>57807</v>
+        <v>57755</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103022</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2033,10 +2033,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>556859</v>
+        <v>556726</v>
       </c>
       <c r="R15" t="n">
-        <v>7227119</v>
+        <v>7227088</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2099,10 +2099,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126091159</v>
+        <v>126091083</v>
       </c>
       <c r="B16" t="n">
-        <v>78972</v>
+        <v>80076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2110,21 +2110,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2134,10 +2134,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>557055</v>
+        <v>556975</v>
       </c>
       <c r="R16" t="n">
-        <v>7227102</v>
+        <v>7227303</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2164,12 +2164,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2200,10 +2200,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126091083</v>
+        <v>126091159</v>
       </c>
       <c r="B17" t="n">
-        <v>80076</v>
+        <v>78972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2211,21 +2211,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>556975</v>
+        <v>557055</v>
       </c>
       <c r="R17" t="n">
-        <v>7227303</v>
+        <v>7227102</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2265,12 +2265,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2301,10 +2301,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126091156</v>
+        <v>126091079</v>
       </c>
       <c r="B18" t="n">
-        <v>78972</v>
+        <v>80076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2312,21 +2312,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2336,10 +2336,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>556815</v>
+        <v>556916</v>
       </c>
       <c r="R18" t="n">
-        <v>7227118</v>
+        <v>7227278</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2366,12 +2366,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2402,10 +2402,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126091079</v>
+        <v>126091022</v>
       </c>
       <c r="B19" t="n">
-        <v>80076</v>
+        <v>91232</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2413,21 +2413,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2437,10 +2437,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>556916</v>
+        <v>557054</v>
       </c>
       <c r="R19" t="n">
-        <v>7227278</v>
+        <v>7227356</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2503,10 +2503,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126091157</v>
+        <v>126091088</v>
       </c>
       <c r="B20" t="n">
-        <v>78972</v>
+        <v>80076</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2514,21 +2514,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2538,10 +2538,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>556844</v>
+        <v>557057</v>
       </c>
       <c r="R20" t="n">
-        <v>7227129</v>
+        <v>7227107</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2574,11 +2574,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Fertil</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2609,10 +2604,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126091022</v>
+        <v>126091156</v>
       </c>
       <c r="B21" t="n">
-        <v>91232</v>
+        <v>78972</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2620,21 +2615,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2644,10 +2639,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>557054</v>
+        <v>556815</v>
       </c>
       <c r="R21" t="n">
-        <v>7227356</v>
+        <v>7227118</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2674,12 +2669,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2710,10 +2705,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126091088</v>
+        <v>126091157</v>
       </c>
       <c r="B22" t="n">
-        <v>80076</v>
+        <v>78972</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2721,21 +2716,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2745,10 +2740,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>557057</v>
+        <v>556844</v>
       </c>
       <c r="R22" t="n">
-        <v>7227107</v>
+        <v>7227129</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2781,6 +2776,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3013,32 +3013,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126091096</v>
+        <v>126091048</v>
       </c>
       <c r="B25" t="n">
-        <v>57651</v>
+        <v>80104</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3048,10 +3048,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>556986</v>
+        <v>556737</v>
       </c>
       <c r="R25" t="n">
-        <v>7227133</v>
+        <v>7227086</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3084,11 +3084,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3119,32 +3114,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126091048</v>
+        <v>126091096</v>
       </c>
       <c r="B26" t="n">
-        <v>80104</v>
+        <v>57651</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3154,10 +3149,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>556737</v>
+        <v>556986</v>
       </c>
       <c r="R26" t="n">
-        <v>7227086</v>
+        <v>7227133</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3190,6 +3185,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3220,10 +3220,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126091021</v>
+        <v>126091158</v>
       </c>
       <c r="B27" t="n">
-        <v>91232</v>
+        <v>78972</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3231,21 +3231,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3255,10 +3255,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>557035</v>
+        <v>556943</v>
       </c>
       <c r="R27" t="n">
-        <v>7227275</v>
+        <v>7227059</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3285,12 +3285,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3422,10 +3422,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126091158</v>
+        <v>126091021</v>
       </c>
       <c r="B29" t="n">
-        <v>78972</v>
+        <v>91232</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3433,21 +3433,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3457,10 +3457,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>556943</v>
+        <v>557035</v>
       </c>
       <c r="R29" t="n">
-        <v>7227059</v>
+        <v>7227275</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3487,12 +3487,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3523,32 +3523,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126091045</v>
+        <v>126091078</v>
       </c>
       <c r="B30" t="n">
-        <v>80104</v>
+        <v>80076</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3558,10 +3558,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>556904</v>
+        <v>556918</v>
       </c>
       <c r="R30" t="n">
-        <v>7227312</v>
+        <v>7227271</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3624,32 +3624,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126091078</v>
+        <v>126091122</v>
       </c>
       <c r="B31" t="n">
-        <v>80076</v>
+        <v>91592</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>2063</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3659,10 +3659,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>556918</v>
+        <v>556726</v>
       </c>
       <c r="R31" t="n">
-        <v>7227271</v>
+        <v>7227064</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3689,12 +3689,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3725,10 +3725,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126091133</v>
+        <v>126091077</v>
       </c>
       <c r="B32" t="n">
-        <v>91250</v>
+        <v>80076</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3736,21 +3736,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3760,10 +3760,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>556729</v>
+        <v>556902</v>
       </c>
       <c r="R32" t="n">
-        <v>7227082</v>
+        <v>7227281</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3790,12 +3790,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3826,32 +3826,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126091097</v>
+        <v>126091133</v>
       </c>
       <c r="B33" t="n">
-        <v>97223</v>
+        <v>91250</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221941</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>557160</v>
+        <v>556729</v>
       </c>
       <c r="R33" t="n">
-        <v>7227183</v>
+        <v>7227082</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3927,32 +3927,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126091077</v>
+        <v>126091045</v>
       </c>
       <c r="B34" t="n">
-        <v>80076</v>
+        <v>80104</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3962,10 +3962,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>556902</v>
+        <v>556904</v>
       </c>
       <c r="R34" t="n">
-        <v>7227281</v>
+        <v>7227312</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4028,32 +4028,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126091122</v>
+        <v>126091097</v>
       </c>
       <c r="B35" t="n">
-        <v>91592</v>
+        <v>97223</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2063</v>
+        <v>221941</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4063,10 +4063,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>556726</v>
+        <v>557160</v>
       </c>
       <c r="R35" t="n">
-        <v>7227064</v>
+        <v>7227183</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4336,45 +4336,52 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126091108</v>
+        <v>126091060</v>
       </c>
       <c r="B38" t="n">
-        <v>80111</v>
+        <v>80076</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>556916</v>
+        <v>556945</v>
       </c>
       <c r="R38" t="n">
-        <v>7227278</v>
+        <v>7227306</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4415,6 +4422,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4437,7 +4445,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126091110</v>
+        <v>126091108</v>
       </c>
       <c r="B39" t="n">
         <v>80111</v>
@@ -4472,10 +4480,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>557049</v>
+        <v>556916</v>
       </c>
       <c r="R39" t="n">
-        <v>7227144</v>
+        <v>7227278</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4502,12 +4510,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4538,52 +4546,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126091060</v>
+        <v>126091110</v>
       </c>
       <c r="B40" t="n">
-        <v>80076</v>
+        <v>80111</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>556945</v>
+        <v>557049</v>
       </c>
       <c r="R40" t="n">
-        <v>7227306</v>
+        <v>7227144</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4610,12 +4611,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4624,7 +4625,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4647,10 +4647,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126091101</v>
+        <v>126091011</v>
       </c>
       <c r="B41" t="n">
-        <v>80075</v>
+        <v>79004</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4658,21 +4658,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4682,10 +4682,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>556918</v>
+        <v>557066</v>
       </c>
       <c r="R41" t="n">
-        <v>7227271</v>
+        <v>7227351</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4849,10 +4849,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126091011</v>
+        <v>126091061</v>
       </c>
       <c r="B43" t="n">
-        <v>79004</v>
+        <v>80076</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4860,34 +4860,41 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>185</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>557066</v>
+        <v>557049</v>
       </c>
       <c r="R43" t="n">
-        <v>7227351</v>
+        <v>7227144</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4914,12 +4921,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4928,6 +4935,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5051,10 +5059,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126091061</v>
+        <v>126091101</v>
       </c>
       <c r="B45" t="n">
-        <v>80076</v>
+        <v>80075</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5062,41 +5070,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>557049</v>
+        <v>556918</v>
       </c>
       <c r="R45" t="n">
-        <v>7227144</v>
+        <v>7227271</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5123,12 +5124,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5137,7 +5138,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5463,27 +5463,27 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126091113</v>
+        <v>126091038</v>
       </c>
       <c r="B49" t="n">
-        <v>57755</v>
+        <v>57651</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5498,10 +5498,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>556728</v>
+        <v>557057</v>
       </c>
       <c r="R49" t="n">
-        <v>7227079</v>
+        <v>7227134</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5534,6 +5534,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack färsk</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5564,27 +5569,27 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126091038</v>
+        <v>126091113</v>
       </c>
       <c r="B50" t="n">
-        <v>57651</v>
+        <v>57755</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5599,10 +5604,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>557057</v>
+        <v>556728</v>
       </c>
       <c r="R50" t="n">
-        <v>7227134</v>
+        <v>7227079</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5635,11 +5640,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack färsk</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5779,10 +5779,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126091353</v>
+        <v>126091171</v>
       </c>
       <c r="B52" t="n">
-        <v>98360</v>
+        <v>80110</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5790,21 +5790,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5814,10 +5814,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>556926</v>
+        <v>557049</v>
       </c>
       <c r="R52" t="n">
-        <v>7227176</v>
+        <v>7227144</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5986,10 +5986,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126091171</v>
+        <v>126091353</v>
       </c>
       <c r="B54" t="n">
-        <v>80110</v>
+        <v>98360</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5997,21 +5997,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6463</v>
+        <v>221952</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6021,10 +6021,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>557049</v>
+        <v>556926</v>
       </c>
       <c r="R54" t="n">
-        <v>7227144</v>
+        <v>7227176</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6051,12 +6051,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6496,32 +6496,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126091091</v>
+        <v>126091082</v>
       </c>
       <c r="B59" t="n">
-        <v>79979</v>
+        <v>80076</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6531,10 +6531,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>557022</v>
+        <v>556947</v>
       </c>
       <c r="R59" t="n">
-        <v>7227286</v>
+        <v>7227303</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6597,32 +6597,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126091082</v>
+        <v>126091091</v>
       </c>
       <c r="B60" t="n">
-        <v>80076</v>
+        <v>79979</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6632,10 +6632,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>556947</v>
+        <v>557022</v>
       </c>
       <c r="R60" t="n">
-        <v>7227303</v>
+        <v>7227286</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6698,10 +6698,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126091054</v>
+        <v>126091446</v>
       </c>
       <c r="B61" t="n">
-        <v>98360</v>
+        <v>80110</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6709,21 +6709,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>556704</v>
+        <v>556925</v>
       </c>
       <c r="R61" t="n">
-        <v>7227103</v>
+        <v>7227179</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6799,10 +6799,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126091446</v>
+        <v>126091054</v>
       </c>
       <c r="B62" t="n">
-        <v>80110</v>
+        <v>98360</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6810,21 +6810,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6463</v>
+        <v>221952</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6834,10 +6834,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>556925</v>
+        <v>556704</v>
       </c>
       <c r="R62" t="n">
-        <v>7227179</v>
+        <v>7227103</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6864,12 +6864,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7203,10 +7203,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126091081</v>
+        <v>126091155</v>
       </c>
       <c r="B66" t="n">
-        <v>80076</v>
+        <v>78972</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7214,21 +7214,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7238,10 +7238,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>556946</v>
+        <v>557073</v>
       </c>
       <c r="R66" t="n">
-        <v>7227279</v>
+        <v>7227326</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7304,10 +7304,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126091155</v>
+        <v>126091081</v>
       </c>
       <c r="B67" t="n">
-        <v>78972</v>
+        <v>80076</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7315,21 +7315,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7339,10 +7339,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>557073</v>
+        <v>556946</v>
       </c>
       <c r="R67" t="n">
-        <v>7227326</v>
+        <v>7227279</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7506,32 +7506,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126091046</v>
+        <v>126091086</v>
       </c>
       <c r="B69" t="n">
-        <v>80104</v>
+        <v>80076</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7541,10 +7541,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>556915</v>
+        <v>556691</v>
       </c>
       <c r="R69" t="n">
-        <v>7227293</v>
+        <v>7227079</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7571,12 +7571,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7607,10 +7607,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126091103</v>
+        <v>126091154</v>
       </c>
       <c r="B70" t="n">
-        <v>80075</v>
+        <v>78972</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7618,21 +7618,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7642,10 +7642,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>556737</v>
+        <v>556904</v>
       </c>
       <c r="R70" t="n">
-        <v>7227086</v>
+        <v>7227312</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7672,12 +7672,17 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7708,32 +7713,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126091154</v>
+        <v>126091046</v>
       </c>
       <c r="B71" t="n">
-        <v>78972</v>
+        <v>80104</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7743,10 +7748,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>556904</v>
+        <v>556915</v>
       </c>
       <c r="R71" t="n">
-        <v>7227312</v>
+        <v>7227293</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7779,11 +7784,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7814,10 +7814,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126091086</v>
+        <v>126091103</v>
       </c>
       <c r="B72" t="n">
-        <v>80076</v>
+        <v>80075</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7825,21 +7825,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7849,10 +7849,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>556691</v>
+        <v>556737</v>
       </c>
       <c r="R72" t="n">
-        <v>7227079</v>
+        <v>7227086</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>

--- a/artfynd/A 23758-2025 artfynd.xlsx
+++ b/artfynd/A 23758-2025 artfynd.xlsx
@@ -1291,32 +1291,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126091170</v>
+        <v>126091117</v>
       </c>
       <c r="B8" t="n">
-        <v>80110</v>
+        <v>57807</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6463</v>
+        <v>103022</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1326,10 +1326,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556915</v>
+        <v>556827</v>
       </c>
       <c r="R8" t="n">
-        <v>7227293</v>
+        <v>7227124</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1392,32 +1392,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126091117</v>
+        <v>126091170</v>
       </c>
       <c r="B9" t="n">
-        <v>57807</v>
+        <v>80110</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103022</v>
+        <v>6463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556827</v>
+        <v>556915</v>
       </c>
       <c r="R9" t="n">
-        <v>7227124</v>
+        <v>7227293</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1897,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126091118</v>
+        <v>126091083</v>
       </c>
       <c r="B14" t="n">
-        <v>57807</v>
+        <v>80076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,21 +1908,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103022</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>556859</v>
+        <v>556975</v>
       </c>
       <c r="R14" t="n">
-        <v>7227119</v>
+        <v>7227303</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1962,12 +1962,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1998,32 +1998,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126091112</v>
+        <v>126091159</v>
       </c>
       <c r="B15" t="n">
-        <v>57755</v>
+        <v>78972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2033,10 +2033,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>556726</v>
+        <v>557055</v>
       </c>
       <c r="R15" t="n">
-        <v>7227088</v>
+        <v>7227102</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2099,32 +2099,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126091083</v>
+        <v>126091112</v>
       </c>
       <c r="B16" t="n">
-        <v>80076</v>
+        <v>57755</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>103031</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2134,10 +2134,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>556975</v>
+        <v>556726</v>
       </c>
       <c r="R16" t="n">
-        <v>7227303</v>
+        <v>7227088</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2164,12 +2164,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2200,10 +2200,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126091159</v>
+        <v>126091118</v>
       </c>
       <c r="B17" t="n">
-        <v>78972</v>
+        <v>57807</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2211,21 +2211,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>103022</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>557055</v>
+        <v>556859</v>
       </c>
       <c r="R17" t="n">
-        <v>7227102</v>
+        <v>7227119</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -3220,10 +3220,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126091158</v>
+        <v>126091021</v>
       </c>
       <c r="B27" t="n">
-        <v>78972</v>
+        <v>91232</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3231,21 +3231,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3255,10 +3255,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>556943</v>
+        <v>557035</v>
       </c>
       <c r="R27" t="n">
-        <v>7227059</v>
+        <v>7227275</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3285,12 +3285,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3321,32 +3321,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126091094</v>
+        <v>126091158</v>
       </c>
       <c r="B28" t="n">
-        <v>79979</v>
+        <v>78972</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>556900</v>
+        <v>556943</v>
       </c>
       <c r="R28" t="n">
-        <v>7227075</v>
+        <v>7227059</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3422,32 +3422,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126091021</v>
+        <v>126091094</v>
       </c>
       <c r="B29" t="n">
-        <v>91232</v>
+        <v>79979</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3457,10 +3457,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>557035</v>
+        <v>556900</v>
       </c>
       <c r="R29" t="n">
-        <v>7227275</v>
+        <v>7227075</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3487,12 +3487,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -5670,52 +5670,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126091059</v>
+        <v>126091171</v>
       </c>
       <c r="B51" t="n">
-        <v>80076</v>
+        <v>80110</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>556914</v>
+        <v>557049</v>
       </c>
       <c r="R51" t="n">
-        <v>7227278</v>
+        <v>7227144</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5742,12 +5735,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5756,7 +5749,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5779,10 +5771,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126091171</v>
+        <v>126091353</v>
       </c>
       <c r="B52" t="n">
-        <v>80110</v>
+        <v>98360</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5790,21 +5782,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6463</v>
+        <v>221952</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5814,10 +5806,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>557049</v>
+        <v>556926</v>
       </c>
       <c r="R52" t="n">
-        <v>7227144</v>
+        <v>7227176</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5844,12 +5836,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5880,10 +5872,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126091037</v>
+        <v>126091059</v>
       </c>
       <c r="B53" t="n">
-        <v>57651</v>
+        <v>80076</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5891,34 +5883,41 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>556702</v>
+        <v>556914</v>
       </c>
       <c r="R53" t="n">
-        <v>7227082</v>
+        <v>7227278</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5945,17 +5944,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5964,6 +5958,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5986,32 +5981,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126091353</v>
+        <v>126091037</v>
       </c>
       <c r="B54" t="n">
-        <v>98360</v>
+        <v>57651</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6021,10 +6016,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>556926</v>
+        <v>556702</v>
       </c>
       <c r="R54" t="n">
-        <v>7227176</v>
+        <v>7227082</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6051,12 +6046,17 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6087,32 +6087,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126091026</v>
+        <v>126091161</v>
       </c>
       <c r="B55" t="n">
-        <v>91929</v>
+        <v>78972</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6122,10 +6122,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>556711</v>
+        <v>557149</v>
       </c>
       <c r="R55" t="n">
-        <v>7227080</v>
+        <v>7227169</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6158,6 +6158,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6188,10 +6193,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126091161</v>
+        <v>126091134</v>
       </c>
       <c r="B56" t="n">
-        <v>78972</v>
+        <v>91250</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6199,21 +6204,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6223,10 +6228,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>557149</v>
+        <v>556726</v>
       </c>
       <c r="R56" t="n">
-        <v>7227169</v>
+        <v>7227062</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6259,11 +6264,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Fertil</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6294,7 +6294,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126091134</v>
+        <v>126091139</v>
       </c>
       <c r="B57" t="n">
         <v>91250</v>
@@ -6329,10 +6329,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>556726</v>
+        <v>557138</v>
       </c>
       <c r="R57" t="n">
-        <v>7227062</v>
+        <v>7227186</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6395,32 +6395,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126091139</v>
+        <v>126091026</v>
       </c>
       <c r="B58" t="n">
-        <v>91250</v>
+        <v>91929</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6430,10 +6430,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>557138</v>
+        <v>556711</v>
       </c>
       <c r="R58" t="n">
-        <v>7227186</v>
+        <v>7227080</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>

--- a/artfynd/A 23758-2025 artfynd.xlsx
+++ b/artfynd/A 23758-2025 artfynd.xlsx
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126091099</v>
+        <v>126091092</v>
       </c>
       <c r="B3" t="n">
-        <v>98243</v>
+        <v>79979</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220093</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>557073</v>
+        <v>556906</v>
       </c>
       <c r="R3" t="n">
-        <v>7227326</v>
+        <v>7227086</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -841,12 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -855,7 +855,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -878,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126091092</v>
+        <v>126091009</v>
       </c>
       <c r="B4" t="n">
-        <v>79979</v>
+        <v>80111</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,34 +888,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>6464</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556906</v>
+        <v>556917</v>
       </c>
       <c r="R4" t="n">
-        <v>7227086</v>
+        <v>7227275</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -943,12 +945,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -957,6 +959,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -979,48 +982,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126091009</v>
+        <v>126091030</v>
       </c>
       <c r="B5" t="n">
-        <v>80111</v>
+        <v>57651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556917</v>
+        <v>557050</v>
       </c>
       <c r="R5" t="n">
-        <v>7227275</v>
+        <v>7227253</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1055,13 +1055,17 @@
           <t>2025-06-18</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1084,32 +1088,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126091030</v>
+        <v>126091099</v>
       </c>
       <c r="B6" t="n">
-        <v>57651</v>
+        <v>98243</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1119,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>557050</v>
+        <v>557073</v>
       </c>
       <c r="R6" t="n">
-        <v>7227253</v>
+        <v>7227326</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1157,17 +1161,13 @@
           <t>2025-06-18</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -3220,10 +3220,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126091021</v>
+        <v>126091158</v>
       </c>
       <c r="B27" t="n">
-        <v>91232</v>
+        <v>78972</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3231,21 +3231,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3255,10 +3255,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>557035</v>
+        <v>556943</v>
       </c>
       <c r="R27" t="n">
-        <v>7227275</v>
+        <v>7227059</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3285,12 +3285,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3321,32 +3321,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126091158</v>
+        <v>126091094</v>
       </c>
       <c r="B28" t="n">
-        <v>78972</v>
+        <v>79979</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>556943</v>
+        <v>556900</v>
       </c>
       <c r="R28" t="n">
-        <v>7227059</v>
+        <v>7227075</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3422,32 +3422,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126091094</v>
+        <v>126091021</v>
       </c>
       <c r="B29" t="n">
-        <v>79979</v>
+        <v>91232</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3457,10 +3457,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>556900</v>
+        <v>557035</v>
       </c>
       <c r="R29" t="n">
-        <v>7227075</v>
+        <v>7227275</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3487,12 +3487,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3523,10 +3523,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126091078</v>
+        <v>126091133</v>
       </c>
       <c r="B30" t="n">
-        <v>80076</v>
+        <v>91250</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3534,21 +3534,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3558,10 +3558,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>556918</v>
+        <v>556729</v>
       </c>
       <c r="R30" t="n">
-        <v>7227271</v>
+        <v>7227082</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3588,12 +3588,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3624,32 +3624,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126091122</v>
+        <v>126091045</v>
       </c>
       <c r="B31" t="n">
-        <v>91592</v>
+        <v>80104</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2063</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3659,10 +3659,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>556726</v>
+        <v>556904</v>
       </c>
       <c r="R31" t="n">
-        <v>7227064</v>
+        <v>7227312</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3689,12 +3689,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3725,7 +3725,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126091077</v>
+        <v>126091078</v>
       </c>
       <c r="B32" t="n">
         <v>80076</v>
@@ -3760,10 +3760,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>556902</v>
+        <v>556918</v>
       </c>
       <c r="R32" t="n">
-        <v>7227281</v>
+        <v>7227271</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3826,32 +3826,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126091133</v>
+        <v>126091122</v>
       </c>
       <c r="B33" t="n">
-        <v>91250</v>
+        <v>91592</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>2063</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>556729</v>
+        <v>556726</v>
       </c>
       <c r="R33" t="n">
-        <v>7227082</v>
+        <v>7227064</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3927,32 +3927,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126091045</v>
+        <v>126091077</v>
       </c>
       <c r="B34" t="n">
-        <v>80104</v>
+        <v>80076</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3962,10 +3962,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>556904</v>
+        <v>556902</v>
       </c>
       <c r="R34" t="n">
-        <v>7227312</v>
+        <v>7227281</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4647,10 +4647,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126091011</v>
+        <v>126091137</v>
       </c>
       <c r="B41" t="n">
-        <v>79004</v>
+        <v>91250</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4658,21 +4658,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>185</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4682,10 +4682,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>557066</v>
+        <v>557054</v>
       </c>
       <c r="R41" t="n">
-        <v>7227351</v>
+        <v>7227134</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4748,10 +4748,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126091025</v>
+        <v>126091101</v>
       </c>
       <c r="B42" t="n">
-        <v>91232</v>
+        <v>80075</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4759,21 +4759,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>556986</v>
+        <v>556918</v>
       </c>
       <c r="R42" t="n">
-        <v>7227133</v>
+        <v>7227271</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4813,12 +4813,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4849,52 +4849,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126091061</v>
+        <v>126091050</v>
       </c>
       <c r="B43" t="n">
-        <v>80076</v>
+        <v>80104</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>557049</v>
+        <v>556992</v>
       </c>
       <c r="R43" t="n">
-        <v>7227144</v>
+        <v>7227120</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4935,7 +4928,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4958,32 +4950,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126091137</v>
+        <v>126091111</v>
       </c>
       <c r="B44" t="n">
-        <v>91250</v>
+        <v>80111</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4993,10 +4985,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>557054</v>
+        <v>557064</v>
       </c>
       <c r="R44" t="n">
-        <v>7227134</v>
+        <v>7227147</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5059,10 +5051,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126091101</v>
+        <v>126091011</v>
       </c>
       <c r="B45" t="n">
-        <v>80075</v>
+        <v>79004</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5070,21 +5062,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5094,10 +5086,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>556918</v>
+        <v>557066</v>
       </c>
       <c r="R45" t="n">
-        <v>7227271</v>
+        <v>7227351</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5160,32 +5152,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126091050</v>
+        <v>126091025</v>
       </c>
       <c r="B46" t="n">
-        <v>80104</v>
+        <v>91232</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5195,10 +5187,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>556992</v>
+        <v>556986</v>
       </c>
       <c r="R46" t="n">
-        <v>7227120</v>
+        <v>7227133</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5261,45 +5253,52 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126091111</v>
+        <v>126091061</v>
       </c>
       <c r="B47" t="n">
-        <v>80111</v>
+        <v>80076</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>557064</v>
+        <v>557049</v>
       </c>
       <c r="R47" t="n">
-        <v>7227147</v>
+        <v>7227144</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5340,6 +5339,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5670,10 +5670,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126091171</v>
+        <v>126091353</v>
       </c>
       <c r="B51" t="n">
-        <v>80110</v>
+        <v>98360</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5681,21 +5681,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6463</v>
+        <v>221952</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5705,10 +5705,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>557049</v>
+        <v>556926</v>
       </c>
       <c r="R51" t="n">
-        <v>7227144</v>
+        <v>7227176</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5735,12 +5735,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5771,45 +5771,52 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126091353</v>
+        <v>126091059</v>
       </c>
       <c r="B52" t="n">
-        <v>98360</v>
+        <v>80076</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>556926</v>
+        <v>556914</v>
       </c>
       <c r="R52" t="n">
-        <v>7227176</v>
+        <v>7227278</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5836,12 +5843,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5850,6 +5857,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5872,52 +5880,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126091059</v>
+        <v>126091171</v>
       </c>
       <c r="B53" t="n">
-        <v>80076</v>
+        <v>80110</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>556914</v>
+        <v>557049</v>
       </c>
       <c r="R53" t="n">
-        <v>7227278</v>
+        <v>7227144</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5944,12 +5945,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5958,7 +5959,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6087,32 +6087,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126091161</v>
+        <v>126091026</v>
       </c>
       <c r="B55" t="n">
-        <v>78972</v>
+        <v>91929</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6122,10 +6122,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>557149</v>
+        <v>556711</v>
       </c>
       <c r="R55" t="n">
-        <v>7227169</v>
+        <v>7227080</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6158,11 +6158,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Fertil</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6193,10 +6188,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126091134</v>
+        <v>126091161</v>
       </c>
       <c r="B56" t="n">
-        <v>91250</v>
+        <v>78972</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6204,21 +6199,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6228,10 +6223,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>556726</v>
+        <v>557149</v>
       </c>
       <c r="R56" t="n">
-        <v>7227062</v>
+        <v>7227169</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6264,6 +6259,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6294,7 +6294,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126091139</v>
+        <v>126091134</v>
       </c>
       <c r="B57" t="n">
         <v>91250</v>
@@ -6329,10 +6329,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>557138</v>
+        <v>556726</v>
       </c>
       <c r="R57" t="n">
-        <v>7227186</v>
+        <v>7227062</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6395,32 +6395,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126091026</v>
+        <v>126091139</v>
       </c>
       <c r="B58" t="n">
-        <v>91929</v>
+        <v>91250</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6430,10 +6430,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>556711</v>
+        <v>557138</v>
       </c>
       <c r="R58" t="n">
-        <v>7227080</v>
+        <v>7227186</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7506,10 +7506,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126091086</v>
+        <v>126091154</v>
       </c>
       <c r="B69" t="n">
-        <v>80076</v>
+        <v>78972</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7517,21 +7517,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7541,10 +7541,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>556691</v>
+        <v>556904</v>
       </c>
       <c r="R69" t="n">
-        <v>7227079</v>
+        <v>7227312</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7571,12 +7571,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7607,10 +7612,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126091154</v>
+        <v>126091086</v>
       </c>
       <c r="B70" t="n">
-        <v>78972</v>
+        <v>80076</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7618,21 +7623,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7642,10 +7647,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>556904</v>
+        <v>556691</v>
       </c>
       <c r="R70" t="n">
-        <v>7227312</v>
+        <v>7227079</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7672,17 +7677,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 23758-2025 artfynd.xlsx
+++ b/artfynd/A 23758-2025 artfynd.xlsx
@@ -675,45 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126091089</v>
+        <v>126091009</v>
       </c>
       <c r="B2" t="n">
-        <v>80076</v>
+        <v>80112</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>557054</v>
+        <v>556917</v>
       </c>
       <c r="R2" t="n">
-        <v>7227146</v>
+        <v>7227275</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -754,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -776,32 +780,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126091092</v>
+        <v>126091089</v>
       </c>
       <c r="B3" t="n">
-        <v>79979</v>
+        <v>80077</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556906</v>
+        <v>557054</v>
       </c>
       <c r="R3" t="n">
-        <v>7227086</v>
+        <v>7227146</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +881,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126091009</v>
+        <v>126091099</v>
       </c>
       <c r="B4" t="n">
-        <v>80111</v>
+        <v>98245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,37 +892,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6464</v>
+        <v>220093</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556917</v>
+        <v>557073</v>
       </c>
       <c r="R4" t="n">
-        <v>7227275</v>
+        <v>7227326</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,7 +986,7 @@
         <v>126091030</v>
       </c>
       <c r="B5" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126091099</v>
+        <v>126091092</v>
       </c>
       <c r="B6" t="n">
-        <v>98243</v>
+        <v>79980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1100,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220093</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>557073</v>
+        <v>556906</v>
       </c>
       <c r="R6" t="n">
-        <v>7227326</v>
+        <v>7227086</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1153,12 +1154,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1167,7 +1168,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1193,7 +1193,7 @@
         <v>126091087</v>
       </c>
       <c r="B7" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,32 +1291,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126091117</v>
+        <v>126091170</v>
       </c>
       <c r="B8" t="n">
-        <v>57807</v>
+        <v>80111</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103022</v>
+        <v>6463</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1326,10 +1326,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556827</v>
+        <v>556915</v>
       </c>
       <c r="R8" t="n">
-        <v>7227124</v>
+        <v>7227293</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1392,32 +1392,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126091170</v>
+        <v>126091117</v>
       </c>
       <c r="B9" t="n">
-        <v>80110</v>
+        <v>57808</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>103022</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556915</v>
+        <v>556827</v>
       </c>
       <c r="R9" t="n">
-        <v>7227293</v>
+        <v>7227124</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1493,10 +1493,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126091080</v>
+        <v>126091138</v>
       </c>
       <c r="B10" t="n">
-        <v>80076</v>
+        <v>91252</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1504,21 +1504,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1528,10 +1528,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>556915</v>
+        <v>557073</v>
       </c>
       <c r="R10" t="n">
-        <v>7227290</v>
+        <v>7227154</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1558,12 +1558,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1594,10 +1594,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126091138</v>
+        <v>126091080</v>
       </c>
       <c r="B11" t="n">
-        <v>91250</v>
+        <v>80077</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1605,21 +1605,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557073</v>
+        <v>556915</v>
       </c>
       <c r="R11" t="n">
-        <v>7227154</v>
+        <v>7227290</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1659,12 +1659,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1698,7 +1698,7 @@
         <v>126091058</v>
       </c>
       <c r="B12" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>126091055</v>
       </c>
       <c r="B13" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,32 +1897,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126091083</v>
+        <v>126091112</v>
       </c>
       <c r="B14" t="n">
-        <v>80076</v>
+        <v>57756</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>103031</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>556975</v>
+        <v>556726</v>
       </c>
       <c r="R14" t="n">
-        <v>7227303</v>
+        <v>7227088</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1962,12 +1962,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2001,7 +2001,7 @@
         <v>126091159</v>
       </c>
       <c r="B15" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2099,32 +2099,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126091112</v>
+        <v>126091083</v>
       </c>
       <c r="B16" t="n">
-        <v>57755</v>
+        <v>80077</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103031</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2134,10 +2134,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>556726</v>
+        <v>556975</v>
       </c>
       <c r="R16" t="n">
-        <v>7227088</v>
+        <v>7227303</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2164,12 +2164,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2203,7 +2203,7 @@
         <v>126091118</v>
       </c>
       <c r="B17" t="n">
-        <v>57807</v>
+        <v>57808</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>126091079</v>
       </c>
       <c r="B18" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>126091022</v>
       </c>
       <c r="B19" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>126091088</v>
       </c>
       <c r="B20" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>126091156</v>
       </c>
       <c r="B21" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>126091157</v>
       </c>
       <c r="B22" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>126091047</v>
       </c>
       <c r="B23" t="n">
-        <v>80104</v>
+        <v>80105</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>126091109</v>
       </c>
       <c r="B24" t="n">
-        <v>80111</v>
+        <v>80112</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>126091048</v>
       </c>
       <c r="B25" t="n">
-        <v>80104</v>
+        <v>80105</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>126091096</v>
       </c>
       <c r="B26" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3220,10 +3220,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126091158</v>
+        <v>126091021</v>
       </c>
       <c r="B27" t="n">
-        <v>78972</v>
+        <v>91234</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3231,21 +3231,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3255,10 +3255,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>556943</v>
+        <v>557035</v>
       </c>
       <c r="R27" t="n">
-        <v>7227059</v>
+        <v>7227275</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3285,12 +3285,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3324,7 +3324,7 @@
         <v>126091094</v>
       </c>
       <c r="B28" t="n">
-        <v>79979</v>
+        <v>79980</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3422,10 +3422,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126091021</v>
+        <v>126091158</v>
       </c>
       <c r="B29" t="n">
-        <v>91232</v>
+        <v>78973</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3433,21 +3433,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3457,10 +3457,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>557035</v>
+        <v>556943</v>
       </c>
       <c r="R29" t="n">
-        <v>7227275</v>
+        <v>7227059</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3487,12 +3487,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3523,10 +3523,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126091133</v>
+        <v>126091078</v>
       </c>
       <c r="B30" t="n">
-        <v>91250</v>
+        <v>80077</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3534,21 +3534,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3558,10 +3558,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>556729</v>
+        <v>556918</v>
       </c>
       <c r="R30" t="n">
-        <v>7227082</v>
+        <v>7227271</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3588,12 +3588,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3624,32 +3624,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126091045</v>
+        <v>126091133</v>
       </c>
       <c r="B31" t="n">
-        <v>80104</v>
+        <v>91252</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3659,10 +3659,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>556904</v>
+        <v>556729</v>
       </c>
       <c r="R31" t="n">
-        <v>7227312</v>
+        <v>7227082</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3689,12 +3689,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3725,32 +3725,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126091078</v>
+        <v>126091045</v>
       </c>
       <c r="B32" t="n">
-        <v>80076</v>
+        <v>80105</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3760,10 +3760,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>556918</v>
+        <v>556904</v>
       </c>
       <c r="R32" t="n">
-        <v>7227271</v>
+        <v>7227312</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3829,7 +3829,7 @@
         <v>126091122</v>
       </c>
       <c r="B33" t="n">
-        <v>91592</v>
+        <v>91594</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>126091077</v>
       </c>
       <c r="B34" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>126091097</v>
       </c>
       <c r="B35" t="n">
-        <v>97223</v>
+        <v>97225</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>126091032</v>
       </c>
       <c r="B36" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>126091131</v>
       </c>
       <c r="B37" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4336,52 +4336,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126091060</v>
+        <v>126091108</v>
       </c>
       <c r="B38" t="n">
-        <v>80076</v>
+        <v>80112</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>556945</v>
+        <v>556916</v>
       </c>
       <c r="R38" t="n">
-        <v>7227306</v>
+        <v>7227278</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4422,7 +4415,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4445,10 +4437,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126091108</v>
+        <v>126091110</v>
       </c>
       <c r="B39" t="n">
-        <v>80111</v>
+        <v>80112</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4480,10 +4472,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>556916</v>
+        <v>557049</v>
       </c>
       <c r="R39" t="n">
-        <v>7227278</v>
+        <v>7227144</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4510,12 +4502,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4546,45 +4538,52 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126091110</v>
+        <v>126091060</v>
       </c>
       <c r="B40" t="n">
-        <v>80111</v>
+        <v>80077</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>557049</v>
+        <v>556945</v>
       </c>
       <c r="R40" t="n">
-        <v>7227144</v>
+        <v>7227306</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4611,12 +4610,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4625,6 +4624,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4647,10 +4647,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126091137</v>
+        <v>126091101</v>
       </c>
       <c r="B41" t="n">
-        <v>91250</v>
+        <v>80076</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4658,21 +4658,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4682,10 +4682,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>557054</v>
+        <v>556918</v>
       </c>
       <c r="R41" t="n">
-        <v>7227134</v>
+        <v>7227271</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4748,10 +4748,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126091101</v>
+        <v>126091137</v>
       </c>
       <c r="B42" t="n">
-        <v>80075</v>
+        <v>91252</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4759,21 +4759,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>556918</v>
+        <v>557054</v>
       </c>
       <c r="R42" t="n">
-        <v>7227271</v>
+        <v>7227134</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4813,12 +4813,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4852,7 +4852,7 @@
         <v>126091050</v>
       </c>
       <c r="B43" t="n">
-        <v>80104</v>
+        <v>80105</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>126091111</v>
       </c>
       <c r="B44" t="n">
-        <v>80111</v>
+        <v>80112</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5051,10 +5051,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126091011</v>
+        <v>126091025</v>
       </c>
       <c r="B45" t="n">
-        <v>79004</v>
+        <v>91234</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5062,21 +5062,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5086,10 +5086,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>557066</v>
+        <v>556986</v>
       </c>
       <c r="R45" t="n">
-        <v>7227351</v>
+        <v>7227133</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5116,12 +5116,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5152,10 +5152,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126091025</v>
+        <v>126091011</v>
       </c>
       <c r="B46" t="n">
-        <v>91232</v>
+        <v>79005</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5163,21 +5163,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5187,10 +5187,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>556986</v>
+        <v>557066</v>
       </c>
       <c r="R46" t="n">
-        <v>7227133</v>
+        <v>7227351</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5217,12 +5217,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5256,7 +5256,7 @@
         <v>126091061</v>
       </c>
       <c r="B47" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>126091142</v>
       </c>
       <c r="B48" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>126091038</v>
       </c>
       <c r="B49" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>126091113</v>
       </c>
       <c r="B50" t="n">
-        <v>57755</v>
+        <v>57756</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5670,10 +5670,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126091353</v>
+        <v>126091171</v>
       </c>
       <c r="B51" t="n">
-        <v>98360</v>
+        <v>80111</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5681,21 +5681,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5705,10 +5705,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>556926</v>
+        <v>557049</v>
       </c>
       <c r="R51" t="n">
-        <v>7227176</v>
+        <v>7227144</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5735,12 +5735,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5774,7 +5774,7 @@
         <v>126091059</v>
       </c>
       <c r="B52" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5880,32 +5880,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126091171</v>
+        <v>126091037</v>
       </c>
       <c r="B53" t="n">
-        <v>80110</v>
+        <v>57652</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5915,10 +5915,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>557049</v>
+        <v>556702</v>
       </c>
       <c r="R53" t="n">
-        <v>7227144</v>
+        <v>7227082</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5951,6 +5951,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5981,32 +5986,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126091037</v>
+        <v>126091353</v>
       </c>
       <c r="B54" t="n">
-        <v>57651</v>
+        <v>98362</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6016,10 +6021,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>556702</v>
+        <v>556926</v>
       </c>
       <c r="R54" t="n">
-        <v>7227082</v>
+        <v>7227176</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6046,17 +6051,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6090,7 +6090,7 @@
         <v>126091026</v>
       </c>
       <c r="B55" t="n">
-        <v>91929</v>
+        <v>91931</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>126091161</v>
       </c>
       <c r="B56" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6297,7 +6297,7 @@
         <v>126091134</v>
       </c>
       <c r="B57" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>126091139</v>
       </c>
       <c r="B58" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6496,32 +6496,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126091082</v>
+        <v>126091091</v>
       </c>
       <c r="B59" t="n">
-        <v>80076</v>
+        <v>79980</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6531,10 +6531,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>556947</v>
+        <v>557022</v>
       </c>
       <c r="R59" t="n">
-        <v>7227303</v>
+        <v>7227286</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6597,10 +6597,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126091091</v>
+        <v>126091446</v>
       </c>
       <c r="B60" t="n">
-        <v>79979</v>
+        <v>80111</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6608,21 +6608,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6456</v>
+        <v>6463</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6632,10 +6632,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>557022</v>
+        <v>556925</v>
       </c>
       <c r="R60" t="n">
-        <v>7227286</v>
+        <v>7227179</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6662,12 +6662,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6698,10 +6698,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126091446</v>
+        <v>126091054</v>
       </c>
       <c r="B61" t="n">
-        <v>80110</v>
+        <v>98362</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6709,21 +6709,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6463</v>
+        <v>221952</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>556925</v>
+        <v>556704</v>
       </c>
       <c r="R61" t="n">
-        <v>7227179</v>
+        <v>7227103</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6799,10 +6799,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126091054</v>
+        <v>126091057</v>
       </c>
       <c r="B62" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6834,10 +6834,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>556704</v>
+        <v>557065</v>
       </c>
       <c r="R62" t="n">
-        <v>7227103</v>
+        <v>7227144</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6900,32 +6900,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126091057</v>
+        <v>126091082</v>
       </c>
       <c r="B63" t="n">
-        <v>98360</v>
+        <v>80077</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6935,10 +6935,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>557065</v>
+        <v>556947</v>
       </c>
       <c r="R63" t="n">
-        <v>7227144</v>
+        <v>7227303</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6965,12 +6965,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7004,7 +7004,7 @@
         <v>126091116</v>
       </c>
       <c r="B64" t="n">
-        <v>57807</v>
+        <v>57808</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7102,32 +7102,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126091136</v>
+        <v>126091056</v>
       </c>
       <c r="B65" t="n">
-        <v>91250</v>
+        <v>98362</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7137,10 +7137,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>556803</v>
+        <v>557140</v>
       </c>
       <c r="R65" t="n">
-        <v>7227106</v>
+        <v>7227297</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7203,10 +7203,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126091155</v>
+        <v>126091136</v>
       </c>
       <c r="B66" t="n">
-        <v>78972</v>
+        <v>91252</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7214,21 +7214,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7238,10 +7238,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>557073</v>
+        <v>556803</v>
       </c>
       <c r="R66" t="n">
-        <v>7227326</v>
+        <v>7227106</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7268,12 +7268,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7304,10 +7304,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126091081</v>
+        <v>126091155</v>
       </c>
       <c r="B67" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7315,21 +7315,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7339,10 +7339,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>556946</v>
+        <v>557073</v>
       </c>
       <c r="R67" t="n">
-        <v>7227279</v>
+        <v>7227326</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7405,32 +7405,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126091056</v>
+        <v>126091081</v>
       </c>
       <c r="B68" t="n">
-        <v>98360</v>
+        <v>80077</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>557140</v>
+        <v>556946</v>
       </c>
       <c r="R68" t="n">
-        <v>7227297</v>
+        <v>7227279</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7470,12 +7470,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7506,10 +7506,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126091154</v>
+        <v>126091103</v>
       </c>
       <c r="B69" t="n">
-        <v>78972</v>
+        <v>80076</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7517,21 +7517,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7541,10 +7541,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>556904</v>
+        <v>556737</v>
       </c>
       <c r="R69" t="n">
-        <v>7227312</v>
+        <v>7227086</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7571,17 +7571,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7612,10 +7607,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126091086</v>
+        <v>126091154</v>
       </c>
       <c r="B70" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7623,21 +7618,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7647,10 +7642,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>556691</v>
+        <v>556904</v>
       </c>
       <c r="R70" t="n">
-        <v>7227079</v>
+        <v>7227312</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7677,12 +7672,17 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7716,7 +7716,7 @@
         <v>126091046</v>
       </c>
       <c r="B71" t="n">
-        <v>80104</v>
+        <v>80105</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7814,10 +7814,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126091103</v>
+        <v>126091086</v>
       </c>
       <c r="B72" t="n">
-        <v>80075</v>
+        <v>80077</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7825,21 +7825,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7849,10 +7849,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>556737</v>
+        <v>556691</v>
       </c>
       <c r="R72" t="n">
-        <v>7227086</v>
+        <v>7227079</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>

--- a/artfynd/A 23758-2025 artfynd.xlsx
+++ b/artfynd/A 23758-2025 artfynd.xlsx
@@ -675,48 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126091009</v>
+        <v>126091030</v>
       </c>
       <c r="B2" t="n">
-        <v>80112</v>
+        <v>57652</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556917</v>
+        <v>557050</v>
       </c>
       <c r="R2" t="n">
-        <v>7227275</v>
+        <v>7227253</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,13 +748,17 @@
           <t>2025-06-18</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -780,45 +781,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126091089</v>
+        <v>126091009</v>
       </c>
       <c r="B3" t="n">
-        <v>80077</v>
+        <v>80112</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>557054</v>
+        <v>556917</v>
       </c>
       <c r="R3" t="n">
-        <v>7227146</v>
+        <v>7227275</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -845,12 +849,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -859,6 +863,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -881,32 +886,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126091099</v>
+        <v>126091089</v>
       </c>
       <c r="B4" t="n">
-        <v>98245</v>
+        <v>80077</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220093</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -916,10 +921,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>557073</v>
+        <v>557054</v>
       </c>
       <c r="R4" t="n">
-        <v>7227326</v>
+        <v>7227146</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -946,12 +951,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -960,7 +965,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -983,32 +987,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126091030</v>
+        <v>126091099</v>
       </c>
       <c r="B5" t="n">
-        <v>57652</v>
+        <v>98245</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1018,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>557050</v>
+        <v>557073</v>
       </c>
       <c r="R5" t="n">
-        <v>7227253</v>
+        <v>7227326</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,17 +1060,13 @@
           <t>2025-06-18</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1190,32 +1190,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126091087</v>
+        <v>126091170</v>
       </c>
       <c r="B7" t="n">
-        <v>80077</v>
+        <v>80111</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556869</v>
+        <v>556915</v>
       </c>
       <c r="R7" t="n">
-        <v>7227096</v>
+        <v>7227293</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1291,32 +1291,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126091170</v>
+        <v>126091087</v>
       </c>
       <c r="B8" t="n">
-        <v>80111</v>
+        <v>80077</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1326,10 +1326,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556915</v>
+        <v>556869</v>
       </c>
       <c r="R8" t="n">
-        <v>7227293</v>
+        <v>7227096</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1897,32 +1897,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126091112</v>
+        <v>126091159</v>
       </c>
       <c r="B14" t="n">
-        <v>57756</v>
+        <v>78973</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>556726</v>
+        <v>557055</v>
       </c>
       <c r="R14" t="n">
-        <v>7227088</v>
+        <v>7227102</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1998,10 +1998,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126091159</v>
+        <v>126091083</v>
       </c>
       <c r="B15" t="n">
-        <v>78973</v>
+        <v>80077</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2009,21 +2009,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2033,10 +2033,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>557055</v>
+        <v>556975</v>
       </c>
       <c r="R15" t="n">
-        <v>7227102</v>
+        <v>7227303</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2063,12 +2063,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2099,10 +2099,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126091083</v>
+        <v>126091118</v>
       </c>
       <c r="B16" t="n">
-        <v>80077</v>
+        <v>57808</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2110,21 +2110,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>103022</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2134,10 +2134,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>556975</v>
+        <v>556859</v>
       </c>
       <c r="R16" t="n">
-        <v>7227303</v>
+        <v>7227119</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2164,12 +2164,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2200,32 +2200,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126091118</v>
+        <v>126091112</v>
       </c>
       <c r="B17" t="n">
-        <v>57808</v>
+        <v>57756</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103022</v>
+        <v>103031</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>556859</v>
+        <v>556726</v>
       </c>
       <c r="R17" t="n">
-        <v>7227119</v>
+        <v>7227088</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -4129,10 +4129,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126091032</v>
+        <v>126091131</v>
       </c>
       <c r="B36" t="n">
-        <v>57652</v>
+        <v>91252</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4140,21 +4140,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4164,10 +4164,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>557048</v>
+        <v>556707</v>
       </c>
       <c r="R36" t="n">
-        <v>7227240</v>
+        <v>7227095</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4194,17 +4194,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4235,10 +4230,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126091131</v>
+        <v>126091032</v>
       </c>
       <c r="B37" t="n">
-        <v>91252</v>
+        <v>57652</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4246,21 +4241,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4270,10 +4265,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>556707</v>
+        <v>557048</v>
       </c>
       <c r="R37" t="n">
-        <v>7227095</v>
+        <v>7227240</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4300,12 +4295,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5670,45 +5670,52 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126091171</v>
+        <v>126091059</v>
       </c>
       <c r="B51" t="n">
-        <v>80111</v>
+        <v>80077</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>557049</v>
+        <v>556914</v>
       </c>
       <c r="R51" t="n">
-        <v>7227144</v>
+        <v>7227278</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5735,12 +5742,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5749,6 +5756,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5771,10 +5779,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126091059</v>
+        <v>126091037</v>
       </c>
       <c r="B52" t="n">
-        <v>80077</v>
+        <v>57652</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5782,41 +5790,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>556914</v>
+        <v>556702</v>
       </c>
       <c r="R52" t="n">
-        <v>7227278</v>
+        <v>7227082</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5843,12 +5844,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5857,7 +5863,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5880,32 +5885,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126091037</v>
+        <v>126091171</v>
       </c>
       <c r="B53" t="n">
-        <v>57652</v>
+        <v>80111</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5915,10 +5920,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>556702</v>
+        <v>557049</v>
       </c>
       <c r="R53" t="n">
-        <v>7227082</v>
+        <v>7227144</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5951,11 +5956,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 23758-2025 artfynd.xlsx
+++ b/artfynd/A 23758-2025 artfynd.xlsx
@@ -675,45 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126091030</v>
+        <v>126091009</v>
       </c>
       <c r="B2" t="n">
-        <v>57652</v>
+        <v>80112</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>557050</v>
+        <v>556917</v>
       </c>
       <c r="R2" t="n">
-        <v>7227253</v>
+        <v>7227275</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,17 +751,13 @@
           <t>2025-06-18</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126091009</v>
+        <v>126091092</v>
       </c>
       <c r="B3" t="n">
-        <v>80112</v>
+        <v>79980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,37 +791,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556917</v>
+        <v>556906</v>
       </c>
       <c r="R3" t="n">
-        <v>7227275</v>
+        <v>7227086</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -849,12 +845,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -863,7 +859,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -987,32 +982,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126091099</v>
+        <v>126091030</v>
       </c>
       <c r="B5" t="n">
-        <v>98245</v>
+        <v>57652</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220093</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1022,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>557073</v>
+        <v>557050</v>
       </c>
       <c r="R5" t="n">
-        <v>7227326</v>
+        <v>7227253</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1060,13 +1055,17 @@
           <t>2025-06-18</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1089,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126091092</v>
+        <v>126091099</v>
       </c>
       <c r="B6" t="n">
-        <v>79980</v>
+        <v>98247</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>220093</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1124,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556906</v>
+        <v>557073</v>
       </c>
       <c r="R6" t="n">
-        <v>7227086</v>
+        <v>7227326</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1154,12 +1153,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1168,6 +1167,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1493,10 +1493,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126091138</v>
+        <v>126091080</v>
       </c>
       <c r="B10" t="n">
-        <v>91252</v>
+        <v>80077</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1504,21 +1504,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1528,10 +1528,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557073</v>
+        <v>556915</v>
       </c>
       <c r="R10" t="n">
-        <v>7227154</v>
+        <v>7227290</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1558,12 +1558,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1594,10 +1594,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126091080</v>
+        <v>126091138</v>
       </c>
       <c r="B11" t="n">
-        <v>80077</v>
+        <v>91254</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1605,21 +1605,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>556915</v>
+        <v>557073</v>
       </c>
       <c r="R11" t="n">
-        <v>7227290</v>
+        <v>7227154</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1659,12 +1659,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1698,7 +1698,7 @@
         <v>126091058</v>
       </c>
       <c r="B12" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>126091055</v>
       </c>
       <c r="B13" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126091159</v>
+        <v>126091083</v>
       </c>
       <c r="B14" t="n">
-        <v>78973</v>
+        <v>80077</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,21 +1908,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557055</v>
+        <v>556975</v>
       </c>
       <c r="R14" t="n">
-        <v>7227102</v>
+        <v>7227303</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1962,12 +1962,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1998,10 +1998,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126091083</v>
+        <v>126091118</v>
       </c>
       <c r="B15" t="n">
-        <v>80077</v>
+        <v>57808</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2009,21 +2009,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>103022</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2033,10 +2033,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>556975</v>
+        <v>556859</v>
       </c>
       <c r="R15" t="n">
-        <v>7227303</v>
+        <v>7227119</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2063,12 +2063,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2099,32 +2099,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126091118</v>
+        <v>126091112</v>
       </c>
       <c r="B16" t="n">
-        <v>57808</v>
+        <v>57756</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103022</v>
+        <v>103031</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2134,10 +2134,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>556859</v>
+        <v>556726</v>
       </c>
       <c r="R16" t="n">
-        <v>7227119</v>
+        <v>7227088</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2200,32 +2200,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126091112</v>
+        <v>126091159</v>
       </c>
       <c r="B17" t="n">
-        <v>57756</v>
+        <v>78973</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>556726</v>
+        <v>557055</v>
       </c>
       <c r="R17" t="n">
-        <v>7227088</v>
+        <v>7227102</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2301,32 +2301,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126091079</v>
+        <v>126091047</v>
       </c>
       <c r="B18" t="n">
-        <v>80077</v>
+        <v>80105</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2336,10 +2336,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>556916</v>
+        <v>556947</v>
       </c>
       <c r="R18" t="n">
-        <v>7227278</v>
+        <v>7227277</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2402,10 +2402,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126091022</v>
+        <v>126091157</v>
       </c>
       <c r="B19" t="n">
-        <v>91234</v>
+        <v>78973</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2413,21 +2413,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2437,10 +2437,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>557054</v>
+        <v>556844</v>
       </c>
       <c r="R19" t="n">
-        <v>7227356</v>
+        <v>7227129</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2467,12 +2467,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2503,7 +2508,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126091088</v>
+        <v>126091079</v>
       </c>
       <c r="B20" t="n">
         <v>80077</v>
@@ -2538,10 +2543,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>557057</v>
+        <v>556916</v>
       </c>
       <c r="R20" t="n">
-        <v>7227107</v>
+        <v>7227278</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2568,12 +2573,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2604,10 +2609,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126091156</v>
+        <v>126091022</v>
       </c>
       <c r="B21" t="n">
-        <v>78973</v>
+        <v>91236</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2615,21 +2620,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2639,10 +2644,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>556815</v>
+        <v>557054</v>
       </c>
       <c r="R21" t="n">
-        <v>7227118</v>
+        <v>7227356</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2669,12 +2674,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2705,10 +2710,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126091157</v>
+        <v>126091088</v>
       </c>
       <c r="B22" t="n">
-        <v>78973</v>
+        <v>80077</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2716,21 +2721,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2740,10 +2745,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>556844</v>
+        <v>557057</v>
       </c>
       <c r="R22" t="n">
-        <v>7227129</v>
+        <v>7227107</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2776,11 +2781,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Fertil</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2811,32 +2811,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126091047</v>
+        <v>126091156</v>
       </c>
       <c r="B23" t="n">
-        <v>80105</v>
+        <v>78973</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2846,10 +2846,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>556947</v>
+        <v>556815</v>
       </c>
       <c r="R23" t="n">
-        <v>7227277</v>
+        <v>7227118</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2876,12 +2876,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3223,7 +3223,7 @@
         <v>126091021</v>
       </c>
       <c r="B27" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>126091133</v>
       </c>
       <c r="B31" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3725,32 +3725,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126091045</v>
+        <v>126091122</v>
       </c>
       <c r="B32" t="n">
-        <v>80105</v>
+        <v>91596</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>2063</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3760,10 +3760,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>556904</v>
+        <v>556726</v>
       </c>
       <c r="R32" t="n">
-        <v>7227312</v>
+        <v>7227064</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3790,12 +3790,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3826,32 +3826,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126091122</v>
+        <v>126091077</v>
       </c>
       <c r="B33" t="n">
-        <v>91594</v>
+        <v>80077</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2063</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>556726</v>
+        <v>556902</v>
       </c>
       <c r="R33" t="n">
-        <v>7227064</v>
+        <v>7227281</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3891,12 +3891,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3927,32 +3927,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126091077</v>
+        <v>126091045</v>
       </c>
       <c r="B34" t="n">
-        <v>80077</v>
+        <v>80105</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3962,10 +3962,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>556902</v>
+        <v>556904</v>
       </c>
       <c r="R34" t="n">
-        <v>7227281</v>
+        <v>7227312</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4031,7 +4031,7 @@
         <v>126091097</v>
       </c>
       <c r="B35" t="n">
-        <v>97225</v>
+        <v>97227</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4129,10 +4129,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126091131</v>
+        <v>126091032</v>
       </c>
       <c r="B36" t="n">
-        <v>91252</v>
+        <v>57652</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4140,21 +4140,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4164,10 +4164,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>556707</v>
+        <v>557048</v>
       </c>
       <c r="R36" t="n">
-        <v>7227095</v>
+        <v>7227240</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4194,12 +4194,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4230,10 +4235,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126091032</v>
+        <v>126091131</v>
       </c>
       <c r="B37" t="n">
-        <v>57652</v>
+        <v>91254</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4241,21 +4246,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4265,10 +4270,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>557048</v>
+        <v>556707</v>
       </c>
       <c r="R37" t="n">
-        <v>7227240</v>
+        <v>7227095</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4295,17 +4300,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4647,32 +4647,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126091101</v>
+        <v>126091111</v>
       </c>
       <c r="B41" t="n">
-        <v>80076</v>
+        <v>80112</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4682,10 +4682,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>556918</v>
+        <v>557064</v>
       </c>
       <c r="R41" t="n">
-        <v>7227271</v>
+        <v>7227147</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4748,32 +4748,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126091137</v>
+        <v>126091050</v>
       </c>
       <c r="B42" t="n">
-        <v>91252</v>
+        <v>80105</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>557054</v>
+        <v>556992</v>
       </c>
       <c r="R42" t="n">
-        <v>7227134</v>
+        <v>7227120</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4849,32 +4849,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126091050</v>
+        <v>126091101</v>
       </c>
       <c r="B43" t="n">
-        <v>80105</v>
+        <v>80076</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>556992</v>
+        <v>556918</v>
       </c>
       <c r="R43" t="n">
-        <v>7227120</v>
+        <v>7227271</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4914,12 +4914,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4950,32 +4950,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126091111</v>
+        <v>126091011</v>
       </c>
       <c r="B44" t="n">
-        <v>80112</v>
+        <v>79005</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>185</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4985,10 +4985,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>557064</v>
+        <v>557066</v>
       </c>
       <c r="R44" t="n">
-        <v>7227147</v>
+        <v>7227351</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5015,12 +5015,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5054,7 +5054,7 @@
         <v>126091025</v>
       </c>
       <c r="B45" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5152,10 +5152,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126091011</v>
+        <v>126091137</v>
       </c>
       <c r="B46" t="n">
-        <v>79005</v>
+        <v>91254</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5163,21 +5163,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>185</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5187,10 +5187,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>557066</v>
+        <v>557054</v>
       </c>
       <c r="R46" t="n">
-        <v>7227351</v>
+        <v>7227134</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5217,12 +5217,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5670,52 +5670,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126091059</v>
+        <v>126091353</v>
       </c>
       <c r="B51" t="n">
-        <v>80077</v>
+        <v>98364</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>221952</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>556914</v>
+        <v>556926</v>
       </c>
       <c r="R51" t="n">
-        <v>7227278</v>
+        <v>7227176</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5742,12 +5735,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5756,7 +5749,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5779,10 +5771,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126091037</v>
+        <v>126091059</v>
       </c>
       <c r="B52" t="n">
-        <v>57652</v>
+        <v>80077</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5790,34 +5782,41 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>556702</v>
+        <v>556914</v>
       </c>
       <c r="R52" t="n">
-        <v>7227082</v>
+        <v>7227278</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5844,17 +5843,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5863,6 +5857,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5986,32 +5981,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126091353</v>
+        <v>126091037</v>
       </c>
       <c r="B54" t="n">
-        <v>98362</v>
+        <v>57652</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6021,10 +6016,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>556926</v>
+        <v>556702</v>
       </c>
       <c r="R54" t="n">
-        <v>7227176</v>
+        <v>7227082</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6051,12 +6046,17 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6090,7 +6090,7 @@
         <v>126091026</v>
       </c>
       <c r="B55" t="n">
-        <v>91931</v>
+        <v>91933</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6188,10 +6188,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126091161</v>
+        <v>126091134</v>
       </c>
       <c r="B56" t="n">
-        <v>78973</v>
+        <v>91254</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6199,21 +6199,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6223,10 +6223,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>557149</v>
+        <v>556726</v>
       </c>
       <c r="R56" t="n">
-        <v>7227169</v>
+        <v>7227062</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6259,11 +6259,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Fertil</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6294,10 +6289,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126091134</v>
+        <v>126091161</v>
       </c>
       <c r="B57" t="n">
-        <v>91252</v>
+        <v>78973</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6305,21 +6300,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6329,10 +6324,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>556726</v>
+        <v>557149</v>
       </c>
       <c r="R57" t="n">
-        <v>7227062</v>
+        <v>7227169</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6365,6 +6360,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6398,7 +6398,7 @@
         <v>126091139</v>
       </c>
       <c r="B58" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6496,32 +6496,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126091091</v>
+        <v>126091082</v>
       </c>
       <c r="B59" t="n">
-        <v>79980</v>
+        <v>80077</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6531,10 +6531,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>557022</v>
+        <v>556947</v>
       </c>
       <c r="R59" t="n">
-        <v>7227286</v>
+        <v>7227303</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6698,10 +6698,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126091054</v>
+        <v>126091091</v>
       </c>
       <c r="B61" t="n">
-        <v>98362</v>
+        <v>79980</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6709,21 +6709,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221952</v>
+        <v>6456</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>556704</v>
+        <v>557022</v>
       </c>
       <c r="R61" t="n">
-        <v>7227103</v>
+        <v>7227286</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6799,10 +6799,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126091057</v>
+        <v>126091054</v>
       </c>
       <c r="B62" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6834,10 +6834,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>557065</v>
+        <v>556704</v>
       </c>
       <c r="R62" t="n">
-        <v>7227144</v>
+        <v>7227103</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6900,32 +6900,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126091082</v>
+        <v>126091057</v>
       </c>
       <c r="B63" t="n">
-        <v>80077</v>
+        <v>98364</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2081</v>
+        <v>221952</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6935,10 +6935,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>556947</v>
+        <v>557065</v>
       </c>
       <c r="R63" t="n">
-        <v>7227303</v>
+        <v>7227144</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6965,12 +6965,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7102,32 +7102,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126091056</v>
+        <v>126091136</v>
       </c>
       <c r="B65" t="n">
-        <v>98362</v>
+        <v>91254</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7137,10 +7137,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>557140</v>
+        <v>556803</v>
       </c>
       <c r="R65" t="n">
-        <v>7227297</v>
+        <v>7227106</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7203,10 +7203,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126091136</v>
+        <v>126091155</v>
       </c>
       <c r="B66" t="n">
-        <v>91252</v>
+        <v>78973</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7214,21 +7214,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7238,10 +7238,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>556803</v>
+        <v>557073</v>
       </c>
       <c r="R66" t="n">
-        <v>7227106</v>
+        <v>7227326</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7268,12 +7268,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7304,10 +7304,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126091155</v>
+        <v>126091081</v>
       </c>
       <c r="B67" t="n">
-        <v>78973</v>
+        <v>80077</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7315,21 +7315,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7339,10 +7339,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>557073</v>
+        <v>556946</v>
       </c>
       <c r="R67" t="n">
-        <v>7227326</v>
+        <v>7227279</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7405,32 +7405,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126091081</v>
+        <v>126091056</v>
       </c>
       <c r="B68" t="n">
-        <v>80077</v>
+        <v>98364</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2081</v>
+        <v>221952</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>556946</v>
+        <v>557140</v>
       </c>
       <c r="R68" t="n">
-        <v>7227279</v>
+        <v>7227297</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7470,12 +7470,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7506,10 +7506,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126091103</v>
+        <v>126091154</v>
       </c>
       <c r="B69" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7517,21 +7517,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7541,10 +7541,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>556737</v>
+        <v>556904</v>
       </c>
       <c r="R69" t="n">
-        <v>7227086</v>
+        <v>7227312</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7571,12 +7571,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7607,10 +7612,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126091154</v>
+        <v>126091086</v>
       </c>
       <c r="B70" t="n">
-        <v>78973</v>
+        <v>80077</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7618,21 +7623,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7642,10 +7647,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>556904</v>
+        <v>556691</v>
       </c>
       <c r="R70" t="n">
-        <v>7227312</v>
+        <v>7227079</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7672,17 +7677,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7814,10 +7814,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126091086</v>
+        <v>126091103</v>
       </c>
       <c r="B72" t="n">
-        <v>80077</v>
+        <v>80076</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7825,21 +7825,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7849,10 +7849,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>556691</v>
+        <v>556737</v>
       </c>
       <c r="R72" t="n">
-        <v>7227079</v>
+        <v>7227086</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>

--- a/artfynd/A 23758-2025 artfynd.xlsx
+++ b/artfynd/A 23758-2025 artfynd.xlsx
@@ -1190,32 +1190,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126091170</v>
+        <v>126091087</v>
       </c>
       <c r="B7" t="n">
-        <v>80111</v>
+        <v>80077</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556915</v>
+        <v>556869</v>
       </c>
       <c r="R7" t="n">
-        <v>7227293</v>
+        <v>7227096</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1291,32 +1291,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126091087</v>
+        <v>126091170</v>
       </c>
       <c r="B8" t="n">
-        <v>80077</v>
+        <v>80111</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1326,10 +1326,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556869</v>
+        <v>556915</v>
       </c>
       <c r="R8" t="n">
-        <v>7227096</v>
+        <v>7227293</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -5362,10 +5362,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126091142</v>
+        <v>126091038</v>
       </c>
       <c r="B48" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5373,21 +5373,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5397,10 +5397,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>557156</v>
+        <v>557057</v>
       </c>
       <c r="R48" t="n">
-        <v>7227270</v>
+        <v>7227134</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5433,6 +5433,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack färsk</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5463,27 +5468,27 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126091038</v>
+        <v>126091113</v>
       </c>
       <c r="B49" t="n">
-        <v>57652</v>
+        <v>57756</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5498,10 +5503,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>557057</v>
+        <v>556728</v>
       </c>
       <c r="R49" t="n">
-        <v>7227134</v>
+        <v>7227079</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5534,11 +5539,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack färsk</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5569,32 +5569,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126091113</v>
+        <v>126091142</v>
       </c>
       <c r="B50" t="n">
-        <v>57756</v>
+        <v>78973</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5604,10 +5604,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>556728</v>
+        <v>557156</v>
       </c>
       <c r="R50" t="n">
-        <v>7227079</v>
+        <v>7227270</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5670,10 +5670,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126091353</v>
+        <v>126091171</v>
       </c>
       <c r="B51" t="n">
-        <v>98364</v>
+        <v>80111</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5681,21 +5681,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5705,10 +5705,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>556926</v>
+        <v>557049</v>
       </c>
       <c r="R51" t="n">
-        <v>7227176</v>
+        <v>7227144</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5735,12 +5735,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5771,10 +5771,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126091059</v>
+        <v>126091037</v>
       </c>
       <c r="B52" t="n">
-        <v>80077</v>
+        <v>57652</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5782,41 +5782,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>556914</v>
+        <v>556702</v>
       </c>
       <c r="R52" t="n">
-        <v>7227278</v>
+        <v>7227082</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5843,12 +5836,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5857,7 +5855,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5880,10 +5877,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126091171</v>
+        <v>126091353</v>
       </c>
       <c r="B53" t="n">
-        <v>80111</v>
+        <v>98364</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5891,21 +5888,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6463</v>
+        <v>221952</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5915,10 +5912,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>557049</v>
+        <v>556926</v>
       </c>
       <c r="R53" t="n">
-        <v>7227144</v>
+        <v>7227176</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5945,12 +5942,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5981,10 +5978,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126091037</v>
+        <v>126091059</v>
       </c>
       <c r="B54" t="n">
-        <v>57652</v>
+        <v>80077</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5992,34 +5989,41 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>556702</v>
+        <v>556914</v>
       </c>
       <c r="R54" t="n">
-        <v>7227082</v>
+        <v>7227278</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6046,17 +6050,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6065,6 +6064,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6496,32 +6496,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126091082</v>
+        <v>126091446</v>
       </c>
       <c r="B59" t="n">
-        <v>80077</v>
+        <v>80111</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6531,10 +6531,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>556947</v>
+        <v>556925</v>
       </c>
       <c r="R59" t="n">
-        <v>7227303</v>
+        <v>7227179</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6561,12 +6561,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6597,10 +6597,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126091446</v>
+        <v>126091091</v>
       </c>
       <c r="B60" t="n">
-        <v>80111</v>
+        <v>79980</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6608,21 +6608,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6463</v>
+        <v>6456</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6632,10 +6632,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>556925</v>
+        <v>557022</v>
       </c>
       <c r="R60" t="n">
-        <v>7227179</v>
+        <v>7227286</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6662,12 +6662,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6698,32 +6698,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126091091</v>
+        <v>126091082</v>
       </c>
       <c r="B61" t="n">
-        <v>79980</v>
+        <v>80077</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>557022</v>
+        <v>556947</v>
       </c>
       <c r="R61" t="n">
-        <v>7227286</v>
+        <v>7227303</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>

--- a/artfynd/A 23758-2025 artfynd.xlsx
+++ b/artfynd/A 23758-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126091009</v>
+        <v>126091092</v>
       </c>
       <c r="B2" t="n">
-        <v>80112</v>
+        <v>79980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6464</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556917</v>
+        <v>556906</v>
       </c>
       <c r="R2" t="n">
-        <v>7227275</v>
+        <v>7227086</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -757,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -780,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126091092</v>
+        <v>126091009</v>
       </c>
       <c r="B3" t="n">
-        <v>79980</v>
+        <v>80112</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,34 +787,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556906</v>
+        <v>556917</v>
       </c>
       <c r="R3" t="n">
-        <v>7227086</v>
+        <v>7227275</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -845,12 +844,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -859,6 +858,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1091,7 +1091,7 @@
         <v>126091099</v>
       </c>
       <c r="B6" t="n">
-        <v>98247</v>
+        <v>98249</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,32 +1190,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126091087</v>
+        <v>126091170</v>
       </c>
       <c r="B7" t="n">
-        <v>80077</v>
+        <v>80111</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556869</v>
+        <v>556915</v>
       </c>
       <c r="R7" t="n">
-        <v>7227096</v>
+        <v>7227293</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1291,32 +1291,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126091170</v>
+        <v>126091087</v>
       </c>
       <c r="B8" t="n">
-        <v>80111</v>
+        <v>80077</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1326,10 +1326,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556915</v>
+        <v>556869</v>
       </c>
       <c r="R8" t="n">
-        <v>7227293</v>
+        <v>7227096</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1493,10 +1493,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126091080</v>
+        <v>126091138</v>
       </c>
       <c r="B10" t="n">
-        <v>80077</v>
+        <v>91256</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1504,21 +1504,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1528,10 +1528,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>556915</v>
+        <v>557073</v>
       </c>
       <c r="R10" t="n">
-        <v>7227290</v>
+        <v>7227154</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1558,12 +1558,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1594,10 +1594,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126091138</v>
+        <v>126091080</v>
       </c>
       <c r="B11" t="n">
-        <v>91254</v>
+        <v>80077</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1605,21 +1605,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557073</v>
+        <v>556915</v>
       </c>
       <c r="R11" t="n">
-        <v>7227154</v>
+        <v>7227290</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1659,12 +1659,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1698,7 +1698,7 @@
         <v>126091058</v>
       </c>
       <c r="B12" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>126091055</v>
       </c>
       <c r="B13" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126091083</v>
+        <v>126091159</v>
       </c>
       <c r="B14" t="n">
-        <v>80077</v>
+        <v>78973</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,21 +1908,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>556975</v>
+        <v>557055</v>
       </c>
       <c r="R14" t="n">
-        <v>7227303</v>
+        <v>7227102</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1962,12 +1962,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1998,32 +1998,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126091118</v>
+        <v>126091112</v>
       </c>
       <c r="B15" t="n">
-        <v>57808</v>
+        <v>57756</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103022</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2033,10 +2033,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>556859</v>
+        <v>556726</v>
       </c>
       <c r="R15" t="n">
-        <v>7227119</v>
+        <v>7227088</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2099,32 +2099,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126091112</v>
+        <v>126091083</v>
       </c>
       <c r="B16" t="n">
-        <v>57756</v>
+        <v>80077</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103031</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2134,10 +2134,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>556726</v>
+        <v>556975</v>
       </c>
       <c r="R16" t="n">
-        <v>7227088</v>
+        <v>7227303</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2164,12 +2164,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2200,10 +2200,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126091159</v>
+        <v>126091118</v>
       </c>
       <c r="B17" t="n">
-        <v>78973</v>
+        <v>57808</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2211,21 +2211,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>103022</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>557055</v>
+        <v>556859</v>
       </c>
       <c r="R17" t="n">
-        <v>7227102</v>
+        <v>7227119</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2301,32 +2301,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126091047</v>
+        <v>126091156</v>
       </c>
       <c r="B18" t="n">
-        <v>80105</v>
+        <v>78973</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2336,10 +2336,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>556947</v>
+        <v>556815</v>
       </c>
       <c r="R18" t="n">
-        <v>7227277</v>
+        <v>7227118</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2366,12 +2366,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2508,32 +2508,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126091079</v>
+        <v>126091047</v>
       </c>
       <c r="B20" t="n">
-        <v>80077</v>
+        <v>80105</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2543,10 +2543,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>556916</v>
+        <v>556947</v>
       </c>
       <c r="R20" t="n">
-        <v>7227278</v>
+        <v>7227277</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2609,10 +2609,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126091022</v>
+        <v>126091079</v>
       </c>
       <c r="B21" t="n">
-        <v>91236</v>
+        <v>80077</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2620,21 +2620,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2644,10 +2644,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>557054</v>
+        <v>556916</v>
       </c>
       <c r="R21" t="n">
-        <v>7227356</v>
+        <v>7227278</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2710,10 +2710,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126091088</v>
+        <v>126091022</v>
       </c>
       <c r="B22" t="n">
-        <v>80077</v>
+        <v>91238</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2721,21 +2721,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>557057</v>
+        <v>557054</v>
       </c>
       <c r="R22" t="n">
-        <v>7227107</v>
+        <v>7227356</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2811,10 +2811,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126091156</v>
+        <v>126091088</v>
       </c>
       <c r="B23" t="n">
-        <v>78973</v>
+        <v>80077</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2822,21 +2822,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2846,10 +2846,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>556815</v>
+        <v>557057</v>
       </c>
       <c r="R23" t="n">
-        <v>7227118</v>
+        <v>7227107</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3013,32 +3013,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126091048</v>
+        <v>126091096</v>
       </c>
       <c r="B25" t="n">
-        <v>80105</v>
+        <v>57652</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3048,10 +3048,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>556737</v>
+        <v>556986</v>
       </c>
       <c r="R25" t="n">
-        <v>7227086</v>
+        <v>7227133</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3084,6 +3084,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3114,32 +3119,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126091096</v>
+        <v>126091048</v>
       </c>
       <c r="B26" t="n">
-        <v>57652</v>
+        <v>80105</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3149,10 +3154,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>556986</v>
+        <v>556737</v>
       </c>
       <c r="R26" t="n">
-        <v>7227133</v>
+        <v>7227086</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3185,11 +3190,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3220,32 +3220,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126091021</v>
+        <v>126091094</v>
       </c>
       <c r="B27" t="n">
-        <v>91236</v>
+        <v>79980</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3255,10 +3255,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>557035</v>
+        <v>556900</v>
       </c>
       <c r="R27" t="n">
-        <v>7227275</v>
+        <v>7227075</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3285,12 +3285,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3321,32 +3321,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126091094</v>
+        <v>126091158</v>
       </c>
       <c r="B28" t="n">
-        <v>79980</v>
+        <v>78973</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>556900</v>
+        <v>556943</v>
       </c>
       <c r="R28" t="n">
-        <v>7227075</v>
+        <v>7227059</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3422,10 +3422,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126091158</v>
+        <v>126091021</v>
       </c>
       <c r="B29" t="n">
-        <v>78973</v>
+        <v>91238</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3433,21 +3433,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3457,10 +3457,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>556943</v>
+        <v>557035</v>
       </c>
       <c r="R29" t="n">
-        <v>7227059</v>
+        <v>7227275</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3487,12 +3487,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3523,32 +3523,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126091078</v>
+        <v>126091045</v>
       </c>
       <c r="B30" t="n">
-        <v>80077</v>
+        <v>80105</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3558,10 +3558,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>556918</v>
+        <v>556904</v>
       </c>
       <c r="R30" t="n">
-        <v>7227271</v>
+        <v>7227312</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3627,7 +3627,7 @@
         <v>126091133</v>
       </c>
       <c r="B31" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3725,32 +3725,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126091122</v>
+        <v>126091078</v>
       </c>
       <c r="B32" t="n">
-        <v>91596</v>
+        <v>80077</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2063</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3760,10 +3760,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>556726</v>
+        <v>556918</v>
       </c>
       <c r="R32" t="n">
-        <v>7227064</v>
+        <v>7227271</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3790,12 +3790,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3826,32 +3826,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126091077</v>
+        <v>126091122</v>
       </c>
       <c r="B33" t="n">
-        <v>80077</v>
+        <v>91598</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>2063</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>556902</v>
+        <v>556726</v>
       </c>
       <c r="R33" t="n">
-        <v>7227281</v>
+        <v>7227064</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3891,12 +3891,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3927,32 +3927,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126091045</v>
+        <v>126091077</v>
       </c>
       <c r="B34" t="n">
-        <v>80105</v>
+        <v>80077</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3962,10 +3962,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>556904</v>
+        <v>556902</v>
       </c>
       <c r="R34" t="n">
-        <v>7227312</v>
+        <v>7227281</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4031,7 +4031,7 @@
         <v>126091097</v>
       </c>
       <c r="B35" t="n">
-        <v>97227</v>
+        <v>97229</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4129,10 +4129,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126091032</v>
+        <v>126091131</v>
       </c>
       <c r="B36" t="n">
-        <v>57652</v>
+        <v>91256</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4140,21 +4140,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4164,10 +4164,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>557048</v>
+        <v>556707</v>
       </c>
       <c r="R36" t="n">
-        <v>7227240</v>
+        <v>7227095</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4194,17 +4194,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4235,10 +4230,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126091131</v>
+        <v>126091032</v>
       </c>
       <c r="B37" t="n">
-        <v>91254</v>
+        <v>57652</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4246,21 +4241,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4270,10 +4265,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>556707</v>
+        <v>557048</v>
       </c>
       <c r="R37" t="n">
-        <v>7227095</v>
+        <v>7227240</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4300,12 +4295,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4647,32 +4647,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126091111</v>
+        <v>126091101</v>
       </c>
       <c r="B41" t="n">
-        <v>80112</v>
+        <v>80076</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4682,10 +4682,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>557064</v>
+        <v>556918</v>
       </c>
       <c r="R41" t="n">
-        <v>7227147</v>
+        <v>7227271</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4748,32 +4748,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126091050</v>
+        <v>126091137</v>
       </c>
       <c r="B42" t="n">
-        <v>80105</v>
+        <v>91256</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>556992</v>
+        <v>557054</v>
       </c>
       <c r="R42" t="n">
-        <v>7227120</v>
+        <v>7227134</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4849,32 +4849,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126091101</v>
+        <v>126091050</v>
       </c>
       <c r="B43" t="n">
-        <v>80076</v>
+        <v>80105</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>556918</v>
+        <v>556992</v>
       </c>
       <c r="R43" t="n">
-        <v>7227271</v>
+        <v>7227120</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4914,12 +4914,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4950,32 +4950,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126091011</v>
+        <v>126091111</v>
       </c>
       <c r="B44" t="n">
-        <v>79005</v>
+        <v>80112</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>185</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4985,10 +4985,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>557066</v>
+        <v>557064</v>
       </c>
       <c r="R44" t="n">
-        <v>7227351</v>
+        <v>7227147</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5015,12 +5015,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5054,7 +5054,7 @@
         <v>126091025</v>
       </c>
       <c r="B45" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5152,10 +5152,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126091137</v>
+        <v>126091011</v>
       </c>
       <c r="B46" t="n">
-        <v>91254</v>
+        <v>79005</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5163,21 +5163,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>185</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5187,10 +5187,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>557054</v>
+        <v>557066</v>
       </c>
       <c r="R46" t="n">
-        <v>7227134</v>
+        <v>7227351</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5217,12 +5217,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5362,10 +5362,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126091038</v>
+        <v>126091142</v>
       </c>
       <c r="B48" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5373,21 +5373,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5397,10 +5397,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>557057</v>
+        <v>557156</v>
       </c>
       <c r="R48" t="n">
-        <v>7227134</v>
+        <v>7227270</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5433,11 +5433,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack färsk</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5468,27 +5463,27 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126091113</v>
+        <v>126091038</v>
       </c>
       <c r="B49" t="n">
-        <v>57756</v>
+        <v>57652</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5503,10 +5498,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>556728</v>
+        <v>557057</v>
       </c>
       <c r="R49" t="n">
-        <v>7227079</v>
+        <v>7227134</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5539,6 +5534,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack färsk</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5569,32 +5569,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126091142</v>
+        <v>126091113</v>
       </c>
       <c r="B50" t="n">
-        <v>78973</v>
+        <v>57756</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5604,10 +5604,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>557156</v>
+        <v>556728</v>
       </c>
       <c r="R50" t="n">
-        <v>7227270</v>
+        <v>7227079</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5877,45 +5877,52 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126091353</v>
+        <v>126091059</v>
       </c>
       <c r="B53" t="n">
-        <v>98364</v>
+        <v>80077</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>556926</v>
+        <v>556914</v>
       </c>
       <c r="R53" t="n">
-        <v>7227176</v>
+        <v>7227278</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5942,12 +5949,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5956,6 +5963,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5978,52 +5986,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126091059</v>
+        <v>126091353</v>
       </c>
       <c r="B54" t="n">
-        <v>80077</v>
+        <v>98366</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2081</v>
+        <v>221952</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>556914</v>
+        <v>556926</v>
       </c>
       <c r="R54" t="n">
-        <v>7227278</v>
+        <v>7227176</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6050,12 +6051,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6064,7 +6065,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6090,7 +6090,7 @@
         <v>126091026</v>
       </c>
       <c r="B55" t="n">
-        <v>91933</v>
+        <v>91935</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6188,10 +6188,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126091134</v>
+        <v>126091161</v>
       </c>
       <c r="B56" t="n">
-        <v>91254</v>
+        <v>78973</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6199,21 +6199,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6223,10 +6223,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>556726</v>
+        <v>557149</v>
       </c>
       <c r="R56" t="n">
-        <v>7227062</v>
+        <v>7227169</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6259,6 +6259,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6289,10 +6294,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126091161</v>
+        <v>126091134</v>
       </c>
       <c r="B57" t="n">
-        <v>78973</v>
+        <v>91256</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6300,21 +6305,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6324,10 +6329,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>557149</v>
+        <v>556726</v>
       </c>
       <c r="R57" t="n">
-        <v>7227169</v>
+        <v>7227062</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6360,11 +6365,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Fertil</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6398,7 +6398,7 @@
         <v>126091139</v>
       </c>
       <c r="B58" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6496,10 +6496,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126091446</v>
+        <v>126091091</v>
       </c>
       <c r="B59" t="n">
-        <v>80111</v>
+        <v>79980</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6507,21 +6507,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6463</v>
+        <v>6456</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6531,10 +6531,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>556925</v>
+        <v>557022</v>
       </c>
       <c r="R59" t="n">
-        <v>7227179</v>
+        <v>7227286</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6561,12 +6561,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6597,10 +6597,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126091091</v>
+        <v>126091446</v>
       </c>
       <c r="B60" t="n">
-        <v>79980</v>
+        <v>80111</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6608,21 +6608,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6456</v>
+        <v>6463</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6632,10 +6632,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>557022</v>
+        <v>556925</v>
       </c>
       <c r="R60" t="n">
-        <v>7227286</v>
+        <v>7227179</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6662,12 +6662,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6802,7 +6802,7 @@
         <v>126091054</v>
       </c>
       <c r="B62" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>126091057</v>
       </c>
       <c r="B63" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>126091136</v>
       </c>
       <c r="B65" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7304,32 +7304,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126091081</v>
+        <v>126091056</v>
       </c>
       <c r="B67" t="n">
-        <v>80077</v>
+        <v>98366</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2081</v>
+        <v>221952</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7339,10 +7339,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>556946</v>
+        <v>557140</v>
       </c>
       <c r="R67" t="n">
-        <v>7227279</v>
+        <v>7227297</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7369,12 +7369,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7405,32 +7405,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126091056</v>
+        <v>126091081</v>
       </c>
       <c r="B68" t="n">
-        <v>98364</v>
+        <v>80077</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>557140</v>
+        <v>556946</v>
       </c>
       <c r="R68" t="n">
-        <v>7227297</v>
+        <v>7227279</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7470,12 +7470,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7506,10 +7506,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126091154</v>
+        <v>126091086</v>
       </c>
       <c r="B69" t="n">
-        <v>78973</v>
+        <v>80077</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7517,21 +7517,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7541,10 +7541,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>556904</v>
+        <v>556691</v>
       </c>
       <c r="R69" t="n">
-        <v>7227312</v>
+        <v>7227079</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7571,17 +7571,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7612,32 +7607,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126091086</v>
+        <v>126091046</v>
       </c>
       <c r="B70" t="n">
-        <v>80077</v>
+        <v>80105</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7647,10 +7642,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>556691</v>
+        <v>556915</v>
       </c>
       <c r="R70" t="n">
-        <v>7227079</v>
+        <v>7227293</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7677,12 +7672,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7713,32 +7708,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126091046</v>
+        <v>126091103</v>
       </c>
       <c r="B71" t="n">
-        <v>80105</v>
+        <v>80076</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7748,10 +7743,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>556915</v>
+        <v>556737</v>
       </c>
       <c r="R71" t="n">
-        <v>7227293</v>
+        <v>7227086</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7778,12 +7773,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7814,10 +7809,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126091103</v>
+        <v>126091154</v>
       </c>
       <c r="B72" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7825,21 +7820,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7849,10 +7844,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>556737</v>
+        <v>556904</v>
       </c>
       <c r="R72" t="n">
-        <v>7227086</v>
+        <v>7227312</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7879,12 +7874,17 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD72" t="b">

--- a/artfynd/A 23758-2025 artfynd.xlsx
+++ b/artfynd/A 23758-2025 artfynd.xlsx
@@ -1190,32 +1190,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126091170</v>
+        <v>126091087</v>
       </c>
       <c r="B7" t="n">
-        <v>80111</v>
+        <v>80077</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556915</v>
+        <v>556869</v>
       </c>
       <c r="R7" t="n">
-        <v>7227293</v>
+        <v>7227096</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1291,32 +1291,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126091087</v>
+        <v>126091170</v>
       </c>
       <c r="B8" t="n">
-        <v>80077</v>
+        <v>80111</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1326,10 +1326,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556869</v>
+        <v>556915</v>
       </c>
       <c r="R8" t="n">
-        <v>7227096</v>
+        <v>7227293</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -3523,32 +3523,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126091045</v>
+        <v>126091078</v>
       </c>
       <c r="B30" t="n">
-        <v>80105</v>
+        <v>80077</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3558,10 +3558,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>556904</v>
+        <v>556918</v>
       </c>
       <c r="R30" t="n">
-        <v>7227312</v>
+        <v>7227271</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3624,32 +3624,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126091133</v>
+        <v>126091045</v>
       </c>
       <c r="B31" t="n">
-        <v>91256</v>
+        <v>80105</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3659,10 +3659,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>556729</v>
+        <v>556904</v>
       </c>
       <c r="R31" t="n">
-        <v>7227082</v>
+        <v>7227312</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3689,12 +3689,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3725,10 +3725,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126091078</v>
+        <v>126091133</v>
       </c>
       <c r="B32" t="n">
-        <v>80077</v>
+        <v>91256</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3736,21 +3736,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3760,10 +3760,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>556918</v>
+        <v>556729</v>
       </c>
       <c r="R32" t="n">
-        <v>7227271</v>
+        <v>7227082</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3790,12 +3790,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -5463,27 +5463,27 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126091038</v>
+        <v>126091113</v>
       </c>
       <c r="B49" t="n">
-        <v>57652</v>
+        <v>57756</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5498,10 +5498,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>557057</v>
+        <v>556728</v>
       </c>
       <c r="R49" t="n">
-        <v>7227134</v>
+        <v>7227079</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5534,11 +5534,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack färsk</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5569,27 +5564,27 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126091113</v>
+        <v>126091038</v>
       </c>
       <c r="B50" t="n">
-        <v>57756</v>
+        <v>57652</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5604,10 +5599,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>556728</v>
+        <v>557057</v>
       </c>
       <c r="R50" t="n">
-        <v>7227079</v>
+        <v>7227134</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5640,6 +5635,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack färsk</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5670,45 +5670,52 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126091171</v>
+        <v>126091059</v>
       </c>
       <c r="B51" t="n">
-        <v>80111</v>
+        <v>80077</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>557049</v>
+        <v>556914</v>
       </c>
       <c r="R51" t="n">
-        <v>7227144</v>
+        <v>7227278</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5735,12 +5742,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5749,6 +5756,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5771,32 +5779,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126091037</v>
+        <v>126091353</v>
       </c>
       <c r="B52" t="n">
-        <v>57652</v>
+        <v>98366</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5806,10 +5814,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>556702</v>
+        <v>556926</v>
       </c>
       <c r="R52" t="n">
-        <v>7227082</v>
+        <v>7227176</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5836,17 +5844,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5877,52 +5880,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126091059</v>
+        <v>126091171</v>
       </c>
       <c r="B53" t="n">
-        <v>80077</v>
+        <v>80111</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>556914</v>
+        <v>557049</v>
       </c>
       <c r="R53" t="n">
-        <v>7227278</v>
+        <v>7227144</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5949,12 +5945,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5963,7 +5959,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5986,32 +5981,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126091353</v>
+        <v>126091037</v>
       </c>
       <c r="B54" t="n">
-        <v>98366</v>
+        <v>57652</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6021,10 +6016,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>556926</v>
+        <v>556702</v>
       </c>
       <c r="R54" t="n">
-        <v>7227176</v>
+        <v>7227082</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6051,12 +6046,17 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7102,32 +7102,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126091136</v>
+        <v>126091056</v>
       </c>
       <c r="B65" t="n">
-        <v>91256</v>
+        <v>98366</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7137,10 +7137,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>556803</v>
+        <v>557140</v>
       </c>
       <c r="R65" t="n">
-        <v>7227106</v>
+        <v>7227297</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7203,10 +7203,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126091155</v>
+        <v>126091136</v>
       </c>
       <c r="B66" t="n">
-        <v>78973</v>
+        <v>91256</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7214,21 +7214,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7238,10 +7238,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>557073</v>
+        <v>556803</v>
       </c>
       <c r="R66" t="n">
-        <v>7227326</v>
+        <v>7227106</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7268,12 +7268,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7304,32 +7304,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126091056</v>
+        <v>126091155</v>
       </c>
       <c r="B67" t="n">
-        <v>98366</v>
+        <v>78973</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7339,10 +7339,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>557140</v>
+        <v>557073</v>
       </c>
       <c r="R67" t="n">
-        <v>7227297</v>
+        <v>7227326</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7369,12 +7369,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7506,32 +7506,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126091086</v>
+        <v>126091046</v>
       </c>
       <c r="B69" t="n">
-        <v>80077</v>
+        <v>80105</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7541,10 +7541,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>556691</v>
+        <v>556915</v>
       </c>
       <c r="R69" t="n">
-        <v>7227079</v>
+        <v>7227293</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7571,12 +7571,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7607,32 +7607,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126091046</v>
+        <v>126091103</v>
       </c>
       <c r="B70" t="n">
-        <v>80105</v>
+        <v>80076</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7642,10 +7642,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>556915</v>
+        <v>556737</v>
       </c>
       <c r="R70" t="n">
-        <v>7227293</v>
+        <v>7227086</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7708,10 +7708,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126091103</v>
+        <v>126091154</v>
       </c>
       <c r="B71" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7719,21 +7719,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7743,10 +7743,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>556737</v>
+        <v>556904</v>
       </c>
       <c r="R71" t="n">
-        <v>7227086</v>
+        <v>7227312</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7773,12 +7773,17 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7809,10 +7814,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126091154</v>
+        <v>126091086</v>
       </c>
       <c r="B72" t="n">
-        <v>78973</v>
+        <v>80077</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7820,21 +7825,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7844,10 +7849,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>556904</v>
+        <v>556691</v>
       </c>
       <c r="R72" t="n">
-        <v>7227312</v>
+        <v>7227079</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7874,17 +7879,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD72" t="b">

--- a/artfynd/A 23758-2025 artfynd.xlsx
+++ b/artfynd/A 23758-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126091092</v>
       </c>
       <c r="B2" t="n">
-        <v>79980</v>
+        <v>79984</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126091009</v>
       </c>
       <c r="B3" t="n">
-        <v>80112</v>
+        <v>80116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,10 +881,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126091089</v>
+        <v>126091030</v>
       </c>
       <c r="B4" t="n">
-        <v>80077</v>
+        <v>57656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -892,21 +892,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -916,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>557054</v>
+        <v>557050</v>
       </c>
       <c r="R4" t="n">
-        <v>7227146</v>
+        <v>7227253</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -946,12 +946,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -982,32 +987,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126091030</v>
+        <v>126091099</v>
       </c>
       <c r="B5" t="n">
-        <v>57652</v>
+        <v>98253</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1017,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>557050</v>
+        <v>557073</v>
       </c>
       <c r="R5" t="n">
-        <v>7227253</v>
+        <v>7227326</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1055,17 +1060,13 @@
           <t>2025-06-18</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1088,32 +1089,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126091099</v>
+        <v>126091089</v>
       </c>
       <c r="B6" t="n">
-        <v>98249</v>
+        <v>80081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220093</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>557073</v>
+        <v>557054</v>
       </c>
       <c r="R6" t="n">
-        <v>7227326</v>
+        <v>7227146</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1153,12 +1154,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1167,7 +1168,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126091087</v>
+        <v>126091117</v>
       </c>
       <c r="B7" t="n">
-        <v>80077</v>
+        <v>57812</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>103022</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556869</v>
+        <v>556827</v>
       </c>
       <c r="R7" t="n">
-        <v>7227096</v>
+        <v>7227124</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,32 +1291,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126091170</v>
+        <v>126091087</v>
       </c>
       <c r="B8" t="n">
-        <v>80111</v>
+        <v>80081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1326,10 +1326,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556915</v>
+        <v>556869</v>
       </c>
       <c r="R8" t="n">
-        <v>7227293</v>
+        <v>7227096</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1392,32 +1392,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126091117</v>
+        <v>126091170</v>
       </c>
       <c r="B9" t="n">
-        <v>57808</v>
+        <v>80115</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103022</v>
+        <v>6463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556827</v>
+        <v>556915</v>
       </c>
       <c r="R9" t="n">
-        <v>7227124</v>
+        <v>7227293</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1493,32 +1493,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126091138</v>
+        <v>126091058</v>
       </c>
       <c r="B10" t="n">
-        <v>91256</v>
+        <v>98370</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1528,10 +1528,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557073</v>
+        <v>557128</v>
       </c>
       <c r="R10" t="n">
-        <v>7227154</v>
+        <v>7227190</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,7 +1597,7 @@
         <v>126091080</v>
       </c>
       <c r="B11" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1695,32 +1695,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126091058</v>
+        <v>126091138</v>
       </c>
       <c r="B12" t="n">
-        <v>98366</v>
+        <v>91260</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>557128</v>
+        <v>557073</v>
       </c>
       <c r="R12" t="n">
-        <v>7227190</v>
+        <v>7227154</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1799,7 +1799,7 @@
         <v>126091055</v>
       </c>
       <c r="B13" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126091159</v>
+        <v>126091083</v>
       </c>
       <c r="B14" t="n">
-        <v>78973</v>
+        <v>80081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,21 +1908,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557055</v>
+        <v>556975</v>
       </c>
       <c r="R14" t="n">
-        <v>7227102</v>
+        <v>7227303</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1962,12 +1962,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1998,32 +1998,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126091112</v>
+        <v>126091159</v>
       </c>
       <c r="B15" t="n">
-        <v>57756</v>
+        <v>78977</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2033,10 +2033,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>556726</v>
+        <v>557055</v>
       </c>
       <c r="R15" t="n">
-        <v>7227088</v>
+        <v>7227102</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2099,10 +2099,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126091083</v>
+        <v>126091118</v>
       </c>
       <c r="B16" t="n">
-        <v>80077</v>
+        <v>57812</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2110,21 +2110,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>103022</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2134,10 +2134,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>556975</v>
+        <v>556859</v>
       </c>
       <c r="R16" t="n">
-        <v>7227303</v>
+        <v>7227119</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2164,12 +2164,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2200,32 +2200,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126091118</v>
+        <v>126091112</v>
       </c>
       <c r="B17" t="n">
-        <v>57808</v>
+        <v>57760</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103022</v>
+        <v>103031</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>556859</v>
+        <v>556726</v>
       </c>
       <c r="R17" t="n">
-        <v>7227119</v>
+        <v>7227088</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2304,7 +2304,7 @@
         <v>126091156</v>
       </c>
       <c r="B18" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2402,32 +2402,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126091157</v>
+        <v>126091047</v>
       </c>
       <c r="B19" t="n">
-        <v>78973</v>
+        <v>80109</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2437,10 +2437,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>556844</v>
+        <v>556947</v>
       </c>
       <c r="R19" t="n">
-        <v>7227129</v>
+        <v>7227277</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2467,17 +2467,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Fertil</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2508,32 +2503,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126091047</v>
+        <v>126091079</v>
       </c>
       <c r="B20" t="n">
-        <v>80105</v>
+        <v>80081</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2543,10 +2538,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>556947</v>
+        <v>556916</v>
       </c>
       <c r="R20" t="n">
-        <v>7227277</v>
+        <v>7227278</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2609,10 +2604,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126091079</v>
+        <v>126091157</v>
       </c>
       <c r="B21" t="n">
-        <v>80077</v>
+        <v>78977</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2620,21 +2615,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2644,10 +2639,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>556916</v>
+        <v>556844</v>
       </c>
       <c r="R21" t="n">
-        <v>7227278</v>
+        <v>7227129</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2674,12 +2669,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2710,10 +2710,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126091022</v>
+        <v>126091088</v>
       </c>
       <c r="B22" t="n">
-        <v>91238</v>
+        <v>80081</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2721,21 +2721,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>557054</v>
+        <v>557057</v>
       </c>
       <c r="R22" t="n">
-        <v>7227356</v>
+        <v>7227107</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2811,10 +2811,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126091088</v>
+        <v>126091022</v>
       </c>
       <c r="B23" t="n">
-        <v>80077</v>
+        <v>91242</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2822,21 +2822,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2846,10 +2846,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>557057</v>
+        <v>557054</v>
       </c>
       <c r="R23" t="n">
-        <v>7227107</v>
+        <v>7227356</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2876,12 +2876,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2915,7 +2915,7 @@
         <v>126091109</v>
       </c>
       <c r="B24" t="n">
-        <v>80112</v>
+        <v>80116</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3013,32 +3013,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126091096</v>
+        <v>126091048</v>
       </c>
       <c r="B25" t="n">
-        <v>57652</v>
+        <v>80109</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3048,10 +3048,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>556986</v>
+        <v>556737</v>
       </c>
       <c r="R25" t="n">
-        <v>7227133</v>
+        <v>7227086</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3084,11 +3084,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3119,32 +3114,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126091048</v>
+        <v>126091096</v>
       </c>
       <c r="B26" t="n">
-        <v>80105</v>
+        <v>57656</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3154,10 +3149,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>556737</v>
+        <v>556986</v>
       </c>
       <c r="R26" t="n">
-        <v>7227086</v>
+        <v>7227133</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3190,6 +3185,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3220,32 +3220,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126091094</v>
+        <v>126091021</v>
       </c>
       <c r="B27" t="n">
-        <v>79980</v>
+        <v>91242</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3255,10 +3255,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>556900</v>
+        <v>557035</v>
       </c>
       <c r="R27" t="n">
-        <v>7227075</v>
+        <v>7227275</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3285,12 +3285,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3321,32 +3321,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126091158</v>
+        <v>126091094</v>
       </c>
       <c r="B28" t="n">
-        <v>78973</v>
+        <v>79984</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>556943</v>
+        <v>556900</v>
       </c>
       <c r="R28" t="n">
-        <v>7227059</v>
+        <v>7227075</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3422,10 +3422,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126091021</v>
+        <v>126091158</v>
       </c>
       <c r="B29" t="n">
-        <v>91238</v>
+        <v>78977</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3433,21 +3433,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3457,10 +3457,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>557035</v>
+        <v>556943</v>
       </c>
       <c r="R29" t="n">
-        <v>7227275</v>
+        <v>7227059</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3487,12 +3487,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3523,32 +3523,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126091078</v>
+        <v>126091045</v>
       </c>
       <c r="B30" t="n">
-        <v>80077</v>
+        <v>80109</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3558,10 +3558,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>556918</v>
+        <v>556904</v>
       </c>
       <c r="R30" t="n">
-        <v>7227271</v>
+        <v>7227312</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3624,32 +3624,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126091045</v>
+        <v>126091078</v>
       </c>
       <c r="B31" t="n">
-        <v>80105</v>
+        <v>80081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3659,10 +3659,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>556904</v>
+        <v>556918</v>
       </c>
       <c r="R31" t="n">
-        <v>7227312</v>
+        <v>7227271</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3728,7 +3728,7 @@
         <v>126091133</v>
       </c>
       <c r="B32" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>126091122</v>
       </c>
       <c r="B33" t="n">
-        <v>91598</v>
+        <v>91602</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>126091077</v>
       </c>
       <c r="B34" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>126091097</v>
       </c>
       <c r="B35" t="n">
-        <v>97229</v>
+        <v>97233</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4129,10 +4129,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126091131</v>
+        <v>126091032</v>
       </c>
       <c r="B36" t="n">
-        <v>91256</v>
+        <v>57656</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4140,21 +4140,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4164,10 +4164,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>556707</v>
+        <v>557048</v>
       </c>
       <c r="R36" t="n">
-        <v>7227095</v>
+        <v>7227240</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4194,12 +4194,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4230,10 +4235,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126091032</v>
+        <v>126091131</v>
       </c>
       <c r="B37" t="n">
-        <v>57652</v>
+        <v>91260</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4241,21 +4246,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4265,10 +4270,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>557048</v>
+        <v>556707</v>
       </c>
       <c r="R37" t="n">
-        <v>7227240</v>
+        <v>7227095</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4295,17 +4300,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4339,7 +4339,7 @@
         <v>126091108</v>
       </c>
       <c r="B38" t="n">
-        <v>80112</v>
+        <v>80116</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4437,45 +4437,52 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126091110</v>
+        <v>126091060</v>
       </c>
       <c r="B39" t="n">
-        <v>80112</v>
+        <v>80081</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>557049</v>
+        <v>556945</v>
       </c>
       <c r="R39" t="n">
-        <v>7227144</v>
+        <v>7227306</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4502,12 +4509,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4516,6 +4523,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4538,52 +4546,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126091060</v>
+        <v>126091110</v>
       </c>
       <c r="B40" t="n">
-        <v>80077</v>
+        <v>80116</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>556945</v>
+        <v>557049</v>
       </c>
       <c r="R40" t="n">
-        <v>7227306</v>
+        <v>7227144</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4610,12 +4611,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4624,7 +4625,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4650,7 +4650,7 @@
         <v>126091101</v>
       </c>
       <c r="B41" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4748,32 +4748,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126091137</v>
+        <v>126091050</v>
       </c>
       <c r="B42" t="n">
-        <v>91256</v>
+        <v>80109</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>557054</v>
+        <v>556992</v>
       </c>
       <c r="R42" t="n">
-        <v>7227134</v>
+        <v>7227120</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4849,10 +4849,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126091050</v>
+        <v>126091111</v>
       </c>
       <c r="B43" t="n">
-        <v>80105</v>
+        <v>80116</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4860,21 +4860,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>556992</v>
+        <v>557064</v>
       </c>
       <c r="R43" t="n">
-        <v>7227120</v>
+        <v>7227147</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4950,32 +4950,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126091111</v>
+        <v>126091137</v>
       </c>
       <c r="B44" t="n">
-        <v>80112</v>
+        <v>91260</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4985,10 +4985,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>557064</v>
+        <v>557054</v>
       </c>
       <c r="R44" t="n">
-        <v>7227147</v>
+        <v>7227134</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5051,10 +5051,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126091025</v>
+        <v>126091061</v>
       </c>
       <c r="B45" t="n">
-        <v>91238</v>
+        <v>80081</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5062,34 +5062,41 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>556986</v>
+        <v>557049</v>
       </c>
       <c r="R45" t="n">
-        <v>7227133</v>
+        <v>7227144</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5130,6 +5137,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5152,10 +5160,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126091011</v>
+        <v>126091025</v>
       </c>
       <c r="B46" t="n">
-        <v>79005</v>
+        <v>91242</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5163,21 +5171,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5187,10 +5195,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>557066</v>
+        <v>556986</v>
       </c>
       <c r="R46" t="n">
-        <v>7227351</v>
+        <v>7227133</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5217,12 +5225,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5253,10 +5261,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126091061</v>
+        <v>126091011</v>
       </c>
       <c r="B47" t="n">
-        <v>80077</v>
+        <v>79009</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5264,41 +5272,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>557049</v>
+        <v>557066</v>
       </c>
       <c r="R47" t="n">
-        <v>7227144</v>
+        <v>7227351</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5325,12 +5326,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5339,7 +5340,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5362,10 +5362,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126091142</v>
+        <v>126091038</v>
       </c>
       <c r="B48" t="n">
-        <v>78973</v>
+        <v>57656</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5373,21 +5373,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5397,10 +5397,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>557156</v>
+        <v>557057</v>
       </c>
       <c r="R48" t="n">
-        <v>7227270</v>
+        <v>7227134</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5433,6 +5433,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack färsk</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5463,32 +5468,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126091113</v>
+        <v>126091142</v>
       </c>
       <c r="B49" t="n">
-        <v>57756</v>
+        <v>78977</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5498,10 +5503,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>556728</v>
+        <v>557156</v>
       </c>
       <c r="R49" t="n">
-        <v>7227079</v>
+        <v>7227270</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5564,27 +5569,27 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126091038</v>
+        <v>126091113</v>
       </c>
       <c r="B50" t="n">
-        <v>57652</v>
+        <v>57760</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5599,10 +5604,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>557057</v>
+        <v>556728</v>
       </c>
       <c r="R50" t="n">
-        <v>7227134</v>
+        <v>7227079</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5635,11 +5640,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack färsk</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5673,7 +5673,7 @@
         <v>126091059</v>
       </c>
       <c r="B51" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5779,10 +5779,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126091353</v>
+        <v>126091171</v>
       </c>
       <c r="B52" t="n">
-        <v>98366</v>
+        <v>80115</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5790,21 +5790,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5814,10 +5814,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>556926</v>
+        <v>557049</v>
       </c>
       <c r="R52" t="n">
-        <v>7227176</v>
+        <v>7227144</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5880,32 +5880,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126091171</v>
+        <v>126091037</v>
       </c>
       <c r="B53" t="n">
-        <v>80111</v>
+        <v>57656</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5915,10 +5915,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>557049</v>
+        <v>556702</v>
       </c>
       <c r="R53" t="n">
-        <v>7227144</v>
+        <v>7227082</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5951,6 +5951,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5981,32 +5986,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126091037</v>
+        <v>126091353</v>
       </c>
       <c r="B54" t="n">
-        <v>57652</v>
+        <v>98370</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6016,10 +6021,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>556702</v>
+        <v>556926</v>
       </c>
       <c r="R54" t="n">
-        <v>7227082</v>
+        <v>7227176</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6046,17 +6051,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6090,7 +6090,7 @@
         <v>126091026</v>
       </c>
       <c r="B55" t="n">
-        <v>91935</v>
+        <v>91939</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>126091161</v>
       </c>
       <c r="B56" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6297,7 +6297,7 @@
         <v>126091134</v>
       </c>
       <c r="B57" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>126091139</v>
       </c>
       <c r="B58" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6496,32 +6496,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126091091</v>
+        <v>126091082</v>
       </c>
       <c r="B59" t="n">
-        <v>79980</v>
+        <v>80081</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6531,10 +6531,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>557022</v>
+        <v>556947</v>
       </c>
       <c r="R59" t="n">
-        <v>7227286</v>
+        <v>7227303</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6597,10 +6597,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126091446</v>
+        <v>126091091</v>
       </c>
       <c r="B60" t="n">
-        <v>80111</v>
+        <v>79984</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6608,21 +6608,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6463</v>
+        <v>6456</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6632,10 +6632,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>556925</v>
+        <v>557022</v>
       </c>
       <c r="R60" t="n">
-        <v>7227179</v>
+        <v>7227286</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6662,12 +6662,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6698,32 +6698,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126091082</v>
+        <v>126091446</v>
       </c>
       <c r="B61" t="n">
-        <v>80077</v>
+        <v>80115</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>556947</v>
+        <v>556925</v>
       </c>
       <c r="R61" t="n">
-        <v>7227303</v>
+        <v>7227179</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6802,7 +6802,7 @@
         <v>126091054</v>
       </c>
       <c r="B62" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>126091057</v>
       </c>
       <c r="B63" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>126091116</v>
       </c>
       <c r="B64" t="n">
-        <v>57808</v>
+        <v>57812</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>126091056</v>
       </c>
       <c r="B65" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7203,10 +7203,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126091136</v>
+        <v>126091155</v>
       </c>
       <c r="B66" t="n">
-        <v>91256</v>
+        <v>78977</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7214,21 +7214,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7238,10 +7238,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>556803</v>
+        <v>557073</v>
       </c>
       <c r="R66" t="n">
-        <v>7227106</v>
+        <v>7227326</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7268,12 +7268,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7304,10 +7304,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126091155</v>
+        <v>126091136</v>
       </c>
       <c r="B67" t="n">
-        <v>78973</v>
+        <v>91260</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7315,21 +7315,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7339,10 +7339,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>557073</v>
+        <v>556803</v>
       </c>
       <c r="R67" t="n">
-        <v>7227326</v>
+        <v>7227106</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7369,12 +7369,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7408,7 +7408,7 @@
         <v>126091081</v>
       </c>
       <c r="B68" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7506,32 +7506,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126091046</v>
+        <v>126091154</v>
       </c>
       <c r="B69" t="n">
-        <v>80105</v>
+        <v>78977</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7541,10 +7541,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>556915</v>
+        <v>556904</v>
       </c>
       <c r="R69" t="n">
-        <v>7227293</v>
+        <v>7227312</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7577,6 +7577,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7607,10 +7612,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126091103</v>
+        <v>126091086</v>
       </c>
       <c r="B70" t="n">
-        <v>80076</v>
+        <v>80081</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7618,21 +7623,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7642,10 +7647,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>556737</v>
+        <v>556691</v>
       </c>
       <c r="R70" t="n">
-        <v>7227086</v>
+        <v>7227079</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7708,32 +7713,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126091154</v>
+        <v>126091046</v>
       </c>
       <c r="B71" t="n">
-        <v>78973</v>
+        <v>80109</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7743,10 +7748,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>556904</v>
+        <v>556915</v>
       </c>
       <c r="R71" t="n">
-        <v>7227312</v>
+        <v>7227293</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7779,11 +7784,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7814,10 +7814,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126091086</v>
+        <v>126091103</v>
       </c>
       <c r="B72" t="n">
-        <v>80077</v>
+        <v>80080</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7825,21 +7825,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7849,10 +7849,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>556691</v>
+        <v>556737</v>
       </c>
       <c r="R72" t="n">
-        <v>7227079</v>
+        <v>7227086</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>

--- a/artfynd/A 23758-2025 artfynd.xlsx
+++ b/artfynd/A 23758-2025 artfynd.xlsx
@@ -1897,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126091083</v>
+        <v>126091159</v>
       </c>
       <c r="B14" t="n">
-        <v>80081</v>
+        <v>78977</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,21 +1908,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>556975</v>
+        <v>557055</v>
       </c>
       <c r="R14" t="n">
-        <v>7227303</v>
+        <v>7227102</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1962,12 +1962,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1998,10 +1998,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126091159</v>
+        <v>126091083</v>
       </c>
       <c r="B15" t="n">
-        <v>78977</v>
+        <v>80081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2009,21 +2009,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2033,10 +2033,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>557055</v>
+        <v>556975</v>
       </c>
       <c r="R15" t="n">
-        <v>7227102</v>
+        <v>7227303</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2063,12 +2063,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -3523,32 +3523,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126091045</v>
+        <v>126091078</v>
       </c>
       <c r="B30" t="n">
-        <v>80109</v>
+        <v>80081</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3558,10 +3558,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>556904</v>
+        <v>556918</v>
       </c>
       <c r="R30" t="n">
-        <v>7227312</v>
+        <v>7227271</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3624,10 +3624,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126091078</v>
+        <v>126091133</v>
       </c>
       <c r="B31" t="n">
-        <v>80081</v>
+        <v>91260</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3635,21 +3635,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3659,10 +3659,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>556918</v>
+        <v>556729</v>
       </c>
       <c r="R31" t="n">
-        <v>7227271</v>
+        <v>7227082</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3689,12 +3689,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3725,32 +3725,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126091133</v>
+        <v>126091122</v>
       </c>
       <c r="B32" t="n">
-        <v>91260</v>
+        <v>91602</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>2063</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3760,10 +3760,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>556729</v>
+        <v>556726</v>
       </c>
       <c r="R32" t="n">
-        <v>7227082</v>
+        <v>7227064</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3826,32 +3826,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126091122</v>
+        <v>126091077</v>
       </c>
       <c r="B33" t="n">
-        <v>91602</v>
+        <v>80081</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2063</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>556726</v>
+        <v>556902</v>
       </c>
       <c r="R33" t="n">
-        <v>7227064</v>
+        <v>7227281</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3891,12 +3891,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3927,32 +3927,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126091077</v>
+        <v>126091045</v>
       </c>
       <c r="B34" t="n">
-        <v>80081</v>
+        <v>80109</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3962,10 +3962,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>556902</v>
+        <v>556904</v>
       </c>
       <c r="R34" t="n">
-        <v>7227281</v>
+        <v>7227312</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5670,10 +5670,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126091059</v>
+        <v>126091037</v>
       </c>
       <c r="B51" t="n">
-        <v>80081</v>
+        <v>57656</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5681,41 +5681,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>556914</v>
+        <v>556702</v>
       </c>
       <c r="R51" t="n">
-        <v>7227278</v>
+        <v>7227082</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5742,12 +5735,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5756,7 +5754,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5779,10 +5776,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126091171</v>
+        <v>126091353</v>
       </c>
       <c r="B52" t="n">
-        <v>80115</v>
+        <v>98370</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5790,21 +5787,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6463</v>
+        <v>221952</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5814,10 +5811,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>557049</v>
+        <v>556926</v>
       </c>
       <c r="R52" t="n">
-        <v>7227144</v>
+        <v>7227176</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5844,12 +5841,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5880,10 +5877,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126091037</v>
+        <v>126091059</v>
       </c>
       <c r="B53" t="n">
-        <v>57656</v>
+        <v>80081</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5891,34 +5888,41 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>556702</v>
+        <v>556914</v>
       </c>
       <c r="R53" t="n">
-        <v>7227082</v>
+        <v>7227278</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5945,17 +5949,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5964,6 +5963,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5986,10 +5986,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126091353</v>
+        <v>126091171</v>
       </c>
       <c r="B54" t="n">
-        <v>98370</v>
+        <v>80115</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5997,21 +5997,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6021,10 +6021,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>556926</v>
+        <v>557049</v>
       </c>
       <c r="R54" t="n">
-        <v>7227176</v>
+        <v>7227144</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6051,12 +6051,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6496,32 +6496,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126091082</v>
+        <v>126091054</v>
       </c>
       <c r="B59" t="n">
-        <v>80081</v>
+        <v>98370</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2081</v>
+        <v>221952</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6531,10 +6531,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>556947</v>
+        <v>556704</v>
       </c>
       <c r="R59" t="n">
-        <v>7227303</v>
+        <v>7227103</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6561,12 +6561,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6597,10 +6597,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126091091</v>
+        <v>126091057</v>
       </c>
       <c r="B60" t="n">
-        <v>79984</v>
+        <v>98370</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6608,21 +6608,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6456</v>
+        <v>221952</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6632,10 +6632,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>557022</v>
+        <v>557065</v>
       </c>
       <c r="R60" t="n">
-        <v>7227286</v>
+        <v>7227144</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6662,12 +6662,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6698,32 +6698,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126091446</v>
+        <v>126091082</v>
       </c>
       <c r="B61" t="n">
-        <v>80115</v>
+        <v>80081</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>556925</v>
+        <v>556947</v>
       </c>
       <c r="R61" t="n">
-        <v>7227179</v>
+        <v>7227303</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6799,10 +6799,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126091054</v>
+        <v>126091091</v>
       </c>
       <c r="B62" t="n">
-        <v>98370</v>
+        <v>79984</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6810,21 +6810,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221952</v>
+        <v>6456</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6834,10 +6834,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>556704</v>
+        <v>557022</v>
       </c>
       <c r="R62" t="n">
-        <v>7227103</v>
+        <v>7227286</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6864,12 +6864,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6900,10 +6900,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126091057</v>
+        <v>126091446</v>
       </c>
       <c r="B63" t="n">
-        <v>98370</v>
+        <v>80115</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6911,21 +6911,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6935,10 +6935,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>557065</v>
+        <v>556925</v>
       </c>
       <c r="R63" t="n">
-        <v>7227144</v>
+        <v>7227179</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6965,12 +6965,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7102,32 +7102,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126091056</v>
+        <v>126091155</v>
       </c>
       <c r="B65" t="n">
-        <v>98370</v>
+        <v>78977</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7137,10 +7137,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>557140</v>
+        <v>557073</v>
       </c>
       <c r="R65" t="n">
-        <v>7227297</v>
+        <v>7227326</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7167,12 +7167,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7203,10 +7203,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126091155</v>
+        <v>126091136</v>
       </c>
       <c r="B66" t="n">
-        <v>78977</v>
+        <v>91260</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7214,21 +7214,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7238,10 +7238,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>557073</v>
+        <v>556803</v>
       </c>
       <c r="R66" t="n">
-        <v>7227326</v>
+        <v>7227106</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7268,12 +7268,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7304,10 +7304,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126091136</v>
+        <v>126091081</v>
       </c>
       <c r="B67" t="n">
-        <v>91260</v>
+        <v>80081</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7315,21 +7315,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7339,10 +7339,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>556803</v>
+        <v>556946</v>
       </c>
       <c r="R67" t="n">
-        <v>7227106</v>
+        <v>7227279</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7369,12 +7369,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7405,32 +7405,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126091081</v>
+        <v>126091056</v>
       </c>
       <c r="B68" t="n">
-        <v>80081</v>
+        <v>98370</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2081</v>
+        <v>221952</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>556946</v>
+        <v>557140</v>
       </c>
       <c r="R68" t="n">
-        <v>7227279</v>
+        <v>7227297</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7470,12 +7470,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD68" t="b">

--- a/artfynd/A 23758-2025 artfynd.xlsx
+++ b/artfynd/A 23758-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126091092</v>
+        <v>126091099</v>
       </c>
       <c r="B2" t="n">
-        <v>79984</v>
+        <v>98256</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>220093</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556906</v>
+        <v>557073</v>
       </c>
       <c r="R2" t="n">
-        <v>7227086</v>
+        <v>7227326</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -754,6 +754,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -776,48 +777,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126091009</v>
+        <v>126091089</v>
       </c>
       <c r="B3" t="n">
-        <v>80116</v>
+        <v>80081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556917</v>
+        <v>557054</v>
       </c>
       <c r="R3" t="n">
-        <v>7227275</v>
+        <v>7227146</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -844,12 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -858,7 +856,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -881,45 +878,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126091030</v>
+        <v>126091009</v>
       </c>
       <c r="B4" t="n">
-        <v>57656</v>
+        <v>80116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>557050</v>
+        <v>556917</v>
       </c>
       <c r="R4" t="n">
-        <v>7227253</v>
+        <v>7227275</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,17 +954,13 @@
           <t>2025-06-18</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -987,10 +983,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126091099</v>
+        <v>126091092</v>
       </c>
       <c r="B5" t="n">
-        <v>98253</v>
+        <v>79984</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -998,21 +994,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220093</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1022,10 +1018,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>557073</v>
+        <v>556906</v>
       </c>
       <c r="R5" t="n">
-        <v>7227326</v>
+        <v>7227086</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1052,12 +1048,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1066,7 +1062,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1089,10 +1084,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126091089</v>
+        <v>126091030</v>
       </c>
       <c r="B6" t="n">
-        <v>80081</v>
+        <v>57656</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,21 +1095,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1124,10 +1119,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>557054</v>
+        <v>557050</v>
       </c>
       <c r="R6" t="n">
-        <v>7227146</v>
+        <v>7227253</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1154,12 +1149,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126091117</v>
+        <v>126091087</v>
       </c>
       <c r="B7" t="n">
-        <v>57812</v>
+        <v>80081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103022</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556827</v>
+        <v>556869</v>
       </c>
       <c r="R7" t="n">
-        <v>7227124</v>
+        <v>7227096</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,32 +1291,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126091087</v>
+        <v>126091170</v>
       </c>
       <c r="B8" t="n">
-        <v>80081</v>
+        <v>80115</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1326,10 +1326,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556869</v>
+        <v>556915</v>
       </c>
       <c r="R8" t="n">
-        <v>7227096</v>
+        <v>7227293</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1392,32 +1392,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126091170</v>
+        <v>126091117</v>
       </c>
       <c r="B9" t="n">
-        <v>80115</v>
+        <v>57812</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>103022</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556915</v>
+        <v>556827</v>
       </c>
       <c r="R9" t="n">
-        <v>7227293</v>
+        <v>7227124</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1493,32 +1493,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126091058</v>
+        <v>126091080</v>
       </c>
       <c r="B10" t="n">
-        <v>98370</v>
+        <v>80081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1528,10 +1528,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557128</v>
+        <v>556915</v>
       </c>
       <c r="R10" t="n">
-        <v>7227190</v>
+        <v>7227290</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1558,12 +1558,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1594,10 +1594,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126091080</v>
+        <v>126091138</v>
       </c>
       <c r="B11" t="n">
-        <v>80081</v>
+        <v>91260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1605,21 +1605,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>556915</v>
+        <v>557073</v>
       </c>
       <c r="R11" t="n">
-        <v>7227290</v>
+        <v>7227154</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1659,12 +1659,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1695,32 +1695,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126091138</v>
+        <v>126091058</v>
       </c>
       <c r="B12" t="n">
-        <v>91260</v>
+        <v>98373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>557073</v>
+        <v>557128</v>
       </c>
       <c r="R12" t="n">
-        <v>7227154</v>
+        <v>7227190</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1799,7 +1799,7 @@
         <v>126091055</v>
       </c>
       <c r="B13" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1998,32 +1998,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126091083</v>
+        <v>126091112</v>
       </c>
       <c r="B15" t="n">
-        <v>80081</v>
+        <v>57760</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2033,10 +2033,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>556975</v>
+        <v>556726</v>
       </c>
       <c r="R15" t="n">
-        <v>7227303</v>
+        <v>7227088</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2063,12 +2063,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2099,10 +2099,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126091118</v>
+        <v>126091083</v>
       </c>
       <c r="B16" t="n">
-        <v>57812</v>
+        <v>80081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2110,21 +2110,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103022</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2134,10 +2134,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>556859</v>
+        <v>556975</v>
       </c>
       <c r="R16" t="n">
-        <v>7227119</v>
+        <v>7227303</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2164,12 +2164,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2200,32 +2200,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126091112</v>
+        <v>126091118</v>
       </c>
       <c r="B17" t="n">
-        <v>57760</v>
+        <v>57812</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103031</v>
+        <v>103022</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>556726</v>
+        <v>556859</v>
       </c>
       <c r="R17" t="n">
-        <v>7227088</v>
+        <v>7227119</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2301,10 +2301,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126091156</v>
+        <v>126091079</v>
       </c>
       <c r="B18" t="n">
-        <v>78977</v>
+        <v>80081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2312,21 +2312,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2336,10 +2336,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>556815</v>
+        <v>556916</v>
       </c>
       <c r="R18" t="n">
-        <v>7227118</v>
+        <v>7227278</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2366,12 +2366,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2402,32 +2402,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126091047</v>
+        <v>126091022</v>
       </c>
       <c r="B19" t="n">
-        <v>80109</v>
+        <v>91242</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2437,10 +2437,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>556947</v>
+        <v>557054</v>
       </c>
       <c r="R19" t="n">
-        <v>7227277</v>
+        <v>7227356</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2503,7 +2503,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126091079</v>
+        <v>126091088</v>
       </c>
       <c r="B20" t="n">
         <v>80081</v>
@@ -2538,10 +2538,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>556916</v>
+        <v>557057</v>
       </c>
       <c r="R20" t="n">
-        <v>7227278</v>
+        <v>7227107</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2568,12 +2568,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2710,10 +2710,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126091088</v>
+        <v>126091156</v>
       </c>
       <c r="B22" t="n">
-        <v>80081</v>
+        <v>78977</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2721,21 +2721,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>557057</v>
+        <v>556815</v>
       </c>
       <c r="R22" t="n">
-        <v>7227107</v>
+        <v>7227118</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2811,32 +2811,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126091022</v>
+        <v>126091047</v>
       </c>
       <c r="B23" t="n">
-        <v>91242</v>
+        <v>80109</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2846,10 +2846,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>557054</v>
+        <v>556947</v>
       </c>
       <c r="R23" t="n">
-        <v>7227356</v>
+        <v>7227277</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3013,32 +3013,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126091048</v>
+        <v>126091096</v>
       </c>
       <c r="B25" t="n">
-        <v>80109</v>
+        <v>57656</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3048,10 +3048,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>556737</v>
+        <v>556986</v>
       </c>
       <c r="R25" t="n">
-        <v>7227086</v>
+        <v>7227133</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3084,6 +3084,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3114,32 +3119,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126091096</v>
+        <v>126091048</v>
       </c>
       <c r="B26" t="n">
-        <v>57656</v>
+        <v>80109</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3149,10 +3154,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>556986</v>
+        <v>556737</v>
       </c>
       <c r="R26" t="n">
-        <v>7227133</v>
+        <v>7227086</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3185,11 +3190,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3220,32 +3220,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126091021</v>
+        <v>126091094</v>
       </c>
       <c r="B27" t="n">
-        <v>91242</v>
+        <v>79984</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3255,10 +3255,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>557035</v>
+        <v>556900</v>
       </c>
       <c r="R27" t="n">
-        <v>7227275</v>
+        <v>7227075</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3285,12 +3285,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3321,32 +3321,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126091094</v>
+        <v>126091158</v>
       </c>
       <c r="B28" t="n">
-        <v>79984</v>
+        <v>78977</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>556900</v>
+        <v>556943</v>
       </c>
       <c r="R28" t="n">
-        <v>7227075</v>
+        <v>7227059</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3422,10 +3422,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126091158</v>
+        <v>126091021</v>
       </c>
       <c r="B29" t="n">
-        <v>78977</v>
+        <v>91242</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3433,21 +3433,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3457,10 +3457,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>556943</v>
+        <v>557035</v>
       </c>
       <c r="R29" t="n">
-        <v>7227059</v>
+        <v>7227275</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3487,12 +3487,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4031,7 +4031,7 @@
         <v>126091097</v>
       </c>
       <c r="B35" t="n">
-        <v>97233</v>
+        <v>97236</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4129,10 +4129,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126091032</v>
+        <v>126091131</v>
       </c>
       <c r="B36" t="n">
-        <v>57656</v>
+        <v>91260</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4140,21 +4140,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4164,10 +4164,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>557048</v>
+        <v>556707</v>
       </c>
       <c r="R36" t="n">
-        <v>7227240</v>
+        <v>7227095</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4194,17 +4194,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4235,10 +4230,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126091131</v>
+        <v>126091032</v>
       </c>
       <c r="B37" t="n">
-        <v>91260</v>
+        <v>57656</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4246,21 +4241,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4270,10 +4265,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>556707</v>
+        <v>557048</v>
       </c>
       <c r="R37" t="n">
-        <v>7227095</v>
+        <v>7227240</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4300,12 +4295,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4336,45 +4336,52 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126091108</v>
+        <v>126091060</v>
       </c>
       <c r="B38" t="n">
-        <v>80116</v>
+        <v>80081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>556916</v>
+        <v>556945</v>
       </c>
       <c r="R38" t="n">
-        <v>7227278</v>
+        <v>7227306</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4415,6 +4422,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4437,52 +4445,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126091060</v>
+        <v>126091108</v>
       </c>
       <c r="B39" t="n">
-        <v>80081</v>
+        <v>80116</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>556945</v>
+        <v>556916</v>
       </c>
       <c r="R39" t="n">
-        <v>7227306</v>
+        <v>7227278</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4523,7 +4524,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4647,10 +4647,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126091101</v>
+        <v>126091137</v>
       </c>
       <c r="B41" t="n">
-        <v>80080</v>
+        <v>91260</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4658,21 +4658,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4682,10 +4682,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>556918</v>
+        <v>557054</v>
       </c>
       <c r="R41" t="n">
-        <v>7227271</v>
+        <v>7227134</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4748,45 +4748,52 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126091050</v>
+        <v>126091061</v>
       </c>
       <c r="B42" t="n">
-        <v>80109</v>
+        <v>80081</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>556992</v>
+        <v>557049</v>
       </c>
       <c r="R42" t="n">
-        <v>7227120</v>
+        <v>7227144</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4827,6 +4834,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4950,32 +4958,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126091137</v>
+        <v>126091050</v>
       </c>
       <c r="B44" t="n">
-        <v>91260</v>
+        <v>80109</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4985,10 +4993,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>557054</v>
+        <v>556992</v>
       </c>
       <c r="R44" t="n">
-        <v>7227134</v>
+        <v>7227120</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5051,10 +5059,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126091061</v>
+        <v>126091101</v>
       </c>
       <c r="B45" t="n">
-        <v>80081</v>
+        <v>80080</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5062,41 +5070,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>557049</v>
+        <v>556918</v>
       </c>
       <c r="R45" t="n">
-        <v>7227144</v>
+        <v>7227271</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5123,12 +5124,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5137,7 +5138,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5362,10 +5362,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126091038</v>
+        <v>126091142</v>
       </c>
       <c r="B48" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5373,21 +5373,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5397,10 +5397,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>557057</v>
+        <v>557156</v>
       </c>
       <c r="R48" t="n">
-        <v>7227134</v>
+        <v>7227270</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5433,11 +5433,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack färsk</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5468,10 +5463,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126091142</v>
+        <v>126091038</v>
       </c>
       <c r="B49" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5479,21 +5474,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5503,10 +5498,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>557156</v>
+        <v>557057</v>
       </c>
       <c r="R49" t="n">
-        <v>7227270</v>
+        <v>7227134</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5539,6 +5534,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack färsk</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5779,7 +5779,7 @@
         <v>126091353</v>
       </c>
       <c r="B52" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6188,10 +6188,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126091161</v>
+        <v>126091134</v>
       </c>
       <c r="B56" t="n">
-        <v>78977</v>
+        <v>91260</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6199,21 +6199,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6223,10 +6223,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>557149</v>
+        <v>556726</v>
       </c>
       <c r="R56" t="n">
-        <v>7227169</v>
+        <v>7227062</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6259,11 +6259,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Fertil</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6294,7 +6289,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126091134</v>
+        <v>126091139</v>
       </c>
       <c r="B57" t="n">
         <v>91260</v>
@@ -6329,10 +6324,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>556726</v>
+        <v>557138</v>
       </c>
       <c r="R57" t="n">
-        <v>7227062</v>
+        <v>7227186</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6395,10 +6390,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126091139</v>
+        <v>126091161</v>
       </c>
       <c r="B58" t="n">
-        <v>91260</v>
+        <v>78977</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6406,21 +6401,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6430,10 +6425,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>557138</v>
+        <v>557149</v>
       </c>
       <c r="R58" t="n">
-        <v>7227186</v>
+        <v>7227169</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6466,6 +6461,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6496,10 +6496,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126091054</v>
+        <v>126091057</v>
       </c>
       <c r="B59" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6531,10 +6531,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>556704</v>
+        <v>557065</v>
       </c>
       <c r="R59" t="n">
-        <v>7227103</v>
+        <v>7227144</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6597,32 +6597,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126091057</v>
+        <v>126091082</v>
       </c>
       <c r="B60" t="n">
-        <v>98370</v>
+        <v>80081</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6632,10 +6632,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>557065</v>
+        <v>556947</v>
       </c>
       <c r="R60" t="n">
-        <v>7227144</v>
+        <v>7227303</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6662,12 +6662,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6698,32 +6698,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126091082</v>
+        <v>126091446</v>
       </c>
       <c r="B61" t="n">
-        <v>80081</v>
+        <v>80115</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>556947</v>
+        <v>556925</v>
       </c>
       <c r="R61" t="n">
-        <v>7227303</v>
+        <v>7227179</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6900,10 +6900,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126091446</v>
+        <v>126091054</v>
       </c>
       <c r="B63" t="n">
-        <v>80115</v>
+        <v>98373</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6911,21 +6911,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6463</v>
+        <v>221952</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6935,10 +6935,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>556925</v>
+        <v>556704</v>
       </c>
       <c r="R63" t="n">
-        <v>7227179</v>
+        <v>7227103</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6965,12 +6965,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7102,10 +7102,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126091155</v>
+        <v>126091136</v>
       </c>
       <c r="B65" t="n">
-        <v>78977</v>
+        <v>91260</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7113,21 +7113,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7137,10 +7137,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>557073</v>
+        <v>556803</v>
       </c>
       <c r="R65" t="n">
-        <v>7227326</v>
+        <v>7227106</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7167,12 +7167,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7203,10 +7203,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126091136</v>
+        <v>126091081</v>
       </c>
       <c r="B66" t="n">
-        <v>91260</v>
+        <v>80081</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7214,21 +7214,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7238,10 +7238,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>556803</v>
+        <v>556946</v>
       </c>
       <c r="R66" t="n">
-        <v>7227106</v>
+        <v>7227279</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7268,12 +7268,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7304,10 +7304,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126091081</v>
+        <v>126091155</v>
       </c>
       <c r="B67" t="n">
-        <v>80081</v>
+        <v>78977</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7315,21 +7315,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7339,10 +7339,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>556946</v>
+        <v>557073</v>
       </c>
       <c r="R67" t="n">
-        <v>7227279</v>
+        <v>7227326</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7408,7 +7408,7 @@
         <v>126091056</v>
       </c>
       <c r="B68" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7506,10 +7506,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126091154</v>
+        <v>126091086</v>
       </c>
       <c r="B69" t="n">
-        <v>78977</v>
+        <v>80081</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7517,21 +7517,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7541,10 +7541,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>556904</v>
+        <v>556691</v>
       </c>
       <c r="R69" t="n">
-        <v>7227312</v>
+        <v>7227079</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7571,17 +7571,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7612,32 +7607,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126091086</v>
+        <v>126091046</v>
       </c>
       <c r="B70" t="n">
-        <v>80081</v>
+        <v>80109</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7647,10 +7642,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>556691</v>
+        <v>556915</v>
       </c>
       <c r="R70" t="n">
-        <v>7227079</v>
+        <v>7227293</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7677,12 +7672,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7713,32 +7708,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126091046</v>
+        <v>126091103</v>
       </c>
       <c r="B71" t="n">
-        <v>80109</v>
+        <v>80080</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7748,10 +7743,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>556915</v>
+        <v>556737</v>
       </c>
       <c r="R71" t="n">
-        <v>7227293</v>
+        <v>7227086</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7778,12 +7773,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7814,10 +7809,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126091103</v>
+        <v>126091154</v>
       </c>
       <c r="B72" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7825,21 +7820,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7849,10 +7844,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>556737</v>
+        <v>556904</v>
       </c>
       <c r="R72" t="n">
-        <v>7227086</v>
+        <v>7227312</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7879,12 +7874,17 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD72" t="b">

--- a/artfynd/A 23758-2025 artfynd.xlsx
+++ b/artfynd/A 23758-2025 artfynd.xlsx
@@ -1190,32 +1190,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126091087</v>
+        <v>126091170</v>
       </c>
       <c r="B7" t="n">
-        <v>80081</v>
+        <v>80115</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556869</v>
+        <v>556915</v>
       </c>
       <c r="R7" t="n">
-        <v>7227096</v>
+        <v>7227293</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1291,32 +1291,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126091170</v>
+        <v>126091087</v>
       </c>
       <c r="B8" t="n">
-        <v>80115</v>
+        <v>80081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1326,10 +1326,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556915</v>
+        <v>556869</v>
       </c>
       <c r="R8" t="n">
-        <v>7227293</v>
+        <v>7227096</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1897,32 +1897,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126091159</v>
+        <v>126091112</v>
       </c>
       <c r="B14" t="n">
-        <v>78977</v>
+        <v>57760</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557055</v>
+        <v>556726</v>
       </c>
       <c r="R14" t="n">
-        <v>7227102</v>
+        <v>7227088</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1998,32 +1998,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126091112</v>
+        <v>126091118</v>
       </c>
       <c r="B15" t="n">
-        <v>57760</v>
+        <v>57812</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>103022</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2033,10 +2033,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>556726</v>
+        <v>556859</v>
       </c>
       <c r="R15" t="n">
-        <v>7227088</v>
+        <v>7227119</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2200,10 +2200,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126091118</v>
+        <v>126091159</v>
       </c>
       <c r="B17" t="n">
-        <v>57812</v>
+        <v>78977</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2211,21 +2211,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103022</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>556859</v>
+        <v>557055</v>
       </c>
       <c r="R17" t="n">
-        <v>7227119</v>
+        <v>7227102</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -4129,10 +4129,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126091131</v>
+        <v>126091032</v>
       </c>
       <c r="B36" t="n">
-        <v>91260</v>
+        <v>57656</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4140,21 +4140,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4164,10 +4164,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>556707</v>
+        <v>557048</v>
       </c>
       <c r="R36" t="n">
-        <v>7227095</v>
+        <v>7227240</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4194,12 +4194,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4230,10 +4235,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126091032</v>
+        <v>126091131</v>
       </c>
       <c r="B37" t="n">
-        <v>57656</v>
+        <v>91260</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4241,21 +4246,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4265,10 +4270,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>557048</v>
+        <v>556707</v>
       </c>
       <c r="R37" t="n">
-        <v>7227240</v>
+        <v>7227095</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4295,17 +4300,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5670,10 +5670,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126091037</v>
+        <v>126091059</v>
       </c>
       <c r="B51" t="n">
-        <v>57656</v>
+        <v>80081</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5681,34 +5681,41 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>556702</v>
+        <v>556914</v>
       </c>
       <c r="R51" t="n">
-        <v>7227082</v>
+        <v>7227278</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5735,17 +5742,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5754,6 +5756,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5776,32 +5779,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126091353</v>
+        <v>126091037</v>
       </c>
       <c r="B52" t="n">
-        <v>98373</v>
+        <v>57656</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5811,10 +5814,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>556926</v>
+        <v>556702</v>
       </c>
       <c r="R52" t="n">
-        <v>7227176</v>
+        <v>7227082</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5841,12 +5844,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5877,52 +5885,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126091059</v>
+        <v>126091171</v>
       </c>
       <c r="B53" t="n">
-        <v>80081</v>
+        <v>80115</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>556914</v>
+        <v>557049</v>
       </c>
       <c r="R53" t="n">
-        <v>7227278</v>
+        <v>7227144</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5949,12 +5950,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5963,7 +5964,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5986,10 +5986,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126091171</v>
+        <v>126091353</v>
       </c>
       <c r="B54" t="n">
-        <v>80115</v>
+        <v>98373</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5997,21 +5997,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6463</v>
+        <v>221952</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6021,10 +6021,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>557049</v>
+        <v>556926</v>
       </c>
       <c r="R54" t="n">
-        <v>7227144</v>
+        <v>7227176</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6051,12 +6051,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7102,10 +7102,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126091136</v>
+        <v>126091155</v>
       </c>
       <c r="B65" t="n">
-        <v>91260</v>
+        <v>78977</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7113,21 +7113,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7137,10 +7137,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>556803</v>
+        <v>557073</v>
       </c>
       <c r="R65" t="n">
-        <v>7227106</v>
+        <v>7227326</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7167,12 +7167,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7203,32 +7203,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126091081</v>
+        <v>126091056</v>
       </c>
       <c r="B66" t="n">
-        <v>80081</v>
+        <v>98373</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2081</v>
+        <v>221952</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7238,10 +7238,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>556946</v>
+        <v>557140</v>
       </c>
       <c r="R66" t="n">
-        <v>7227279</v>
+        <v>7227297</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7268,12 +7268,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7304,10 +7304,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126091155</v>
+        <v>126091136</v>
       </c>
       <c r="B67" t="n">
-        <v>78977</v>
+        <v>91260</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7315,21 +7315,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7339,10 +7339,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>557073</v>
+        <v>556803</v>
       </c>
       <c r="R67" t="n">
-        <v>7227326</v>
+        <v>7227106</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7369,12 +7369,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7405,32 +7405,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126091056</v>
+        <v>126091081</v>
       </c>
       <c r="B68" t="n">
-        <v>98373</v>
+        <v>80081</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>557140</v>
+        <v>556946</v>
       </c>
       <c r="R68" t="n">
-        <v>7227297</v>
+        <v>7227279</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7470,12 +7470,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7506,32 +7506,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126091086</v>
+        <v>126091046</v>
       </c>
       <c r="B69" t="n">
-        <v>80081</v>
+        <v>80109</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7541,10 +7541,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>556691</v>
+        <v>556915</v>
       </c>
       <c r="R69" t="n">
-        <v>7227079</v>
+        <v>7227293</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7571,12 +7571,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7607,32 +7607,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126091046</v>
+        <v>126091103</v>
       </c>
       <c r="B70" t="n">
-        <v>80109</v>
+        <v>80080</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7642,10 +7642,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>556915</v>
+        <v>556737</v>
       </c>
       <c r="R70" t="n">
-        <v>7227293</v>
+        <v>7227086</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7708,10 +7708,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126091103</v>
+        <v>126091154</v>
       </c>
       <c r="B71" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7719,21 +7719,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7743,10 +7743,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>556737</v>
+        <v>556904</v>
       </c>
       <c r="R71" t="n">
-        <v>7227086</v>
+        <v>7227312</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7773,12 +7773,17 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7809,10 +7814,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126091154</v>
+        <v>126091086</v>
       </c>
       <c r="B72" t="n">
-        <v>78977</v>
+        <v>80081</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7820,21 +7825,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7844,10 +7849,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>556904</v>
+        <v>556691</v>
       </c>
       <c r="R72" t="n">
-        <v>7227312</v>
+        <v>7227079</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7874,17 +7879,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD72" t="b">

--- a/artfynd/A 23758-2025 artfynd.xlsx
+++ b/artfynd/A 23758-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126091099</v>
+        <v>126091092</v>
       </c>
       <c r="B2" t="n">
-        <v>98256</v>
+        <v>79984</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220093</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>557073</v>
+        <v>556906</v>
       </c>
       <c r="R2" t="n">
-        <v>7227326</v>
+        <v>7227086</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -754,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,45 +776,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126091089</v>
+        <v>126091009</v>
       </c>
       <c r="B3" t="n">
-        <v>80081</v>
+        <v>80116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>557054</v>
+        <v>556917</v>
       </c>
       <c r="R3" t="n">
-        <v>7227146</v>
+        <v>7227275</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -842,12 +844,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -856,6 +858,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -878,48 +881,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126091009</v>
+        <v>126091089</v>
       </c>
       <c r="B4" t="n">
-        <v>80116</v>
+        <v>80081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556917</v>
+        <v>557054</v>
       </c>
       <c r="R4" t="n">
-        <v>7227275</v>
+        <v>7227146</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -946,12 +946,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -960,7 +960,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -983,32 +982,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126091092</v>
+        <v>126091030</v>
       </c>
       <c r="B5" t="n">
-        <v>79984</v>
+        <v>57656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1018,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556906</v>
+        <v>557050</v>
       </c>
       <c r="R5" t="n">
-        <v>7227086</v>
+        <v>7227253</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1048,12 +1047,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1084,32 +1088,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126091030</v>
+        <v>126091099</v>
       </c>
       <c r="B6" t="n">
-        <v>57656</v>
+        <v>98256</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1119,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>557050</v>
+        <v>557073</v>
       </c>
       <c r="R6" t="n">
-        <v>7227253</v>
+        <v>7227326</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1157,17 +1161,13 @@
           <t>2025-06-18</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126091087</v>
+        <v>126091117</v>
       </c>
       <c r="B8" t="n">
-        <v>80081</v>
+        <v>57812</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,21 +1302,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>103022</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1326,10 +1326,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556869</v>
+        <v>556827</v>
       </c>
       <c r="R8" t="n">
-        <v>7227096</v>
+        <v>7227124</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,10 +1392,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126091117</v>
+        <v>126091087</v>
       </c>
       <c r="B9" t="n">
-        <v>57812</v>
+        <v>80081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1403,21 +1403,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103022</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556827</v>
+        <v>556869</v>
       </c>
       <c r="R9" t="n">
-        <v>7227124</v>
+        <v>7227096</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1594,32 +1594,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126091138</v>
+        <v>126091058</v>
       </c>
       <c r="B11" t="n">
-        <v>91260</v>
+        <v>98373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557073</v>
+        <v>557128</v>
       </c>
       <c r="R11" t="n">
-        <v>7227154</v>
+        <v>7227190</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,32 +1695,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126091058</v>
+        <v>126091138</v>
       </c>
       <c r="B12" t="n">
-        <v>98373</v>
+        <v>91260</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>557128</v>
+        <v>557073</v>
       </c>
       <c r="R12" t="n">
-        <v>7227190</v>
+        <v>7227154</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1897,32 +1897,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126091112</v>
+        <v>126091159</v>
       </c>
       <c r="B14" t="n">
-        <v>57760</v>
+        <v>78977</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>556726</v>
+        <v>557055</v>
       </c>
       <c r="R14" t="n">
-        <v>7227088</v>
+        <v>7227102</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1998,10 +1998,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126091118</v>
+        <v>126091083</v>
       </c>
       <c r="B15" t="n">
-        <v>57812</v>
+        <v>80081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2009,21 +2009,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103022</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2033,10 +2033,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>556859</v>
+        <v>556975</v>
       </c>
       <c r="R15" t="n">
-        <v>7227119</v>
+        <v>7227303</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2063,12 +2063,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2099,32 +2099,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126091083</v>
+        <v>126091112</v>
       </c>
       <c r="B16" t="n">
-        <v>80081</v>
+        <v>57760</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>103031</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2134,10 +2134,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>556975</v>
+        <v>556726</v>
       </c>
       <c r="R16" t="n">
-        <v>7227303</v>
+        <v>7227088</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2164,12 +2164,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2200,10 +2200,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126091159</v>
+        <v>126091118</v>
       </c>
       <c r="B17" t="n">
-        <v>78977</v>
+        <v>57812</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2211,21 +2211,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>103022</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>557055</v>
+        <v>556859</v>
       </c>
       <c r="R17" t="n">
-        <v>7227102</v>
+        <v>7227119</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2301,10 +2301,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126091079</v>
+        <v>126091156</v>
       </c>
       <c r="B18" t="n">
-        <v>80081</v>
+        <v>78977</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2312,21 +2312,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2336,10 +2336,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>556916</v>
+        <v>556815</v>
       </c>
       <c r="R18" t="n">
-        <v>7227278</v>
+        <v>7227118</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2366,12 +2366,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2402,10 +2402,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126091022</v>
+        <v>126091157</v>
       </c>
       <c r="B19" t="n">
-        <v>91242</v>
+        <v>78977</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2413,21 +2413,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2437,10 +2437,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>557054</v>
+        <v>556844</v>
       </c>
       <c r="R19" t="n">
-        <v>7227356</v>
+        <v>7227129</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2467,12 +2467,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2503,32 +2508,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126091088</v>
+        <v>126091047</v>
       </c>
       <c r="B20" t="n">
-        <v>80081</v>
+        <v>80109</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2538,10 +2543,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>557057</v>
+        <v>556947</v>
       </c>
       <c r="R20" t="n">
-        <v>7227107</v>
+        <v>7227277</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2568,12 +2573,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2604,10 +2609,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126091157</v>
+        <v>126091088</v>
       </c>
       <c r="B21" t="n">
-        <v>78977</v>
+        <v>80081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2615,21 +2620,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2639,10 +2644,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>556844</v>
+        <v>557057</v>
       </c>
       <c r="R21" t="n">
-        <v>7227129</v>
+        <v>7227107</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2675,11 +2680,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Fertil</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2710,10 +2710,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126091156</v>
+        <v>126091022</v>
       </c>
       <c r="B22" t="n">
-        <v>78977</v>
+        <v>91242</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2721,21 +2721,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>556815</v>
+        <v>557054</v>
       </c>
       <c r="R22" t="n">
-        <v>7227118</v>
+        <v>7227356</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2811,32 +2811,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126091047</v>
+        <v>126091079</v>
       </c>
       <c r="B23" t="n">
-        <v>80109</v>
+        <v>80081</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2846,10 +2846,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>556947</v>
+        <v>556916</v>
       </c>
       <c r="R23" t="n">
-        <v>7227277</v>
+        <v>7227278</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3013,32 +3013,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126091096</v>
+        <v>126091048</v>
       </c>
       <c r="B25" t="n">
-        <v>57656</v>
+        <v>80109</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3048,10 +3048,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>556986</v>
+        <v>556737</v>
       </c>
       <c r="R25" t="n">
-        <v>7227133</v>
+        <v>7227086</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3084,11 +3084,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3119,32 +3114,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126091048</v>
+        <v>126091096</v>
       </c>
       <c r="B26" t="n">
-        <v>80109</v>
+        <v>57656</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3154,10 +3149,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>556737</v>
+        <v>556986</v>
       </c>
       <c r="R26" t="n">
-        <v>7227086</v>
+        <v>7227133</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3190,6 +3185,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3523,32 +3523,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126091078</v>
+        <v>126091045</v>
       </c>
       <c r="B30" t="n">
-        <v>80081</v>
+        <v>80109</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3558,10 +3558,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>556918</v>
+        <v>556904</v>
       </c>
       <c r="R30" t="n">
-        <v>7227271</v>
+        <v>7227312</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3725,32 +3725,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126091122</v>
+        <v>126091077</v>
       </c>
       <c r="B32" t="n">
-        <v>91602</v>
+        <v>80081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2063</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3760,10 +3760,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>556726</v>
+        <v>556902</v>
       </c>
       <c r="R32" t="n">
-        <v>7227064</v>
+        <v>7227281</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3790,12 +3790,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3826,32 +3826,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126091077</v>
+        <v>126091122</v>
       </c>
       <c r="B33" t="n">
-        <v>80081</v>
+        <v>91602</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>2063</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>556902</v>
+        <v>556726</v>
       </c>
       <c r="R33" t="n">
-        <v>7227281</v>
+        <v>7227064</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3891,12 +3891,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3927,32 +3927,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126091045</v>
+        <v>126091078</v>
       </c>
       <c r="B34" t="n">
-        <v>80109</v>
+        <v>80081</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3962,10 +3962,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>556904</v>
+        <v>556918</v>
       </c>
       <c r="R34" t="n">
-        <v>7227312</v>
+        <v>7227271</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4129,10 +4129,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126091032</v>
+        <v>126091131</v>
       </c>
       <c r="B36" t="n">
-        <v>57656</v>
+        <v>91260</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4140,21 +4140,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4164,10 +4164,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>557048</v>
+        <v>556707</v>
       </c>
       <c r="R36" t="n">
-        <v>7227240</v>
+        <v>7227095</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4194,17 +4194,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4235,10 +4230,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126091131</v>
+        <v>126091032</v>
       </c>
       <c r="B37" t="n">
-        <v>91260</v>
+        <v>57656</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4246,21 +4241,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4270,10 +4265,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>556707</v>
+        <v>557048</v>
       </c>
       <c r="R37" t="n">
-        <v>7227095</v>
+        <v>7227240</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4300,12 +4295,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4647,10 +4647,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126091137</v>
+        <v>126091011</v>
       </c>
       <c r="B41" t="n">
-        <v>91260</v>
+        <v>79009</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4658,21 +4658,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4682,10 +4682,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>557054</v>
+        <v>557066</v>
       </c>
       <c r="R41" t="n">
-        <v>7227134</v>
+        <v>7227351</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4748,10 +4748,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126091061</v>
+        <v>126091101</v>
       </c>
       <c r="B42" t="n">
-        <v>80081</v>
+        <v>80080</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4759,41 +4759,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>557049</v>
+        <v>556918</v>
       </c>
       <c r="R42" t="n">
-        <v>7227144</v>
+        <v>7227271</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4820,12 +4813,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4834,7 +4827,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4857,32 +4849,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126091111</v>
+        <v>126091137</v>
       </c>
       <c r="B43" t="n">
-        <v>80116</v>
+        <v>91260</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4892,10 +4884,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>557064</v>
+        <v>557054</v>
       </c>
       <c r="R43" t="n">
-        <v>7227147</v>
+        <v>7227134</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5059,32 +5051,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126091101</v>
+        <v>126091111</v>
       </c>
       <c r="B45" t="n">
-        <v>80080</v>
+        <v>80116</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5094,10 +5086,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>556918</v>
+        <v>557064</v>
       </c>
       <c r="R45" t="n">
-        <v>7227271</v>
+        <v>7227147</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5124,12 +5116,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5261,10 +5253,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126091011</v>
+        <v>126091061</v>
       </c>
       <c r="B47" t="n">
-        <v>79009</v>
+        <v>80081</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5272,34 +5264,41 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>557066</v>
+        <v>557049</v>
       </c>
       <c r="R47" t="n">
-        <v>7227351</v>
+        <v>7227144</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5326,12 +5325,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5340,6 +5339,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5463,27 +5463,27 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126091038</v>
+        <v>126091113</v>
       </c>
       <c r="B49" t="n">
-        <v>57656</v>
+        <v>57760</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5498,10 +5498,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>557057</v>
+        <v>556728</v>
       </c>
       <c r="R49" t="n">
-        <v>7227134</v>
+        <v>7227079</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5534,11 +5534,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack färsk</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5569,27 +5564,27 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126091113</v>
+        <v>126091038</v>
       </c>
       <c r="B50" t="n">
-        <v>57760</v>
+        <v>57656</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5604,10 +5599,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>556728</v>
+        <v>557057</v>
       </c>
       <c r="R50" t="n">
-        <v>7227079</v>
+        <v>7227134</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5640,6 +5635,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack färsk</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5670,52 +5670,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126091059</v>
+        <v>126091171</v>
       </c>
       <c r="B51" t="n">
-        <v>80081</v>
+        <v>80115</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>556914</v>
+        <v>557049</v>
       </c>
       <c r="R51" t="n">
-        <v>7227278</v>
+        <v>7227144</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5742,12 +5735,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5756,7 +5749,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5779,10 +5771,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126091037</v>
+        <v>126091059</v>
       </c>
       <c r="B52" t="n">
-        <v>57656</v>
+        <v>80081</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5790,34 +5782,41 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>556702</v>
+        <v>556914</v>
       </c>
       <c r="R52" t="n">
-        <v>7227082</v>
+        <v>7227278</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5844,17 +5843,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5863,6 +5857,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5885,32 +5880,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126091171</v>
+        <v>126091037</v>
       </c>
       <c r="B53" t="n">
-        <v>80115</v>
+        <v>57656</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5920,10 +5915,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>557049</v>
+        <v>556702</v>
       </c>
       <c r="R53" t="n">
-        <v>7227144</v>
+        <v>7227082</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5956,6 +5951,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6188,10 +6188,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126091134</v>
+        <v>126091161</v>
       </c>
       <c r="B56" t="n">
-        <v>91260</v>
+        <v>78977</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6199,21 +6199,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6223,10 +6223,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>556726</v>
+        <v>557149</v>
       </c>
       <c r="R56" t="n">
-        <v>7227062</v>
+        <v>7227169</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6259,6 +6259,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6289,7 +6294,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126091139</v>
+        <v>126091134</v>
       </c>
       <c r="B57" t="n">
         <v>91260</v>
@@ -6324,10 +6329,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>557138</v>
+        <v>556726</v>
       </c>
       <c r="R57" t="n">
-        <v>7227186</v>
+        <v>7227062</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6390,10 +6395,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126091161</v>
+        <v>126091139</v>
       </c>
       <c r="B58" t="n">
-        <v>78977</v>
+        <v>91260</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6401,21 +6406,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6425,10 +6430,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>557149</v>
+        <v>557138</v>
       </c>
       <c r="R58" t="n">
-        <v>7227169</v>
+        <v>7227186</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6461,11 +6466,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Fertil</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6496,7 +6496,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126091057</v>
+        <v>126091054</v>
       </c>
       <c r="B59" t="n">
         <v>98373</v>
@@ -6531,10 +6531,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>557065</v>
+        <v>556704</v>
       </c>
       <c r="R59" t="n">
-        <v>7227144</v>
+        <v>7227103</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6597,32 +6597,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126091082</v>
+        <v>126091057</v>
       </c>
       <c r="B60" t="n">
-        <v>80081</v>
+        <v>98373</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>221952</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6632,10 +6632,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>556947</v>
+        <v>557065</v>
       </c>
       <c r="R60" t="n">
-        <v>7227303</v>
+        <v>7227144</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6662,12 +6662,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6799,32 +6799,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126091091</v>
+        <v>126091082</v>
       </c>
       <c r="B62" t="n">
-        <v>79984</v>
+        <v>80081</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6834,10 +6834,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>557022</v>
+        <v>556947</v>
       </c>
       <c r="R62" t="n">
-        <v>7227286</v>
+        <v>7227303</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6900,10 +6900,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126091054</v>
+        <v>126091091</v>
       </c>
       <c r="B63" t="n">
-        <v>98373</v>
+        <v>79984</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6911,21 +6911,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221952</v>
+        <v>6456</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6935,10 +6935,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>556704</v>
+        <v>557022</v>
       </c>
       <c r="R63" t="n">
-        <v>7227103</v>
+        <v>7227286</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6965,12 +6965,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7102,32 +7102,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126091155</v>
+        <v>126091056</v>
       </c>
       <c r="B65" t="n">
-        <v>78977</v>
+        <v>98373</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7137,10 +7137,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>557073</v>
+        <v>557140</v>
       </c>
       <c r="R65" t="n">
-        <v>7227326</v>
+        <v>7227297</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7167,12 +7167,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7203,32 +7203,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126091056</v>
+        <v>126091136</v>
       </c>
       <c r="B66" t="n">
-        <v>98373</v>
+        <v>91260</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7238,10 +7238,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>557140</v>
+        <v>556803</v>
       </c>
       <c r="R66" t="n">
-        <v>7227297</v>
+        <v>7227106</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7304,10 +7304,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126091136</v>
+        <v>126091155</v>
       </c>
       <c r="B67" t="n">
-        <v>91260</v>
+        <v>78977</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7315,21 +7315,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7339,10 +7339,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>556803</v>
+        <v>557073</v>
       </c>
       <c r="R67" t="n">
-        <v>7227106</v>
+        <v>7227326</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7369,12 +7369,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 23758-2025 artfynd.xlsx
+++ b/artfynd/A 23758-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126091092</v>
+        <v>126091030</v>
       </c>
       <c r="B2" t="n">
-        <v>79984</v>
+        <v>57656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556906</v>
+        <v>557050</v>
       </c>
       <c r="R2" t="n">
-        <v>7227086</v>
+        <v>7227253</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126091009</v>
+        <v>126091099</v>
       </c>
       <c r="B3" t="n">
-        <v>80116</v>
+        <v>98256</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,37 +792,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>220093</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556917</v>
+        <v>557073</v>
       </c>
       <c r="R3" t="n">
-        <v>7227275</v>
+        <v>7227326</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,32 +883,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126091089</v>
+        <v>126091092</v>
       </c>
       <c r="B4" t="n">
-        <v>80081</v>
+        <v>79984</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -916,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>557054</v>
+        <v>556906</v>
       </c>
       <c r="R4" t="n">
-        <v>7227146</v>
+        <v>7227086</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,45 +984,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126091030</v>
+        <v>126091009</v>
       </c>
       <c r="B5" t="n">
-        <v>57656</v>
+        <v>80116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>557050</v>
+        <v>556917</v>
       </c>
       <c r="R5" t="n">
-        <v>7227253</v>
+        <v>7227275</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1055,17 +1060,13 @@
           <t>2025-06-18</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1088,32 +1089,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126091099</v>
+        <v>126091089</v>
       </c>
       <c r="B6" t="n">
-        <v>98256</v>
+        <v>80081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220093</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>557073</v>
+        <v>557054</v>
       </c>
       <c r="R6" t="n">
-        <v>7227326</v>
+        <v>7227146</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1153,12 +1154,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1167,7 +1168,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126091117</v>
+        <v>126091087</v>
       </c>
       <c r="B8" t="n">
-        <v>57812</v>
+        <v>80081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,21 +1302,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103022</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1326,10 +1326,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556827</v>
+        <v>556869</v>
       </c>
       <c r="R8" t="n">
-        <v>7227124</v>
+        <v>7227096</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,10 +1392,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126091087</v>
+        <v>126091117</v>
       </c>
       <c r="B9" t="n">
-        <v>80081</v>
+        <v>57812</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1403,21 +1403,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>103022</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556869</v>
+        <v>556827</v>
       </c>
       <c r="R9" t="n">
-        <v>7227096</v>
+        <v>7227124</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -4336,52 +4336,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126091060</v>
+        <v>126091108</v>
       </c>
       <c r="B38" t="n">
-        <v>80081</v>
+        <v>80116</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>556945</v>
+        <v>556916</v>
       </c>
       <c r="R38" t="n">
-        <v>7227306</v>
+        <v>7227278</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4422,7 +4415,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4445,7 +4437,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126091108</v>
+        <v>126091110</v>
       </c>
       <c r="B39" t="n">
         <v>80116</v>
@@ -4480,10 +4472,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>556916</v>
+        <v>557049</v>
       </c>
       <c r="R39" t="n">
-        <v>7227278</v>
+        <v>7227144</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4510,12 +4502,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4546,45 +4538,52 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126091110</v>
+        <v>126091060</v>
       </c>
       <c r="B40" t="n">
-        <v>80116</v>
+        <v>80081</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>557049</v>
+        <v>556945</v>
       </c>
       <c r="R40" t="n">
-        <v>7227144</v>
+        <v>7227306</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4611,12 +4610,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4625,6 +4624,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4647,10 +4647,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126091011</v>
+        <v>126091101</v>
       </c>
       <c r="B41" t="n">
-        <v>79009</v>
+        <v>80080</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4658,21 +4658,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4682,10 +4682,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>557066</v>
+        <v>556918</v>
       </c>
       <c r="R41" t="n">
-        <v>7227351</v>
+        <v>7227271</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4748,10 +4748,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126091101</v>
+        <v>126091137</v>
       </c>
       <c r="B42" t="n">
-        <v>80080</v>
+        <v>91260</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4759,21 +4759,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>556918</v>
+        <v>557054</v>
       </c>
       <c r="R42" t="n">
-        <v>7227271</v>
+        <v>7227134</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4813,12 +4813,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4849,32 +4849,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126091137</v>
+        <v>126091050</v>
       </c>
       <c r="B43" t="n">
-        <v>91260</v>
+        <v>80109</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>557054</v>
+        <v>556992</v>
       </c>
       <c r="R43" t="n">
-        <v>7227134</v>
+        <v>7227120</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4950,10 +4950,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126091050</v>
+        <v>126091111</v>
       </c>
       <c r="B44" t="n">
-        <v>80109</v>
+        <v>80116</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4961,21 +4961,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4985,10 +4985,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>556992</v>
+        <v>557064</v>
       </c>
       <c r="R44" t="n">
-        <v>7227120</v>
+        <v>7227147</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5051,32 +5051,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126091111</v>
+        <v>126091025</v>
       </c>
       <c r="B45" t="n">
-        <v>80116</v>
+        <v>91242</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5086,10 +5086,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>557064</v>
+        <v>556986</v>
       </c>
       <c r="R45" t="n">
-        <v>7227147</v>
+        <v>7227133</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5152,10 +5152,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126091025</v>
+        <v>126091061</v>
       </c>
       <c r="B46" t="n">
-        <v>91242</v>
+        <v>80081</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5163,34 +5163,41 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>556986</v>
+        <v>557049</v>
       </c>
       <c r="R46" t="n">
-        <v>7227133</v>
+        <v>7227144</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5231,6 +5238,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5253,10 +5261,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126091061</v>
+        <v>126091011</v>
       </c>
       <c r="B47" t="n">
-        <v>80081</v>
+        <v>79009</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5264,41 +5272,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>557049</v>
+        <v>557066</v>
       </c>
       <c r="R47" t="n">
-        <v>7227144</v>
+        <v>7227351</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5325,12 +5326,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5339,7 +5340,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5463,27 +5463,27 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126091113</v>
+        <v>126091038</v>
       </c>
       <c r="B49" t="n">
-        <v>57760</v>
+        <v>57656</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5498,10 +5498,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>556728</v>
+        <v>557057</v>
       </c>
       <c r="R49" t="n">
-        <v>7227079</v>
+        <v>7227134</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5534,6 +5534,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack färsk</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5564,27 +5569,27 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126091038</v>
+        <v>126091113</v>
       </c>
       <c r="B50" t="n">
-        <v>57656</v>
+        <v>57760</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5599,10 +5604,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>557057</v>
+        <v>556728</v>
       </c>
       <c r="R50" t="n">
-        <v>7227134</v>
+        <v>7227079</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5635,11 +5640,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack färsk</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6087,32 +6087,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126091026</v>
+        <v>126091161</v>
       </c>
       <c r="B55" t="n">
-        <v>91939</v>
+        <v>78977</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6122,10 +6122,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>556711</v>
+        <v>557149</v>
       </c>
       <c r="R55" t="n">
-        <v>7227080</v>
+        <v>7227169</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6158,6 +6158,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6188,10 +6193,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126091161</v>
+        <v>126091134</v>
       </c>
       <c r="B56" t="n">
-        <v>78977</v>
+        <v>91260</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6199,21 +6204,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6223,10 +6228,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>557149</v>
+        <v>556726</v>
       </c>
       <c r="R56" t="n">
-        <v>7227169</v>
+        <v>7227062</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6259,11 +6264,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Fertil</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6294,7 +6294,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126091134</v>
+        <v>126091139</v>
       </c>
       <c r="B57" t="n">
         <v>91260</v>
@@ -6329,10 +6329,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>556726</v>
+        <v>557138</v>
       </c>
       <c r="R57" t="n">
-        <v>7227062</v>
+        <v>7227186</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6395,32 +6395,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126091139</v>
+        <v>126091026</v>
       </c>
       <c r="B58" t="n">
-        <v>91260</v>
+        <v>91939</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6430,10 +6430,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>557138</v>
+        <v>556711</v>
       </c>
       <c r="R58" t="n">
-        <v>7227186</v>
+        <v>7227080</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6496,10 +6496,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126091054</v>
+        <v>126091091</v>
       </c>
       <c r="B59" t="n">
-        <v>98373</v>
+        <v>79984</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6507,21 +6507,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221952</v>
+        <v>6456</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6531,10 +6531,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>556704</v>
+        <v>557022</v>
       </c>
       <c r="R59" t="n">
-        <v>7227103</v>
+        <v>7227286</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6561,12 +6561,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6597,10 +6597,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126091057</v>
+        <v>126091446</v>
       </c>
       <c r="B60" t="n">
-        <v>98373</v>
+        <v>80115</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6608,21 +6608,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6632,10 +6632,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>557065</v>
+        <v>556925</v>
       </c>
       <c r="R60" t="n">
-        <v>7227144</v>
+        <v>7227179</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6662,12 +6662,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6698,10 +6698,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126091446</v>
+        <v>126091054</v>
       </c>
       <c r="B61" t="n">
-        <v>80115</v>
+        <v>98373</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6709,21 +6709,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6463</v>
+        <v>221952</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>556925</v>
+        <v>556704</v>
       </c>
       <c r="R61" t="n">
-        <v>7227179</v>
+        <v>7227103</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6799,32 +6799,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126091082</v>
+        <v>126091057</v>
       </c>
       <c r="B62" t="n">
-        <v>80081</v>
+        <v>98373</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2081</v>
+        <v>221952</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6834,10 +6834,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>556947</v>
+        <v>557065</v>
       </c>
       <c r="R62" t="n">
-        <v>7227303</v>
+        <v>7227144</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6864,12 +6864,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6900,32 +6900,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126091091</v>
+        <v>126091082</v>
       </c>
       <c r="B63" t="n">
-        <v>79984</v>
+        <v>80081</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6935,10 +6935,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>557022</v>
+        <v>556947</v>
       </c>
       <c r="R63" t="n">
-        <v>7227286</v>
+        <v>7227303</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>

--- a/artfynd/A 23758-2025 artfynd.xlsx
+++ b/artfynd/A 23758-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126091030</v>
+        <v>126091092</v>
       </c>
       <c r="B2" t="n">
-        <v>57656</v>
+        <v>79987</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>557050</v>
+        <v>556906</v>
       </c>
       <c r="R2" t="n">
-        <v>7227253</v>
+        <v>7227086</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126091099</v>
+        <v>126091089</v>
       </c>
       <c r="B3" t="n">
-        <v>98256</v>
+        <v>80084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220093</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -816,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>557073</v>
+        <v>557054</v>
       </c>
       <c r="R3" t="n">
-        <v>7227326</v>
+        <v>7227146</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -846,12 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -860,7 +855,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -883,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126091092</v>
+        <v>126091009</v>
       </c>
       <c r="B4" t="n">
-        <v>79984</v>
+        <v>80119</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -894,34 +888,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>6464</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556906</v>
+        <v>556917</v>
       </c>
       <c r="R4" t="n">
-        <v>7227086</v>
+        <v>7227275</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,12 +945,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -962,6 +959,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -984,48 +982,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126091009</v>
+        <v>126091030</v>
       </c>
       <c r="B5" t="n">
-        <v>80116</v>
+        <v>57657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556917</v>
+        <v>557050</v>
       </c>
       <c r="R5" t="n">
-        <v>7227275</v>
+        <v>7227253</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1060,13 +1055,17 @@
           <t>2025-06-18</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1089,32 +1088,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126091089</v>
+        <v>126091099</v>
       </c>
       <c r="B6" t="n">
-        <v>80081</v>
+        <v>98265</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>220093</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1124,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>557054</v>
+        <v>557073</v>
       </c>
       <c r="R6" t="n">
-        <v>7227146</v>
+        <v>7227326</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1154,12 +1153,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1168,6 +1167,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1193,7 +1193,7 @@
         <v>126091170</v>
       </c>
       <c r="B7" t="n">
-        <v>80115</v>
+        <v>80118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>126091087</v>
       </c>
       <c r="B8" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>126091117</v>
       </c>
       <c r="B9" t="n">
-        <v>57812</v>
+        <v>57813</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,32 +1493,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126091080</v>
+        <v>126091058</v>
       </c>
       <c r="B10" t="n">
-        <v>80081</v>
+        <v>98382</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1528,10 +1528,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>556915</v>
+        <v>557128</v>
       </c>
       <c r="R10" t="n">
-        <v>7227290</v>
+        <v>7227190</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1558,12 +1558,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1594,32 +1594,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126091058</v>
+        <v>126091080</v>
       </c>
       <c r="B11" t="n">
-        <v>98373</v>
+        <v>80084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557128</v>
+        <v>556915</v>
       </c>
       <c r="R11" t="n">
-        <v>7227190</v>
+        <v>7227290</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1659,12 +1659,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1698,7 +1698,7 @@
         <v>126091138</v>
       </c>
       <c r="B12" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>126091055</v>
       </c>
       <c r="B13" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>126091159</v>
       </c>
       <c r="B14" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>126091083</v>
       </c>
       <c r="B15" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2099,32 +2099,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126091112</v>
+        <v>126091118</v>
       </c>
       <c r="B16" t="n">
-        <v>57760</v>
+        <v>57813</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103031</v>
+        <v>103022</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2134,10 +2134,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>556726</v>
+        <v>556859</v>
       </c>
       <c r="R16" t="n">
-        <v>7227088</v>
+        <v>7227119</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2200,32 +2200,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126091118</v>
+        <v>126091112</v>
       </c>
       <c r="B17" t="n">
-        <v>57812</v>
+        <v>57761</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103022</v>
+        <v>103031</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>556859</v>
+        <v>556726</v>
       </c>
       <c r="R17" t="n">
-        <v>7227119</v>
+        <v>7227088</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2301,10 +2301,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126091156</v>
+        <v>126091022</v>
       </c>
       <c r="B18" t="n">
-        <v>78977</v>
+        <v>91245</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2312,21 +2312,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2336,10 +2336,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>556815</v>
+        <v>557054</v>
       </c>
       <c r="R18" t="n">
-        <v>7227118</v>
+        <v>7227356</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2366,12 +2366,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2402,10 +2402,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126091157</v>
+        <v>126091156</v>
       </c>
       <c r="B19" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2437,10 +2437,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>556844</v>
+        <v>556815</v>
       </c>
       <c r="R19" t="n">
-        <v>7227129</v>
+        <v>7227118</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2473,11 +2473,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Fertil</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2508,32 +2503,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126091047</v>
+        <v>126091079</v>
       </c>
       <c r="B20" t="n">
-        <v>80109</v>
+        <v>80084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2543,10 +2538,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>556947</v>
+        <v>556916</v>
       </c>
       <c r="R20" t="n">
-        <v>7227277</v>
+        <v>7227278</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2609,10 +2604,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126091088</v>
+        <v>126091157</v>
       </c>
       <c r="B21" t="n">
-        <v>80081</v>
+        <v>78980</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2620,21 +2615,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2644,10 +2639,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>557057</v>
+        <v>556844</v>
       </c>
       <c r="R21" t="n">
-        <v>7227107</v>
+        <v>7227129</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2680,6 +2675,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2710,10 +2710,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126091022</v>
+        <v>126091088</v>
       </c>
       <c r="B22" t="n">
-        <v>91242</v>
+        <v>80084</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2721,21 +2721,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>557054</v>
+        <v>557057</v>
       </c>
       <c r="R22" t="n">
-        <v>7227356</v>
+        <v>7227107</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2811,32 +2811,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126091079</v>
+        <v>126091047</v>
       </c>
       <c r="B23" t="n">
-        <v>80081</v>
+        <v>80112</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2846,10 +2846,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>556916</v>
+        <v>556947</v>
       </c>
       <c r="R23" t="n">
-        <v>7227278</v>
+        <v>7227277</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2915,7 +2915,7 @@
         <v>126091109</v>
       </c>
       <c r="B24" t="n">
-        <v>80116</v>
+        <v>80119</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>126091048</v>
       </c>
       <c r="B25" t="n">
-        <v>80109</v>
+        <v>80112</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>126091096</v>
       </c>
       <c r="B26" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>126091094</v>
       </c>
       <c r="B27" t="n">
-        <v>79984</v>
+        <v>79987</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>126091158</v>
       </c>
       <c r="B28" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>126091021</v>
       </c>
       <c r="B29" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3523,10 +3523,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126091045</v>
+        <v>126091097</v>
       </c>
       <c r="B30" t="n">
-        <v>80109</v>
+        <v>97245</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3534,21 +3534,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>221941</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3558,10 +3558,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>556904</v>
+        <v>557160</v>
       </c>
       <c r="R30" t="n">
-        <v>7227312</v>
+        <v>7227183</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3588,12 +3588,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3624,32 +3624,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126091133</v>
+        <v>126091045</v>
       </c>
       <c r="B31" t="n">
-        <v>91260</v>
+        <v>80112</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3659,10 +3659,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>556729</v>
+        <v>556904</v>
       </c>
       <c r="R31" t="n">
-        <v>7227082</v>
+        <v>7227312</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3689,12 +3689,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3725,10 +3725,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126091077</v>
+        <v>126091078</v>
       </c>
       <c r="B32" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3760,10 +3760,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>556902</v>
+        <v>556918</v>
       </c>
       <c r="R32" t="n">
-        <v>7227281</v>
+        <v>7227271</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3826,32 +3826,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126091122</v>
+        <v>126091133</v>
       </c>
       <c r="B33" t="n">
-        <v>91602</v>
+        <v>91263</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2063</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>556726</v>
+        <v>556729</v>
       </c>
       <c r="R33" t="n">
-        <v>7227064</v>
+        <v>7227082</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3927,32 +3927,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126091078</v>
+        <v>126091122</v>
       </c>
       <c r="B34" t="n">
-        <v>80081</v>
+        <v>91605</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>2063</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3962,10 +3962,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>556918</v>
+        <v>556726</v>
       </c>
       <c r="R34" t="n">
-        <v>7227271</v>
+        <v>7227064</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3992,12 +3992,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4028,32 +4028,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126091097</v>
+        <v>126091077</v>
       </c>
       <c r="B35" t="n">
-        <v>97236</v>
+        <v>80084</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221941</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4063,10 +4063,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>557160</v>
+        <v>556902</v>
       </c>
       <c r="R35" t="n">
-        <v>7227183</v>
+        <v>7227281</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4093,12 +4093,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4129,10 +4129,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126091131</v>
+        <v>126091032</v>
       </c>
       <c r="B36" t="n">
-        <v>91260</v>
+        <v>57657</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4140,21 +4140,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4164,10 +4164,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>556707</v>
+        <v>557048</v>
       </c>
       <c r="R36" t="n">
-        <v>7227095</v>
+        <v>7227240</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4194,12 +4194,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4230,10 +4235,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126091032</v>
+        <v>126091131</v>
       </c>
       <c r="B37" t="n">
-        <v>57656</v>
+        <v>91263</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4241,21 +4246,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4265,10 +4270,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>557048</v>
+        <v>556707</v>
       </c>
       <c r="R37" t="n">
-        <v>7227240</v>
+        <v>7227095</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4295,17 +4300,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4336,45 +4336,52 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126091108</v>
+        <v>126091060</v>
       </c>
       <c r="B38" t="n">
-        <v>80116</v>
+        <v>80084</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>556916</v>
+        <v>556945</v>
       </c>
       <c r="R38" t="n">
-        <v>7227278</v>
+        <v>7227306</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4415,6 +4422,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4437,10 +4445,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126091110</v>
+        <v>126091108</v>
       </c>
       <c r="B39" t="n">
-        <v>80116</v>
+        <v>80119</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4472,10 +4480,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>557049</v>
+        <v>556916</v>
       </c>
       <c r="R39" t="n">
-        <v>7227144</v>
+        <v>7227278</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4502,12 +4510,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4538,52 +4546,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126091060</v>
+        <v>126091110</v>
       </c>
       <c r="B40" t="n">
-        <v>80081</v>
+        <v>80119</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>556945</v>
+        <v>557049</v>
       </c>
       <c r="R40" t="n">
-        <v>7227306</v>
+        <v>7227144</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4610,12 +4611,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4624,7 +4625,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4647,10 +4647,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126091101</v>
+        <v>126091025</v>
       </c>
       <c r="B41" t="n">
-        <v>80080</v>
+        <v>91245</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4658,21 +4658,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4682,10 +4682,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>556918</v>
+        <v>556986</v>
       </c>
       <c r="R41" t="n">
-        <v>7227271</v>
+        <v>7227133</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4748,10 +4748,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126091137</v>
+        <v>126091011</v>
       </c>
       <c r="B42" t="n">
-        <v>91260</v>
+        <v>79012</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4759,21 +4759,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>185</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>557054</v>
+        <v>557066</v>
       </c>
       <c r="R42" t="n">
-        <v>7227134</v>
+        <v>7227351</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4813,12 +4813,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4849,32 +4849,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126091050</v>
+        <v>126091101</v>
       </c>
       <c r="B43" t="n">
-        <v>80109</v>
+        <v>80083</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>556992</v>
+        <v>556918</v>
       </c>
       <c r="R43" t="n">
-        <v>7227120</v>
+        <v>7227271</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4914,12 +4914,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4950,32 +4950,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126091111</v>
+        <v>126091137</v>
       </c>
       <c r="B44" t="n">
-        <v>80116</v>
+        <v>91263</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4985,10 +4985,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>557064</v>
+        <v>557054</v>
       </c>
       <c r="R44" t="n">
-        <v>7227147</v>
+        <v>7227134</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5051,10 +5051,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126091025</v>
+        <v>126091061</v>
       </c>
       <c r="B45" t="n">
-        <v>91242</v>
+        <v>80084</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5062,34 +5062,41 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>556986</v>
+        <v>557049</v>
       </c>
       <c r="R45" t="n">
-        <v>7227133</v>
+        <v>7227144</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5130,6 +5137,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5152,52 +5160,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126091061</v>
+        <v>126091050</v>
       </c>
       <c r="B46" t="n">
-        <v>80081</v>
+        <v>80112</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>557049</v>
+        <v>556992</v>
       </c>
       <c r="R46" t="n">
-        <v>7227144</v>
+        <v>7227120</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5238,7 +5239,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5261,32 +5261,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126091011</v>
+        <v>126091111</v>
       </c>
       <c r="B47" t="n">
-        <v>79009</v>
+        <v>80119</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>6464</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5296,10 +5296,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>557066</v>
+        <v>557064</v>
       </c>
       <c r="R47" t="n">
-        <v>7227351</v>
+        <v>7227147</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5326,12 +5326,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5362,10 +5362,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126091142</v>
+        <v>126091038</v>
       </c>
       <c r="B48" t="n">
-        <v>78977</v>
+        <v>57657</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5373,21 +5373,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5397,10 +5397,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>557156</v>
+        <v>557057</v>
       </c>
       <c r="R48" t="n">
-        <v>7227270</v>
+        <v>7227134</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5433,6 +5433,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack färsk</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5463,27 +5468,27 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126091038</v>
+        <v>126091113</v>
       </c>
       <c r="B49" t="n">
-        <v>57656</v>
+        <v>57761</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5498,10 +5503,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>557057</v>
+        <v>556728</v>
       </c>
       <c r="R49" t="n">
-        <v>7227134</v>
+        <v>7227079</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5534,11 +5539,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack färsk</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5569,32 +5569,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126091113</v>
+        <v>126091142</v>
       </c>
       <c r="B50" t="n">
-        <v>57760</v>
+        <v>78980</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5604,10 +5604,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>556728</v>
+        <v>557156</v>
       </c>
       <c r="R50" t="n">
-        <v>7227079</v>
+        <v>7227270</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5670,45 +5670,52 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126091171</v>
+        <v>126091059</v>
       </c>
       <c r="B51" t="n">
-        <v>80115</v>
+        <v>80084</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>557049</v>
+        <v>556914</v>
       </c>
       <c r="R51" t="n">
-        <v>7227144</v>
+        <v>7227278</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5735,12 +5742,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5749,6 +5756,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5771,52 +5779,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126091059</v>
+        <v>126091171</v>
       </c>
       <c r="B52" t="n">
-        <v>80081</v>
+        <v>80118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>556914</v>
+        <v>557049</v>
       </c>
       <c r="R52" t="n">
-        <v>7227278</v>
+        <v>7227144</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5843,12 +5844,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5857,7 +5858,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5883,7 +5883,7 @@
         <v>126091037</v>
       </c>
       <c r="B53" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>126091353</v>
       </c>
       <c r="B54" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6087,32 +6087,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126091161</v>
+        <v>126091026</v>
       </c>
       <c r="B55" t="n">
-        <v>78977</v>
+        <v>91942</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6122,10 +6122,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>557149</v>
+        <v>556711</v>
       </c>
       <c r="R55" t="n">
-        <v>7227169</v>
+        <v>7227080</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6158,11 +6158,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Fertil</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6193,10 +6188,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126091134</v>
+        <v>126091161</v>
       </c>
       <c r="B56" t="n">
-        <v>91260</v>
+        <v>78980</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6204,21 +6199,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6228,10 +6223,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>556726</v>
+        <v>557149</v>
       </c>
       <c r="R56" t="n">
-        <v>7227062</v>
+        <v>7227169</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6264,6 +6259,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6294,10 +6294,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126091139</v>
+        <v>126091134</v>
       </c>
       <c r="B57" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6329,10 +6329,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>557138</v>
+        <v>556726</v>
       </c>
       <c r="R57" t="n">
-        <v>7227186</v>
+        <v>7227062</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6395,32 +6395,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126091026</v>
+        <v>126091139</v>
       </c>
       <c r="B58" t="n">
-        <v>91939</v>
+        <v>91263</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6430,10 +6430,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>556711</v>
+        <v>557138</v>
       </c>
       <c r="R58" t="n">
-        <v>7227080</v>
+        <v>7227186</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6499,7 +6499,7 @@
         <v>126091091</v>
       </c>
       <c r="B59" t="n">
-        <v>79984</v>
+        <v>79987</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6597,32 +6597,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126091446</v>
+        <v>126091082</v>
       </c>
       <c r="B60" t="n">
-        <v>80115</v>
+        <v>80084</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6632,10 +6632,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>556925</v>
+        <v>556947</v>
       </c>
       <c r="R60" t="n">
-        <v>7227179</v>
+        <v>7227303</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6662,12 +6662,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6698,10 +6698,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126091054</v>
+        <v>126091446</v>
       </c>
       <c r="B61" t="n">
-        <v>98373</v>
+        <v>80118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6709,21 +6709,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>556704</v>
+        <v>556925</v>
       </c>
       <c r="R61" t="n">
-        <v>7227103</v>
+        <v>7227179</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6799,10 +6799,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126091057</v>
+        <v>126091054</v>
       </c>
       <c r="B62" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6834,10 +6834,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>557065</v>
+        <v>556704</v>
       </c>
       <c r="R62" t="n">
-        <v>7227144</v>
+        <v>7227103</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6900,32 +6900,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126091082</v>
+        <v>126091057</v>
       </c>
       <c r="B63" t="n">
-        <v>80081</v>
+        <v>98382</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2081</v>
+        <v>221952</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6935,10 +6935,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>556947</v>
+        <v>557065</v>
       </c>
       <c r="R63" t="n">
-        <v>7227303</v>
+        <v>7227144</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6965,12 +6965,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7004,7 +7004,7 @@
         <v>126091116</v>
       </c>
       <c r="B64" t="n">
-        <v>57812</v>
+        <v>57813</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7102,32 +7102,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126091056</v>
+        <v>126091136</v>
       </c>
       <c r="B65" t="n">
-        <v>98373</v>
+        <v>91263</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7137,10 +7137,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>557140</v>
+        <v>556803</v>
       </c>
       <c r="R65" t="n">
-        <v>7227297</v>
+        <v>7227106</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7203,10 +7203,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126091136</v>
+        <v>126091081</v>
       </c>
       <c r="B66" t="n">
-        <v>91260</v>
+        <v>80084</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7214,21 +7214,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7238,10 +7238,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>556803</v>
+        <v>556946</v>
       </c>
       <c r="R66" t="n">
-        <v>7227106</v>
+        <v>7227279</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7268,12 +7268,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7307,7 +7307,7 @@
         <v>126091155</v>
       </c>
       <c r="B67" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7405,32 +7405,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126091081</v>
+        <v>126091056</v>
       </c>
       <c r="B68" t="n">
-        <v>80081</v>
+        <v>98382</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2081</v>
+        <v>221952</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>556946</v>
+        <v>557140</v>
       </c>
       <c r="R68" t="n">
-        <v>7227279</v>
+        <v>7227297</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7470,12 +7470,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7509,7 +7509,7 @@
         <v>126091046</v>
       </c>
       <c r="B69" t="n">
-        <v>80109</v>
+        <v>80112</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         <v>126091103</v>
       </c>
       <c r="B70" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         <v>126091154</v>
       </c>
       <c r="B71" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>126091086</v>
       </c>
       <c r="B72" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 23758-2025 artfynd.xlsx
+++ b/artfynd/A 23758-2025 artfynd.xlsx
@@ -1493,32 +1493,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126091058</v>
+        <v>126091080</v>
       </c>
       <c r="B10" t="n">
-        <v>98382</v>
+        <v>80084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1528,10 +1528,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557128</v>
+        <v>556915</v>
       </c>
       <c r="R10" t="n">
-        <v>7227190</v>
+        <v>7227290</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1558,12 +1558,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1594,10 +1594,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126091080</v>
+        <v>126091138</v>
       </c>
       <c r="B11" t="n">
-        <v>80084</v>
+        <v>91263</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1605,21 +1605,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>556915</v>
+        <v>557073</v>
       </c>
       <c r="R11" t="n">
-        <v>7227290</v>
+        <v>7227154</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1659,12 +1659,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1695,32 +1695,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126091138</v>
+        <v>126091058</v>
       </c>
       <c r="B12" t="n">
-        <v>91263</v>
+        <v>98382</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>557073</v>
+        <v>557128</v>
       </c>
       <c r="R12" t="n">
-        <v>7227154</v>
+        <v>7227190</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -3013,32 +3013,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126091048</v>
+        <v>126091096</v>
       </c>
       <c r="B25" t="n">
-        <v>80112</v>
+        <v>57657</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3048,10 +3048,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>556737</v>
+        <v>556986</v>
       </c>
       <c r="R25" t="n">
-        <v>7227086</v>
+        <v>7227133</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3084,6 +3084,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3114,32 +3119,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126091096</v>
+        <v>126091048</v>
       </c>
       <c r="B26" t="n">
-        <v>57657</v>
+        <v>80112</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3149,10 +3154,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>556986</v>
+        <v>556737</v>
       </c>
       <c r="R26" t="n">
-        <v>7227133</v>
+        <v>7227086</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3185,11 +3190,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4129,10 +4129,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126091032</v>
+        <v>126091131</v>
       </c>
       <c r="B36" t="n">
-        <v>57657</v>
+        <v>91263</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4140,21 +4140,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4164,10 +4164,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>557048</v>
+        <v>556707</v>
       </c>
       <c r="R36" t="n">
-        <v>7227240</v>
+        <v>7227095</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4194,17 +4194,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4235,10 +4230,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126091131</v>
+        <v>126091032</v>
       </c>
       <c r="B37" t="n">
-        <v>91263</v>
+        <v>57657</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4246,21 +4241,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4270,10 +4265,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>556707</v>
+        <v>557048</v>
       </c>
       <c r="R37" t="n">
-        <v>7227095</v>
+        <v>7227240</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4300,12 +4295,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4647,10 +4647,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126091025</v>
+        <v>126091101</v>
       </c>
       <c r="B41" t="n">
-        <v>91245</v>
+        <v>80083</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4658,21 +4658,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4682,10 +4682,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>556986</v>
+        <v>556918</v>
       </c>
       <c r="R41" t="n">
-        <v>7227133</v>
+        <v>7227271</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4748,10 +4748,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126091011</v>
+        <v>126091137</v>
       </c>
       <c r="B42" t="n">
-        <v>79012</v>
+        <v>91263</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4759,21 +4759,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>185</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>557066</v>
+        <v>557054</v>
       </c>
       <c r="R42" t="n">
-        <v>7227351</v>
+        <v>7227134</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4813,12 +4813,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4849,10 +4849,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126091101</v>
+        <v>126091061</v>
       </c>
       <c r="B43" t="n">
-        <v>80083</v>
+        <v>80084</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4860,34 +4860,41 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>556918</v>
+        <v>557049</v>
       </c>
       <c r="R43" t="n">
-        <v>7227271</v>
+        <v>7227144</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4914,12 +4921,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4928,6 +4935,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4950,32 +4958,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126091137</v>
+        <v>126091050</v>
       </c>
       <c r="B44" t="n">
-        <v>91263</v>
+        <v>80112</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4985,10 +4993,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>557054</v>
+        <v>556992</v>
       </c>
       <c r="R44" t="n">
-        <v>7227134</v>
+        <v>7227120</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5051,52 +5059,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126091061</v>
+        <v>126091111</v>
       </c>
       <c r="B45" t="n">
-        <v>80084</v>
+        <v>80119</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>557049</v>
+        <v>557064</v>
       </c>
       <c r="R45" t="n">
-        <v>7227144</v>
+        <v>7227147</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5137,7 +5138,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5160,32 +5160,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126091050</v>
+        <v>126091025</v>
       </c>
       <c r="B46" t="n">
-        <v>80112</v>
+        <v>91245</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5195,10 +5195,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>556992</v>
+        <v>556986</v>
       </c>
       <c r="R46" t="n">
-        <v>7227120</v>
+        <v>7227133</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5261,32 +5261,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126091111</v>
+        <v>126091011</v>
       </c>
       <c r="B47" t="n">
-        <v>80119</v>
+        <v>79012</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6464</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5296,10 +5296,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>557064</v>
+        <v>557066</v>
       </c>
       <c r="R47" t="n">
-        <v>7227147</v>
+        <v>7227351</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5326,12 +5326,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5670,52 +5670,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126091059</v>
+        <v>126091353</v>
       </c>
       <c r="B51" t="n">
-        <v>80084</v>
+        <v>98382</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>221952</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>556914</v>
+        <v>556926</v>
       </c>
       <c r="R51" t="n">
-        <v>7227278</v>
+        <v>7227176</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5742,12 +5735,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5756,7 +5749,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5779,45 +5771,52 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126091171</v>
+        <v>126091059</v>
       </c>
       <c r="B52" t="n">
-        <v>80118</v>
+        <v>80084</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>557049</v>
+        <v>556914</v>
       </c>
       <c r="R52" t="n">
-        <v>7227144</v>
+        <v>7227278</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5844,12 +5843,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5858,6 +5857,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5880,32 +5880,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126091037</v>
+        <v>126091171</v>
       </c>
       <c r="B53" t="n">
-        <v>57657</v>
+        <v>80118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5915,10 +5915,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>556702</v>
+        <v>557049</v>
       </c>
       <c r="R53" t="n">
-        <v>7227082</v>
+        <v>7227144</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5951,11 +5951,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5986,32 +5981,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126091353</v>
+        <v>126091037</v>
       </c>
       <c r="B54" t="n">
-        <v>98382</v>
+        <v>57657</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6021,10 +6016,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>556926</v>
+        <v>556702</v>
       </c>
       <c r="R54" t="n">
-        <v>7227176</v>
+        <v>7227082</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6051,12 +6046,17 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7708,10 +7708,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126091154</v>
+        <v>126091086</v>
       </c>
       <c r="B71" t="n">
-        <v>78980</v>
+        <v>80084</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7719,21 +7719,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7743,10 +7743,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>556904</v>
+        <v>556691</v>
       </c>
       <c r="R71" t="n">
-        <v>7227312</v>
+        <v>7227079</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7773,17 +7773,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7814,10 +7809,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126091086</v>
+        <v>126091154</v>
       </c>
       <c r="B72" t="n">
-        <v>80084</v>
+        <v>78980</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7825,21 +7820,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7849,10 +7844,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>556691</v>
+        <v>556904</v>
       </c>
       <c r="R72" t="n">
-        <v>7227079</v>
+        <v>7227312</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7879,12 +7874,17 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD72" t="b">

--- a/artfynd/A 23758-2025 artfynd.xlsx
+++ b/artfynd/A 23758-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126091092</v>
+        <v>126091089</v>
       </c>
       <c r="B2" t="n">
-        <v>79987</v>
+        <v>80084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556906</v>
+        <v>557054</v>
       </c>
       <c r="R2" t="n">
-        <v>7227086</v>
+        <v>7227146</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126091089</v>
+        <v>126091092</v>
       </c>
       <c r="B3" t="n">
-        <v>80084</v>
+        <v>79987</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>557054</v>
+        <v>556906</v>
       </c>
       <c r="R3" t="n">
-        <v>7227146</v>
+        <v>7227086</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1190,32 +1190,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126091170</v>
+        <v>126091117</v>
       </c>
       <c r="B7" t="n">
-        <v>80118</v>
+        <v>57813</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6463</v>
+        <v>103022</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556915</v>
+        <v>556827</v>
       </c>
       <c r="R7" t="n">
-        <v>7227293</v>
+        <v>7227124</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1291,32 +1291,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126091087</v>
+        <v>126091170</v>
       </c>
       <c r="B8" t="n">
-        <v>80084</v>
+        <v>80118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1326,10 +1326,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556869</v>
+        <v>556915</v>
       </c>
       <c r="R8" t="n">
-        <v>7227096</v>
+        <v>7227293</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1392,10 +1392,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126091117</v>
+        <v>126091087</v>
       </c>
       <c r="B9" t="n">
-        <v>57813</v>
+        <v>80084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1403,21 +1403,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103022</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556827</v>
+        <v>556869</v>
       </c>
       <c r="R9" t="n">
-        <v>7227124</v>
+        <v>7227096</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1897,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126091159</v>
+        <v>126091118</v>
       </c>
       <c r="B14" t="n">
-        <v>78980</v>
+        <v>57813</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,21 +1908,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>103022</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557055</v>
+        <v>556859</v>
       </c>
       <c r="R14" t="n">
-        <v>7227102</v>
+        <v>7227119</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1998,10 +1998,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126091083</v>
+        <v>126091159</v>
       </c>
       <c r="B15" t="n">
-        <v>80084</v>
+        <v>78980</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2009,21 +2009,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2033,10 +2033,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>556975</v>
+        <v>557055</v>
       </c>
       <c r="R15" t="n">
-        <v>7227303</v>
+        <v>7227102</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2063,12 +2063,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2099,10 +2099,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126091118</v>
+        <v>126091083</v>
       </c>
       <c r="B16" t="n">
-        <v>57813</v>
+        <v>80084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2110,21 +2110,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103022</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2134,10 +2134,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>556859</v>
+        <v>556975</v>
       </c>
       <c r="R16" t="n">
-        <v>7227119</v>
+        <v>7227303</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2164,12 +2164,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2301,10 +2301,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126091022</v>
+        <v>126091157</v>
       </c>
       <c r="B18" t="n">
-        <v>91245</v>
+        <v>78980</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2312,21 +2312,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2336,10 +2336,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>557054</v>
+        <v>556844</v>
       </c>
       <c r="R18" t="n">
-        <v>7227356</v>
+        <v>7227129</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2366,12 +2366,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2402,32 +2407,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126091156</v>
+        <v>126091047</v>
       </c>
       <c r="B19" t="n">
-        <v>78980</v>
+        <v>80112</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2437,10 +2442,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>556815</v>
+        <v>556947</v>
       </c>
       <c r="R19" t="n">
-        <v>7227118</v>
+        <v>7227277</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2467,12 +2472,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2503,7 +2508,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126091079</v>
+        <v>126091088</v>
       </c>
       <c r="B20" t="n">
         <v>80084</v>
@@ -2538,10 +2543,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>556916</v>
+        <v>557057</v>
       </c>
       <c r="R20" t="n">
-        <v>7227278</v>
+        <v>7227107</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2568,12 +2573,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2604,10 +2609,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126091157</v>
+        <v>126091079</v>
       </c>
       <c r="B21" t="n">
-        <v>78980</v>
+        <v>80084</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2615,21 +2620,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2639,10 +2644,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>556844</v>
+        <v>556916</v>
       </c>
       <c r="R21" t="n">
-        <v>7227129</v>
+        <v>7227278</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2669,17 +2674,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Fertil</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2710,10 +2710,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126091088</v>
+        <v>126091022</v>
       </c>
       <c r="B22" t="n">
-        <v>80084</v>
+        <v>91245</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2721,21 +2721,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>557057</v>
+        <v>557054</v>
       </c>
       <c r="R22" t="n">
-        <v>7227107</v>
+        <v>7227356</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2811,32 +2811,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126091047</v>
+        <v>126091156</v>
       </c>
       <c r="B23" t="n">
-        <v>80112</v>
+        <v>78980</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2846,10 +2846,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>556947</v>
+        <v>556815</v>
       </c>
       <c r="R23" t="n">
-        <v>7227277</v>
+        <v>7227118</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2876,12 +2876,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3013,32 +3013,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126091096</v>
+        <v>126091048</v>
       </c>
       <c r="B25" t="n">
-        <v>57657</v>
+        <v>80112</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3048,10 +3048,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>556986</v>
+        <v>556737</v>
       </c>
       <c r="R25" t="n">
-        <v>7227133</v>
+        <v>7227086</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3084,11 +3084,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3119,32 +3114,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126091048</v>
+        <v>126091096</v>
       </c>
       <c r="B26" t="n">
-        <v>80112</v>
+        <v>57657</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3154,10 +3149,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>556737</v>
+        <v>556986</v>
       </c>
       <c r="R26" t="n">
-        <v>7227086</v>
+        <v>7227133</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3190,6 +3185,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3220,32 +3220,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126091094</v>
+        <v>126091021</v>
       </c>
       <c r="B27" t="n">
-        <v>79987</v>
+        <v>91245</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3255,10 +3255,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>556900</v>
+        <v>557035</v>
       </c>
       <c r="R27" t="n">
-        <v>7227075</v>
+        <v>7227275</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3285,12 +3285,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3321,32 +3321,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126091158</v>
+        <v>126091094</v>
       </c>
       <c r="B28" t="n">
-        <v>78980</v>
+        <v>79987</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>556943</v>
+        <v>556900</v>
       </c>
       <c r="R28" t="n">
-        <v>7227059</v>
+        <v>7227075</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3422,10 +3422,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126091021</v>
+        <v>126091158</v>
       </c>
       <c r="B29" t="n">
-        <v>91245</v>
+        <v>78980</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3433,21 +3433,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3457,10 +3457,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>557035</v>
+        <v>556943</v>
       </c>
       <c r="R29" t="n">
-        <v>7227275</v>
+        <v>7227059</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3487,12 +3487,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3624,32 +3624,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126091045</v>
+        <v>126091077</v>
       </c>
       <c r="B31" t="n">
-        <v>80112</v>
+        <v>80084</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3659,10 +3659,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>556904</v>
+        <v>556902</v>
       </c>
       <c r="R31" t="n">
-        <v>7227312</v>
+        <v>7227281</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3725,32 +3725,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126091078</v>
+        <v>126091045</v>
       </c>
       <c r="B32" t="n">
-        <v>80084</v>
+        <v>80112</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3760,10 +3760,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>556918</v>
+        <v>556904</v>
       </c>
       <c r="R32" t="n">
-        <v>7227271</v>
+        <v>7227312</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3826,10 +3826,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126091133</v>
+        <v>126091078</v>
       </c>
       <c r="B33" t="n">
-        <v>91263</v>
+        <v>80084</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3837,21 +3837,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>556729</v>
+        <v>556918</v>
       </c>
       <c r="R33" t="n">
-        <v>7227082</v>
+        <v>7227271</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3891,12 +3891,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4028,10 +4028,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126091077</v>
+        <v>126091133</v>
       </c>
       <c r="B35" t="n">
-        <v>80084</v>
+        <v>91263</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4039,21 +4039,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4063,10 +4063,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>556902</v>
+        <v>556729</v>
       </c>
       <c r="R35" t="n">
-        <v>7227281</v>
+        <v>7227082</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4093,12 +4093,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4336,52 +4336,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126091060</v>
+        <v>126091108</v>
       </c>
       <c r="B38" t="n">
-        <v>80084</v>
+        <v>80119</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>556945</v>
+        <v>556916</v>
       </c>
       <c r="R38" t="n">
-        <v>7227306</v>
+        <v>7227278</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4422,7 +4415,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4445,7 +4437,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126091108</v>
+        <v>126091110</v>
       </c>
       <c r="B39" t="n">
         <v>80119</v>
@@ -4480,10 +4472,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>556916</v>
+        <v>557049</v>
       </c>
       <c r="R39" t="n">
-        <v>7227278</v>
+        <v>7227144</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4510,12 +4502,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4546,45 +4538,52 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126091110</v>
+        <v>126091060</v>
       </c>
       <c r="B40" t="n">
-        <v>80119</v>
+        <v>80084</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>557049</v>
+        <v>556945</v>
       </c>
       <c r="R40" t="n">
-        <v>7227144</v>
+        <v>7227306</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4611,12 +4610,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4625,6 +4624,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4647,10 +4647,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126091101</v>
+        <v>126091061</v>
       </c>
       <c r="B41" t="n">
-        <v>80083</v>
+        <v>80084</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4658,34 +4658,41 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>556918</v>
+        <v>557049</v>
       </c>
       <c r="R41" t="n">
-        <v>7227271</v>
+        <v>7227144</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4712,12 +4719,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4726,6 +4733,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4748,10 +4756,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126091137</v>
+        <v>126091011</v>
       </c>
       <c r="B42" t="n">
-        <v>91263</v>
+        <v>79012</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4759,21 +4767,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>185</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4783,10 +4791,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>557054</v>
+        <v>557066</v>
       </c>
       <c r="R42" t="n">
-        <v>7227134</v>
+        <v>7227351</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4813,12 +4821,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4849,10 +4857,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126091061</v>
+        <v>126091025</v>
       </c>
       <c r="B43" t="n">
-        <v>80084</v>
+        <v>91245</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4860,41 +4868,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>557049</v>
+        <v>556986</v>
       </c>
       <c r="R43" t="n">
-        <v>7227144</v>
+        <v>7227133</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4935,7 +4936,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4958,32 +4958,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126091050</v>
+        <v>126091101</v>
       </c>
       <c r="B44" t="n">
-        <v>80112</v>
+        <v>80083</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>556992</v>
+        <v>556918</v>
       </c>
       <c r="R44" t="n">
-        <v>7227120</v>
+        <v>7227271</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5023,12 +5023,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5059,10 +5059,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126091111</v>
+        <v>126091050</v>
       </c>
       <c r="B45" t="n">
-        <v>80119</v>
+        <v>80112</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5070,21 +5070,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5094,10 +5094,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>557064</v>
+        <v>556992</v>
       </c>
       <c r="R45" t="n">
-        <v>7227147</v>
+        <v>7227120</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5160,32 +5160,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126091025</v>
+        <v>126091111</v>
       </c>
       <c r="B46" t="n">
-        <v>91245</v>
+        <v>80119</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5195,10 +5195,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>556986</v>
+        <v>557064</v>
       </c>
       <c r="R46" t="n">
-        <v>7227133</v>
+        <v>7227147</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5261,10 +5261,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126091011</v>
+        <v>126091137</v>
       </c>
       <c r="B47" t="n">
-        <v>79012</v>
+        <v>91263</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5272,21 +5272,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5296,10 +5296,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>557066</v>
+        <v>557054</v>
       </c>
       <c r="R47" t="n">
-        <v>7227351</v>
+        <v>7227134</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5326,12 +5326,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5362,10 +5362,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126091038</v>
+        <v>126091142</v>
       </c>
       <c r="B48" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5373,21 +5373,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5397,10 +5397,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>557057</v>
+        <v>557156</v>
       </c>
       <c r="R48" t="n">
-        <v>7227134</v>
+        <v>7227270</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5433,11 +5433,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack färsk</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5468,27 +5463,27 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126091113</v>
+        <v>126091038</v>
       </c>
       <c r="B49" t="n">
-        <v>57761</v>
+        <v>57657</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5503,10 +5498,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>556728</v>
+        <v>557057</v>
       </c>
       <c r="R49" t="n">
-        <v>7227079</v>
+        <v>7227134</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5539,6 +5534,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack färsk</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5569,32 +5569,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126091142</v>
+        <v>126091113</v>
       </c>
       <c r="B50" t="n">
-        <v>78980</v>
+        <v>57761</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5604,10 +5604,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>557156</v>
+        <v>556728</v>
       </c>
       <c r="R50" t="n">
-        <v>7227270</v>
+        <v>7227079</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5670,10 +5670,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126091353</v>
+        <v>126091171</v>
       </c>
       <c r="B51" t="n">
-        <v>98382</v>
+        <v>80118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5681,21 +5681,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5705,10 +5705,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>556926</v>
+        <v>557049</v>
       </c>
       <c r="R51" t="n">
-        <v>7227176</v>
+        <v>7227144</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5735,12 +5735,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5771,10 +5771,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126091059</v>
+        <v>126091037</v>
       </c>
       <c r="B52" t="n">
-        <v>80084</v>
+        <v>57657</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5782,41 +5782,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>556914</v>
+        <v>556702</v>
       </c>
       <c r="R52" t="n">
-        <v>7227278</v>
+        <v>7227082</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5843,12 +5836,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5857,7 +5855,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5880,45 +5877,52 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126091171</v>
+        <v>126091059</v>
       </c>
       <c r="B53" t="n">
-        <v>80118</v>
+        <v>80084</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>557049</v>
+        <v>556914</v>
       </c>
       <c r="R53" t="n">
-        <v>7227144</v>
+        <v>7227278</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5945,12 +5949,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5959,6 +5963,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5981,32 +5986,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126091037</v>
+        <v>126091353</v>
       </c>
       <c r="B54" t="n">
-        <v>57657</v>
+        <v>98382</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6016,10 +6021,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>556702</v>
+        <v>556926</v>
       </c>
       <c r="R54" t="n">
-        <v>7227082</v>
+        <v>7227176</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6046,17 +6051,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6087,32 +6087,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126091026</v>
+        <v>126091161</v>
       </c>
       <c r="B55" t="n">
-        <v>91942</v>
+        <v>78980</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6122,10 +6122,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>556711</v>
+        <v>557149</v>
       </c>
       <c r="R55" t="n">
-        <v>7227080</v>
+        <v>7227169</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6158,6 +6158,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6188,32 +6193,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126091161</v>
+        <v>126091026</v>
       </c>
       <c r="B56" t="n">
-        <v>78980</v>
+        <v>91942</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6223,10 +6228,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>557149</v>
+        <v>556711</v>
       </c>
       <c r="R56" t="n">
-        <v>7227169</v>
+        <v>7227080</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6259,11 +6264,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Fertil</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6496,32 +6496,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126091091</v>
+        <v>126091082</v>
       </c>
       <c r="B59" t="n">
-        <v>79987</v>
+        <v>80084</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6531,10 +6531,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>557022</v>
+        <v>556947</v>
       </c>
       <c r="R59" t="n">
-        <v>7227286</v>
+        <v>7227303</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6597,32 +6597,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126091082</v>
+        <v>126091091</v>
       </c>
       <c r="B60" t="n">
-        <v>80084</v>
+        <v>79987</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6632,10 +6632,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>556947</v>
+        <v>557022</v>
       </c>
       <c r="R60" t="n">
-        <v>7227303</v>
+        <v>7227286</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7102,32 +7102,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126091136</v>
+        <v>126091056</v>
       </c>
       <c r="B65" t="n">
-        <v>91263</v>
+        <v>98382</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7137,10 +7137,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>556803</v>
+        <v>557140</v>
       </c>
       <c r="R65" t="n">
-        <v>7227106</v>
+        <v>7227297</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7203,10 +7203,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126091081</v>
+        <v>126091136</v>
       </c>
       <c r="B66" t="n">
-        <v>80084</v>
+        <v>91263</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7214,21 +7214,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7238,10 +7238,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>556946</v>
+        <v>556803</v>
       </c>
       <c r="R66" t="n">
-        <v>7227279</v>
+        <v>7227106</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7268,12 +7268,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7304,10 +7304,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126091155</v>
+        <v>126091081</v>
       </c>
       <c r="B67" t="n">
-        <v>78980</v>
+        <v>80084</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7315,21 +7315,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7339,10 +7339,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>557073</v>
+        <v>556946</v>
       </c>
       <c r="R67" t="n">
-        <v>7227326</v>
+        <v>7227279</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7405,32 +7405,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126091056</v>
+        <v>126091155</v>
       </c>
       <c r="B68" t="n">
-        <v>98382</v>
+        <v>78980</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>557140</v>
+        <v>557073</v>
       </c>
       <c r="R68" t="n">
-        <v>7227297</v>
+        <v>7227326</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7470,12 +7470,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7506,32 +7506,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126091046</v>
+        <v>126091086</v>
       </c>
       <c r="B69" t="n">
-        <v>80112</v>
+        <v>80084</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7541,10 +7541,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>556915</v>
+        <v>556691</v>
       </c>
       <c r="R69" t="n">
-        <v>7227293</v>
+        <v>7227079</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7571,12 +7571,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7607,32 +7607,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126091103</v>
+        <v>126091046</v>
       </c>
       <c r="B70" t="n">
-        <v>80083</v>
+        <v>80112</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7642,10 +7642,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>556737</v>
+        <v>556915</v>
       </c>
       <c r="R70" t="n">
-        <v>7227086</v>
+        <v>7227293</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7708,10 +7708,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126091086</v>
+        <v>126091103</v>
       </c>
       <c r="B71" t="n">
-        <v>80084</v>
+        <v>80083</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7719,21 +7719,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7743,10 +7743,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>556691</v>
+        <v>556737</v>
       </c>
       <c r="R71" t="n">
-        <v>7227079</v>
+        <v>7227086</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>

--- a/artfynd/A 23758-2025 artfynd.xlsx
+++ b/artfynd/A 23758-2025 artfynd.xlsx
@@ -2301,10 +2301,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126091157</v>
+        <v>126091088</v>
       </c>
       <c r="B18" t="n">
-        <v>78980</v>
+        <v>80084</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2312,21 +2312,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2336,10 +2336,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>556844</v>
+        <v>557057</v>
       </c>
       <c r="R18" t="n">
-        <v>7227129</v>
+        <v>7227107</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2372,11 +2372,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Fertil</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2407,32 +2402,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126091047</v>
+        <v>126091157</v>
       </c>
       <c r="B19" t="n">
-        <v>80112</v>
+        <v>78980</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2442,10 +2437,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>556947</v>
+        <v>556844</v>
       </c>
       <c r="R19" t="n">
-        <v>7227277</v>
+        <v>7227129</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2472,12 +2467,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2508,32 +2508,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126091088</v>
+        <v>126091047</v>
       </c>
       <c r="B20" t="n">
-        <v>80084</v>
+        <v>80112</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2543,10 +2543,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>557057</v>
+        <v>556947</v>
       </c>
       <c r="R20" t="n">
-        <v>7227107</v>
+        <v>7227277</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2573,12 +2573,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3013,32 +3013,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126091048</v>
+        <v>126091096</v>
       </c>
       <c r="B25" t="n">
-        <v>80112</v>
+        <v>57657</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3048,10 +3048,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>556737</v>
+        <v>556986</v>
       </c>
       <c r="R25" t="n">
-        <v>7227086</v>
+        <v>7227133</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3084,6 +3084,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3114,32 +3119,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126091096</v>
+        <v>126091048</v>
       </c>
       <c r="B26" t="n">
-        <v>57657</v>
+        <v>80112</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3149,10 +3154,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>556986</v>
+        <v>556737</v>
       </c>
       <c r="R26" t="n">
-        <v>7227133</v>
+        <v>7227086</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3185,11 +3190,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3220,32 +3220,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126091021</v>
+        <v>126091094</v>
       </c>
       <c r="B27" t="n">
-        <v>91245</v>
+        <v>79987</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3255,10 +3255,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>557035</v>
+        <v>556900</v>
       </c>
       <c r="R27" t="n">
-        <v>7227275</v>
+        <v>7227075</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3285,12 +3285,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3321,32 +3321,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126091094</v>
+        <v>126091158</v>
       </c>
       <c r="B28" t="n">
-        <v>79987</v>
+        <v>78980</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>556900</v>
+        <v>556943</v>
       </c>
       <c r="R28" t="n">
-        <v>7227075</v>
+        <v>7227059</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3422,10 +3422,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126091158</v>
+        <v>126091021</v>
       </c>
       <c r="B29" t="n">
-        <v>78980</v>
+        <v>91245</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3433,21 +3433,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3457,10 +3457,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>556943</v>
+        <v>557035</v>
       </c>
       <c r="R29" t="n">
-        <v>7227059</v>
+        <v>7227275</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3487,12 +3487,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -5362,32 +5362,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126091142</v>
+        <v>126091113</v>
       </c>
       <c r="B48" t="n">
-        <v>78980</v>
+        <v>57761</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5397,10 +5397,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>557156</v>
+        <v>556728</v>
       </c>
       <c r="R48" t="n">
-        <v>7227270</v>
+        <v>7227079</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5463,10 +5463,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126091038</v>
+        <v>126091142</v>
       </c>
       <c r="B49" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5474,21 +5474,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5498,10 +5498,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>557057</v>
+        <v>557156</v>
       </c>
       <c r="R49" t="n">
-        <v>7227134</v>
+        <v>7227270</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5534,11 +5534,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack färsk</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5569,27 +5564,27 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126091113</v>
+        <v>126091038</v>
       </c>
       <c r="B50" t="n">
-        <v>57761</v>
+        <v>57657</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5604,10 +5599,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>556728</v>
+        <v>557057</v>
       </c>
       <c r="R50" t="n">
-        <v>7227079</v>
+        <v>7227134</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5640,6 +5635,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack färsk</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5670,45 +5670,52 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126091171</v>
+        <v>126091059</v>
       </c>
       <c r="B51" t="n">
-        <v>80118</v>
+        <v>80084</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>557049</v>
+        <v>556914</v>
       </c>
       <c r="R51" t="n">
-        <v>7227144</v>
+        <v>7227278</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5735,12 +5742,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5749,6 +5756,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5771,32 +5779,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126091037</v>
+        <v>126091171</v>
       </c>
       <c r="B52" t="n">
-        <v>57657</v>
+        <v>80118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5806,10 +5814,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>556702</v>
+        <v>557049</v>
       </c>
       <c r="R52" t="n">
-        <v>7227082</v>
+        <v>7227144</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5842,11 +5850,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5877,10 +5880,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126091059</v>
+        <v>126091037</v>
       </c>
       <c r="B53" t="n">
-        <v>80084</v>
+        <v>57657</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5888,41 +5891,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>556914</v>
+        <v>556702</v>
       </c>
       <c r="R53" t="n">
-        <v>7227278</v>
+        <v>7227082</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5949,12 +5945,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5963,7 +5964,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 23758-2025 artfynd.xlsx
+++ b/artfynd/A 23758-2025 artfynd.xlsx
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126091092</v>
+        <v>126091009</v>
       </c>
       <c r="B3" t="n">
-        <v>79987</v>
+        <v>80119</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,34 +787,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556906</v>
+        <v>556917</v>
       </c>
       <c r="R3" t="n">
-        <v>7227086</v>
+        <v>7227275</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -841,12 +844,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -855,6 +858,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -877,48 +881,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126091009</v>
+        <v>126091030</v>
       </c>
       <c r="B4" t="n">
-        <v>80119</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556917</v>
+        <v>557050</v>
       </c>
       <c r="R4" t="n">
-        <v>7227275</v>
+        <v>7227253</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -953,13 +954,17 @@
           <t>2025-06-18</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -982,32 +987,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126091030</v>
+        <v>126091092</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>79987</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1017,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>557050</v>
+        <v>556906</v>
       </c>
       <c r="R5" t="n">
-        <v>7227253</v>
+        <v>7227086</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1047,17 +1052,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1897,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126091118</v>
+        <v>126091159</v>
       </c>
       <c r="B14" t="n">
-        <v>57813</v>
+        <v>78980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,21 +1908,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103022</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>556859</v>
+        <v>557055</v>
       </c>
       <c r="R14" t="n">
-        <v>7227119</v>
+        <v>7227102</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1998,32 +1998,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126091159</v>
+        <v>126091112</v>
       </c>
       <c r="B15" t="n">
-        <v>78980</v>
+        <v>57761</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2033,10 +2033,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>557055</v>
+        <v>556726</v>
       </c>
       <c r="R15" t="n">
-        <v>7227102</v>
+        <v>7227088</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2200,32 +2200,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126091112</v>
+        <v>126091118</v>
       </c>
       <c r="B17" t="n">
-        <v>57761</v>
+        <v>57813</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103031</v>
+        <v>103022</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>556726</v>
+        <v>556859</v>
       </c>
       <c r="R17" t="n">
-        <v>7227088</v>
+        <v>7227119</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2301,10 +2301,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126091088</v>
+        <v>126091157</v>
       </c>
       <c r="B18" t="n">
-        <v>80084</v>
+        <v>78980</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2312,21 +2312,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2336,10 +2336,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>557057</v>
+        <v>556844</v>
       </c>
       <c r="R18" t="n">
-        <v>7227107</v>
+        <v>7227129</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2372,6 +2372,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2402,32 +2407,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126091157</v>
+        <v>126091047</v>
       </c>
       <c r="B19" t="n">
-        <v>78980</v>
+        <v>80112</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2437,10 +2442,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>556844</v>
+        <v>556947</v>
       </c>
       <c r="R19" t="n">
-        <v>7227129</v>
+        <v>7227277</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2467,17 +2472,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Fertil</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2508,32 +2508,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126091047</v>
+        <v>126091088</v>
       </c>
       <c r="B20" t="n">
-        <v>80112</v>
+        <v>80084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2543,10 +2543,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>556947</v>
+        <v>557057</v>
       </c>
       <c r="R20" t="n">
-        <v>7227277</v>
+        <v>7227107</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2573,12 +2573,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3013,32 +3013,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126091096</v>
+        <v>126091048</v>
       </c>
       <c r="B25" t="n">
-        <v>57657</v>
+        <v>80112</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3048,10 +3048,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>556986</v>
+        <v>556737</v>
       </c>
       <c r="R25" t="n">
-        <v>7227133</v>
+        <v>7227086</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3084,11 +3084,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3119,32 +3114,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126091048</v>
+        <v>126091096</v>
       </c>
       <c r="B26" t="n">
-        <v>80112</v>
+        <v>57657</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3154,10 +3149,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>556737</v>
+        <v>556986</v>
       </c>
       <c r="R26" t="n">
-        <v>7227086</v>
+        <v>7227133</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3190,6 +3185,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4647,10 +4647,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126091061</v>
+        <v>126091011</v>
       </c>
       <c r="B41" t="n">
-        <v>80084</v>
+        <v>79012</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4658,41 +4658,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>557049</v>
+        <v>557066</v>
       </c>
       <c r="R41" t="n">
-        <v>7227144</v>
+        <v>7227351</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4719,12 +4712,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4733,7 +4726,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4756,10 +4748,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126091011</v>
+        <v>126091137</v>
       </c>
       <c r="B42" t="n">
-        <v>79012</v>
+        <v>91263</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4767,21 +4759,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>185</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4791,10 +4783,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>557066</v>
+        <v>557054</v>
       </c>
       <c r="R42" t="n">
-        <v>7227351</v>
+        <v>7227134</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4821,12 +4813,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4857,10 +4849,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126091025</v>
+        <v>126091061</v>
       </c>
       <c r="B43" t="n">
-        <v>91245</v>
+        <v>80084</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4868,34 +4860,41 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>556986</v>
+        <v>557049</v>
       </c>
       <c r="R43" t="n">
-        <v>7227133</v>
+        <v>7227144</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4936,6 +4935,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4958,10 +4958,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126091101</v>
+        <v>126091025</v>
       </c>
       <c r="B44" t="n">
-        <v>80083</v>
+        <v>91245</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4969,21 +4969,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>556918</v>
+        <v>556986</v>
       </c>
       <c r="R44" t="n">
-        <v>7227271</v>
+        <v>7227133</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5023,12 +5023,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5059,32 +5059,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126091050</v>
+        <v>126091101</v>
       </c>
       <c r="B45" t="n">
-        <v>80112</v>
+        <v>80083</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5094,10 +5094,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>556992</v>
+        <v>556918</v>
       </c>
       <c r="R45" t="n">
-        <v>7227120</v>
+        <v>7227271</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5124,12 +5124,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5160,10 +5160,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126091111</v>
+        <v>126091050</v>
       </c>
       <c r="B46" t="n">
-        <v>80119</v>
+        <v>80112</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5171,21 +5171,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5195,10 +5195,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>557064</v>
+        <v>556992</v>
       </c>
       <c r="R46" t="n">
-        <v>7227147</v>
+        <v>7227120</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5261,32 +5261,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126091137</v>
+        <v>126091111</v>
       </c>
       <c r="B47" t="n">
-        <v>91263</v>
+        <v>80119</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5296,10 +5296,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>557054</v>
+        <v>557064</v>
       </c>
       <c r="R47" t="n">
-        <v>7227134</v>
+        <v>7227147</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5362,32 +5362,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126091113</v>
+        <v>126091142</v>
       </c>
       <c r="B48" t="n">
-        <v>57761</v>
+        <v>78980</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5397,10 +5397,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>556728</v>
+        <v>557156</v>
       </c>
       <c r="R48" t="n">
-        <v>7227079</v>
+        <v>7227270</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5463,10 +5463,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126091142</v>
+        <v>126091038</v>
       </c>
       <c r="B49" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5474,21 +5474,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5498,10 +5498,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>557156</v>
+        <v>557057</v>
       </c>
       <c r="R49" t="n">
-        <v>7227270</v>
+        <v>7227134</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5534,6 +5534,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack färsk</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5564,27 +5569,27 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126091038</v>
+        <v>126091113</v>
       </c>
       <c r="B50" t="n">
-        <v>57657</v>
+        <v>57761</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5599,10 +5604,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>557057</v>
+        <v>556728</v>
       </c>
       <c r="R50" t="n">
-        <v>7227134</v>
+        <v>7227079</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5635,11 +5640,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack färsk</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5670,52 +5670,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126091059</v>
+        <v>126091171</v>
       </c>
       <c r="B51" t="n">
-        <v>80084</v>
+        <v>80118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>556914</v>
+        <v>557049</v>
       </c>
       <c r="R51" t="n">
-        <v>7227278</v>
+        <v>7227144</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5742,12 +5735,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5756,7 +5749,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5779,32 +5771,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126091171</v>
+        <v>126091037</v>
       </c>
       <c r="B52" t="n">
-        <v>80118</v>
+        <v>57657</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5814,10 +5806,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>557049</v>
+        <v>556702</v>
       </c>
       <c r="R52" t="n">
-        <v>7227144</v>
+        <v>7227082</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5850,6 +5842,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5880,10 +5877,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126091037</v>
+        <v>126091059</v>
       </c>
       <c r="B53" t="n">
-        <v>57657</v>
+        <v>80084</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5891,34 +5888,41 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>556702</v>
+        <v>556914</v>
       </c>
       <c r="R53" t="n">
-        <v>7227082</v>
+        <v>7227278</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5945,17 +5949,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5964,6 +5963,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 23758-2025 artfynd.xlsx
+++ b/artfynd/A 23758-2025 artfynd.xlsx
@@ -1897,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126091159</v>
+        <v>126091118</v>
       </c>
       <c r="B14" t="n">
-        <v>78980</v>
+        <v>57813</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,21 +1908,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>103022</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557055</v>
+        <v>556859</v>
       </c>
       <c r="R14" t="n">
-        <v>7227102</v>
+        <v>7227119</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1998,32 +1998,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126091112</v>
+        <v>126091159</v>
       </c>
       <c r="B15" t="n">
-        <v>57761</v>
+        <v>78980</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2033,10 +2033,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>556726</v>
+        <v>557055</v>
       </c>
       <c r="R15" t="n">
-        <v>7227088</v>
+        <v>7227102</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2200,32 +2200,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126091118</v>
+        <v>126091112</v>
       </c>
       <c r="B17" t="n">
-        <v>57813</v>
+        <v>57761</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103022</v>
+        <v>103031</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>556859</v>
+        <v>556726</v>
       </c>
       <c r="R17" t="n">
-        <v>7227119</v>
+        <v>7227088</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -3220,32 +3220,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126091094</v>
+        <v>126091021</v>
       </c>
       <c r="B27" t="n">
-        <v>79987</v>
+        <v>91245</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3255,10 +3255,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>556900</v>
+        <v>557035</v>
       </c>
       <c r="R27" t="n">
-        <v>7227075</v>
+        <v>7227275</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3285,12 +3285,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3321,32 +3321,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126091158</v>
+        <v>126091094</v>
       </c>
       <c r="B28" t="n">
-        <v>78980</v>
+        <v>79987</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>556943</v>
+        <v>556900</v>
       </c>
       <c r="R28" t="n">
-        <v>7227059</v>
+        <v>7227075</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3422,10 +3422,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126091021</v>
+        <v>126091158</v>
       </c>
       <c r="B29" t="n">
-        <v>91245</v>
+        <v>78980</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3433,21 +3433,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3457,10 +3457,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>557035</v>
+        <v>556943</v>
       </c>
       <c r="R29" t="n">
-        <v>7227275</v>
+        <v>7227059</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3487,12 +3487,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4647,10 +4647,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126091011</v>
+        <v>126091061</v>
       </c>
       <c r="B41" t="n">
-        <v>79012</v>
+        <v>80084</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4658,34 +4658,41 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>185</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>557066</v>
+        <v>557049</v>
       </c>
       <c r="R41" t="n">
-        <v>7227351</v>
+        <v>7227144</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4712,12 +4719,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4726,6 +4733,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4748,10 +4756,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126091137</v>
+        <v>126091011</v>
       </c>
       <c r="B42" t="n">
-        <v>91263</v>
+        <v>79012</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4759,21 +4767,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>185</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4783,10 +4791,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>557054</v>
+        <v>557066</v>
       </c>
       <c r="R42" t="n">
-        <v>7227134</v>
+        <v>7227351</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4813,12 +4821,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4849,10 +4857,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126091061</v>
+        <v>126091025</v>
       </c>
       <c r="B43" t="n">
-        <v>80084</v>
+        <v>91245</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4860,41 +4868,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>557049</v>
+        <v>556986</v>
       </c>
       <c r="R43" t="n">
-        <v>7227144</v>
+        <v>7227133</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4935,7 +4936,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4958,10 +4958,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126091025</v>
+        <v>126091101</v>
       </c>
       <c r="B44" t="n">
-        <v>91245</v>
+        <v>80083</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4969,21 +4969,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>556986</v>
+        <v>556918</v>
       </c>
       <c r="R44" t="n">
-        <v>7227133</v>
+        <v>7227271</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5023,12 +5023,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5059,32 +5059,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126091101</v>
+        <v>126091050</v>
       </c>
       <c r="B45" t="n">
-        <v>80083</v>
+        <v>80112</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5094,10 +5094,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>556918</v>
+        <v>556992</v>
       </c>
       <c r="R45" t="n">
-        <v>7227271</v>
+        <v>7227120</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5124,12 +5124,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5160,10 +5160,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126091050</v>
+        <v>126091111</v>
       </c>
       <c r="B46" t="n">
-        <v>80112</v>
+        <v>80119</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5171,21 +5171,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5195,10 +5195,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>556992</v>
+        <v>557064</v>
       </c>
       <c r="R46" t="n">
-        <v>7227120</v>
+        <v>7227147</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5261,32 +5261,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126091111</v>
+        <v>126091137</v>
       </c>
       <c r="B47" t="n">
-        <v>80119</v>
+        <v>91263</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5296,10 +5296,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>557064</v>
+        <v>557054</v>
       </c>
       <c r="R47" t="n">
-        <v>7227147</v>
+        <v>7227134</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -7102,32 +7102,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126091056</v>
+        <v>126091155</v>
       </c>
       <c r="B65" t="n">
-        <v>98382</v>
+        <v>78980</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7137,10 +7137,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>557140</v>
+        <v>557073</v>
       </c>
       <c r="R65" t="n">
-        <v>7227297</v>
+        <v>7227326</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7167,12 +7167,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7203,10 +7203,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126091136</v>
+        <v>126091081</v>
       </c>
       <c r="B66" t="n">
-        <v>91263</v>
+        <v>80084</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7214,21 +7214,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7238,10 +7238,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>556803</v>
+        <v>556946</v>
       </c>
       <c r="R66" t="n">
-        <v>7227106</v>
+        <v>7227279</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7268,12 +7268,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7304,10 +7304,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126091081</v>
+        <v>126091136</v>
       </c>
       <c r="B67" t="n">
-        <v>80084</v>
+        <v>91263</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7315,21 +7315,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7339,10 +7339,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>556946</v>
+        <v>556803</v>
       </c>
       <c r="R67" t="n">
-        <v>7227279</v>
+        <v>7227106</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7369,12 +7369,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7405,32 +7405,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126091155</v>
+        <v>126091056</v>
       </c>
       <c r="B68" t="n">
-        <v>78980</v>
+        <v>98382</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>557073</v>
+        <v>557140</v>
       </c>
       <c r="R68" t="n">
-        <v>7227326</v>
+        <v>7227297</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7470,12 +7470,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD68" t="b">

--- a/artfynd/A 23758-2025 artfynd.xlsx
+++ b/artfynd/A 23758-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126091089</v>
       </c>
       <c r="B2" t="n">
-        <v>80084</v>
+        <v>80122</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126091009</v>
       </c>
       <c r="B3" t="n">
-        <v>80119</v>
+        <v>80157</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>126091030</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,6 +910,14 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
@@ -990,7 +998,7 @@
         <v>126091092</v>
       </c>
       <c r="B5" t="n">
-        <v>79987</v>
+        <v>80025</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1099,7 @@
         <v>126091099</v>
       </c>
       <c r="B6" t="n">
-        <v>98265</v>
+        <v>98352</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1201,7 @@
         <v>126091117</v>
       </c>
       <c r="B7" t="n">
-        <v>57813</v>
+        <v>57817</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,7 +1302,7 @@
         <v>126091170</v>
       </c>
       <c r="B8" t="n">
-        <v>80118</v>
+        <v>80156</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1395,7 +1403,7 @@
         <v>126091087</v>
       </c>
       <c r="B9" t="n">
-        <v>80084</v>
+        <v>80122</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1496,7 +1504,7 @@
         <v>126091080</v>
       </c>
       <c r="B10" t="n">
-        <v>80084</v>
+        <v>80122</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1597,7 +1605,7 @@
         <v>126091138</v>
       </c>
       <c r="B11" t="n">
-        <v>91263</v>
+        <v>91348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1706,7 @@
         <v>126091058</v>
       </c>
       <c r="B12" t="n">
-        <v>98382</v>
+        <v>98469</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1799,7 +1807,7 @@
         <v>126091055</v>
       </c>
       <c r="B13" t="n">
-        <v>98382</v>
+        <v>98469</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1900,7 +1908,7 @@
         <v>126091118</v>
       </c>
       <c r="B14" t="n">
-        <v>57813</v>
+        <v>57817</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2001,7 +2009,7 @@
         <v>126091159</v>
       </c>
       <c r="B15" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2102,7 +2110,7 @@
         <v>126091083</v>
       </c>
       <c r="B16" t="n">
-        <v>80084</v>
+        <v>80122</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,7 +2211,7 @@
         <v>126091112</v>
       </c>
       <c r="B17" t="n">
-        <v>57761</v>
+        <v>57765</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2304,7 +2312,7 @@
         <v>126091157</v>
       </c>
       <c r="B18" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2410,7 +2418,7 @@
         <v>126091047</v>
       </c>
       <c r="B19" t="n">
-        <v>80112</v>
+        <v>80150</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2511,7 +2519,7 @@
         <v>126091088</v>
       </c>
       <c r="B20" t="n">
-        <v>80084</v>
+        <v>80122</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2612,7 +2620,7 @@
         <v>126091079</v>
       </c>
       <c r="B21" t="n">
-        <v>80084</v>
+        <v>80122</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2713,7 +2721,7 @@
         <v>126091022</v>
       </c>
       <c r="B22" t="n">
-        <v>91245</v>
+        <v>91330</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2814,7 +2822,7 @@
         <v>126091156</v>
       </c>
       <c r="B23" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2915,7 +2923,7 @@
         <v>126091109</v>
       </c>
       <c r="B24" t="n">
-        <v>80119</v>
+        <v>80157</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3016,7 +3024,7 @@
         <v>126091048</v>
       </c>
       <c r="B25" t="n">
-        <v>80112</v>
+        <v>80150</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3117,7 +3125,7 @@
         <v>126091096</v>
       </c>
       <c r="B26" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3143,6 +3151,14 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
@@ -3223,7 +3239,7 @@
         <v>126091094</v>
       </c>
       <c r="B27" t="n">
-        <v>79987</v>
+        <v>80025</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3324,7 +3340,7 @@
         <v>126091158</v>
       </c>
       <c r="B28" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3425,7 +3441,7 @@
         <v>126091021</v>
       </c>
       <c r="B29" t="n">
-        <v>91245</v>
+        <v>91330</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3526,7 +3542,7 @@
         <v>126091078</v>
       </c>
       <c r="B30" t="n">
-        <v>80084</v>
+        <v>80122</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3627,7 +3643,7 @@
         <v>126091077</v>
       </c>
       <c r="B31" t="n">
-        <v>80084</v>
+        <v>80122</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3728,7 +3744,7 @@
         <v>126091045</v>
       </c>
       <c r="B32" t="n">
-        <v>80112</v>
+        <v>80150</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3829,7 +3845,7 @@
         <v>126091122</v>
       </c>
       <c r="B33" t="n">
-        <v>91605</v>
+        <v>91690</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3930,7 +3946,7 @@
         <v>126091133</v>
       </c>
       <c r="B34" t="n">
-        <v>91263</v>
+        <v>91348</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4031,7 +4047,7 @@
         <v>126091097</v>
       </c>
       <c r="B35" t="n">
-        <v>97245</v>
+        <v>97331</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4132,7 +4148,7 @@
         <v>126091131</v>
       </c>
       <c r="B36" t="n">
-        <v>91263</v>
+        <v>91348</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4233,7 +4249,7 @@
         <v>126091032</v>
       </c>
       <c r="B37" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4259,6 +4275,14 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
@@ -4339,7 +4363,7 @@
         <v>126091060</v>
       </c>
       <c r="B38" t="n">
-        <v>80084</v>
+        <v>80122</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4448,7 +4472,7 @@
         <v>126091108</v>
       </c>
       <c r="B39" t="n">
-        <v>80119</v>
+        <v>80157</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4549,7 +4573,7 @@
         <v>126091110</v>
       </c>
       <c r="B40" t="n">
-        <v>80119</v>
+        <v>80157</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4650,7 +4674,7 @@
         <v>126091061</v>
       </c>
       <c r="B41" t="n">
-        <v>80084</v>
+        <v>80122</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4759,7 +4783,7 @@
         <v>126091011</v>
       </c>
       <c r="B42" t="n">
-        <v>79012</v>
+        <v>79050</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4860,7 +4884,7 @@
         <v>126091025</v>
       </c>
       <c r="B43" t="n">
-        <v>91245</v>
+        <v>91330</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4961,7 +4985,7 @@
         <v>126091101</v>
       </c>
       <c r="B44" t="n">
-        <v>80083</v>
+        <v>80121</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5062,7 +5086,7 @@
         <v>126091050</v>
       </c>
       <c r="B45" t="n">
-        <v>80112</v>
+        <v>80150</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5163,7 +5187,7 @@
         <v>126091111</v>
       </c>
       <c r="B46" t="n">
-        <v>80119</v>
+        <v>80157</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5264,7 +5288,7 @@
         <v>126091137</v>
       </c>
       <c r="B47" t="n">
-        <v>91263</v>
+        <v>91348</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5365,7 +5389,7 @@
         <v>126091113</v>
       </c>
       <c r="B48" t="n">
-        <v>57761</v>
+        <v>57765</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5466,7 +5490,7 @@
         <v>126091142</v>
       </c>
       <c r="B49" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5567,7 +5591,7 @@
         <v>126091038</v>
       </c>
       <c r="B50" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5593,6 +5617,14 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
@@ -5673,7 +5705,7 @@
         <v>126091059</v>
       </c>
       <c r="B51" t="n">
-        <v>80084</v>
+        <v>80122</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5782,7 +5814,7 @@
         <v>126091171</v>
       </c>
       <c r="B52" t="n">
-        <v>80118</v>
+        <v>80156</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5883,7 +5915,7 @@
         <v>126091037</v>
       </c>
       <c r="B53" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5909,6 +5941,14 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
@@ -6090,7 +6130,7 @@
         <v>126091161</v>
       </c>
       <c r="B55" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6196,7 +6236,7 @@
         <v>126091026</v>
       </c>
       <c r="B56" t="n">
-        <v>91942</v>
+        <v>92027</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6297,7 +6337,7 @@
         <v>126091134</v>
       </c>
       <c r="B57" t="n">
-        <v>91263</v>
+        <v>91348</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6398,7 +6438,7 @@
         <v>126091139</v>
       </c>
       <c r="B58" t="n">
-        <v>91263</v>
+        <v>91348</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6499,7 +6539,7 @@
         <v>126091054</v>
       </c>
       <c r="B59" t="n">
-        <v>98382</v>
+        <v>98469</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6600,7 +6640,7 @@
         <v>126091057</v>
       </c>
       <c r="B60" t="n">
-        <v>98382</v>
+        <v>98469</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6701,7 +6741,7 @@
         <v>126091082</v>
       </c>
       <c r="B61" t="n">
-        <v>80084</v>
+        <v>80122</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6802,7 +6842,7 @@
         <v>126091091</v>
       </c>
       <c r="B62" t="n">
-        <v>79987</v>
+        <v>80025</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7004,7 +7044,7 @@
         <v>126091116</v>
       </c>
       <c r="B64" t="n">
-        <v>57813</v>
+        <v>57817</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7105,7 +7145,7 @@
         <v>126091056</v>
       </c>
       <c r="B65" t="n">
-        <v>98382</v>
+        <v>98469</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7206,7 +7246,7 @@
         <v>126091136</v>
       </c>
       <c r="B66" t="n">
-        <v>91263</v>
+        <v>91348</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7307,7 +7347,7 @@
         <v>126091081</v>
       </c>
       <c r="B67" t="n">
-        <v>80084</v>
+        <v>80122</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7408,7 +7448,7 @@
         <v>126091155</v>
       </c>
       <c r="B68" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7509,7 +7549,7 @@
         <v>126091086</v>
       </c>
       <c r="B69" t="n">
-        <v>80084</v>
+        <v>80122</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7610,7 +7650,7 @@
         <v>126091046</v>
       </c>
       <c r="B70" t="n">
-        <v>80112</v>
+        <v>80150</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7711,7 +7751,7 @@
         <v>126091103</v>
       </c>
       <c r="B71" t="n">
-        <v>80083</v>
+        <v>80121</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7812,7 +7852,7 @@
         <v>126091154</v>
       </c>
       <c r="B72" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
